--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AB91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,54 +437,51 @@
         <v>scopeNote</v>
       </c>
       <c r="M1" t="str">
-        <v>relevantLZS</v>
+        <v>relevantProperty</v>
       </c>
       <c r="N1" t="str">
-        <v>relevantProperty</v>
+        <v>maxValue</v>
       </c>
       <c r="O1" t="str">
-        <v>maxValue</v>
+        <v>operatie</v>
       </c>
       <c r="P1" t="str">
-        <v>operatie</v>
+        <v>minValue</v>
       </c>
       <c r="Q1" t="str">
-        <v>minValue</v>
+        <v>subject</v>
       </c>
       <c r="R1" t="str">
-        <v>subject</v>
+        <v>relevantQuantityKind</v>
       </c>
       <c r="S1" t="str">
-        <v>relevantQuantityKind</v>
+        <v>seeAlso</v>
       </c>
       <c r="T1" t="str">
-        <v>seeAlso</v>
+        <v>relevantCodeList</v>
       </c>
       <c r="U1" t="str">
-        <v>relevantCodeList</v>
+        <v>referentiewaardeType</v>
       </c>
       <c r="V1" t="str">
-        <v>referentiewaardeType</v>
+        <v>technischefiche</v>
       </c>
       <c r="W1" t="str">
-        <v>technischefiche</v>
+        <v>broader</v>
       </c>
       <c r="X1" t="str">
-        <v>broader</v>
+        <v>broaderTransitive</v>
       </c>
       <c r="Y1" t="str">
-        <v>broaderTransitive</v>
+        <v>semanticRelation</v>
       </c>
       <c r="Z1" t="str">
-        <v>semanticRelation</v>
+        <v>narrower</v>
       </c>
       <c r="AA1" t="str">
-        <v>narrower</v>
+        <v>narrowerTransitive</v>
       </c>
       <c r="AB1" t="str">
-        <v>narrowerTransitive</v>
-      </c>
-      <c r="AC1" t="str">
         <v>hasTopConcept</v>
       </c>
     </row>
@@ -573,9 +570,6 @@
       <c r="AB2" t="str">
         <v>null</v>
       </c>
-      <c r="AC2" t="str">
-        <v>null</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -662,9 +656,6 @@
       <c r="AB3" t="str">
         <v>null</v>
       </c>
-      <c r="AC3" t="str">
-        <v>null</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -751,9 +742,6 @@
       <c r="AB4" t="str">
         <v>null</v>
       </c>
-      <c r="AC4" t="str">
-        <v>null</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -840,9 +828,6 @@
       <c r="AB5" t="str">
         <v>null</v>
       </c>
-      <c r="AC5" t="str">
-        <v>null</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -929,9 +914,6 @@
       <c r="AB6" t="str">
         <v>null</v>
       </c>
-      <c r="AC6" t="str">
-        <v>null</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1018,9 +1000,6 @@
       <c r="AB7" t="str">
         <v>null</v>
       </c>
-      <c r="AC7" t="str">
-        <v>null</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -1107,13 +1086,10 @@
       <c r="AB8" t="str">
         <v>null</v>
       </c>
-      <c r="AC8" t="str">
-        <v>null</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/dataleverancierstatus/gevalideerd</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/dataleverancierstatus/gevalideerd</v>
       </c>
       <c r="B9" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1125,7 +1101,7 @@
         <v>null</v>
       </c>
       <c r="E9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/dataleverancierstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/dataleverancierstatus</v>
       </c>
       <c r="F9" t="str">
         <v>gevalideerd</v>
@@ -1134,7 +1110,7 @@
         <v>Gevalideerd</v>
       </c>
       <c r="H9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/dataleverancierstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/dataleverancierstatus</v>
       </c>
       <c r="I9" t="str">
         <v>null</v>
@@ -1194,15 +1170,12 @@
         <v>null</v>
       </c>
       <c r="AB9" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC9" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/dataleverancierstatus/geweigerd</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/dataleverancierstatus/geweigerd</v>
       </c>
       <c r="B10" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1214,7 +1187,7 @@
         <v>null</v>
       </c>
       <c r="E10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/dataleverancierstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/dataleverancierstatus</v>
       </c>
       <c r="F10" t="str">
         <v>geweigerd</v>
@@ -1223,7 +1196,7 @@
         <v>Geweigerd</v>
       </c>
       <c r="H10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/dataleverancierstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/dataleverancierstatus</v>
       </c>
       <c r="I10" t="str">
         <v>null</v>
@@ -1283,15 +1256,12 @@
         <v>null</v>
       </c>
       <c r="AB10" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC10" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/dataleverancierstatus/ingetrokken</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/dataleverancierstatus/ingetrokken</v>
       </c>
       <c r="B11" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1303,7 +1273,7 @@
         <v>null</v>
       </c>
       <c r="E11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/dataleverancierstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/dataleverancierstatus</v>
       </c>
       <c r="F11" t="str">
         <v>ingetrokken</v>
@@ -1312,7 +1282,7 @@
         <v>Ingetrokken</v>
       </c>
       <c r="H11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/dataleverancierstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/dataleverancierstatus</v>
       </c>
       <c r="I11" t="str">
         <v>null</v>
@@ -1372,15 +1342,12 @@
         <v>null</v>
       </c>
       <c r="AB11" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC11" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/dataleverancierstatus/nietgevalideerd</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/dataleverancierstatus/nietgevalideerd</v>
       </c>
       <c r="B12" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1392,7 +1359,7 @@
         <v>null</v>
       </c>
       <c r="E12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/dataleverancierstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/dataleverancierstatus</v>
       </c>
       <c r="F12" t="str">
         <v>nietgevalideerd</v>
@@ -1401,7 +1368,7 @@
         <v>Niet gevalideerd</v>
       </c>
       <c r="H12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/dataleverancierstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/dataleverancierstatus</v>
       </c>
       <c r="I12" t="str">
         <v>null</v>
@@ -1461,15 +1428,12 @@
         <v>null</v>
       </c>
       <c r="AB12" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC12" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/hetelektronischmonitoringssysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/hetelektronischmonitoringssysteem</v>
       </c>
       <c r="B13" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
@@ -1481,7 +1445,7 @@
         <v>null</v>
       </c>
       <c r="E13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/medium</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/medium</v>
       </c>
       <c r="F13" t="str">
         <v>null</v>
@@ -1490,7 +1454,7 @@
         <v>Het elektronisch monitoringssysteem</v>
       </c>
       <c r="H13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/medium</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/medium</v>
       </c>
       <c r="I13" t="str">
         <v>null</v>
@@ -1550,15 +1514,12 @@
         <v>null</v>
       </c>
       <c r="AB13" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC13" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/lucht</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/lucht</v>
       </c>
       <c r="B14" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
@@ -1570,7 +1531,7 @@
         <v>null</v>
       </c>
       <c r="E14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/medium</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/medium</v>
       </c>
       <c r="F14" t="str">
         <v>null</v>
@@ -1579,7 +1540,7 @@
         <v>Lucht</v>
       </c>
       <c r="H14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/medium</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/medium</v>
       </c>
       <c r="I14" t="str">
         <v>null</v>
@@ -1639,15 +1600,12 @@
         <v>null</v>
       </c>
       <c r="AB14" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC14" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/spuiwater</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/spuiwater</v>
       </c>
       <c r="B15" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
@@ -1659,7 +1617,7 @@
         <v>null</v>
       </c>
       <c r="E15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/medium</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/medium</v>
       </c>
       <c r="F15" t="str">
         <v>null</v>
@@ -1668,7 +1626,7 @@
         <v>Spuiwater</v>
       </c>
       <c r="H15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/medium</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/medium</v>
       </c>
       <c r="I15" t="str">
         <v>null</v>
@@ -1728,15 +1686,12 @@
         <v>null</v>
       </c>
       <c r="AB15" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC15" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/stal</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/stal</v>
       </c>
       <c r="B16" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
@@ -1748,7 +1703,7 @@
         <v>null</v>
       </c>
       <c r="E16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/medium</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/medium</v>
       </c>
       <c r="F16" t="str">
         <v>null</v>
@@ -1757,7 +1712,7 @@
         <v>Stal</v>
       </c>
       <c r="H16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/medium</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/medium</v>
       </c>
       <c r="I16" t="str">
         <v>null</v>
@@ -1817,15 +1772,12 @@
         <v>null</v>
       </c>
       <c r="AB16" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC16" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/waswater</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/waswater</v>
       </c>
       <c r="B17" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
@@ -1837,7 +1789,7 @@
         <v>null</v>
       </c>
       <c r="E17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/medium</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/medium</v>
       </c>
       <c r="F17" t="str">
         <v>null</v>
@@ -1846,7 +1798,7 @@
         <v>Waswater</v>
       </c>
       <c r="H17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/medium</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/medium</v>
       </c>
       <c r="I17" t="str">
         <v>null</v>
@@ -1906,15 +1858,12 @@
         <v>null</v>
       </c>
       <c r="AB17" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC17" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_1</v>
       </c>
       <c r="B18" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1926,7 +1875,7 @@
         <v>null</v>
       </c>
       <c r="E18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F18" t="str">
         <v>null</v>
@@ -1935,7 +1884,7 @@
         <v>Zuurtegraad waswater &lt; 6 (S1 systeem)</v>
       </c>
       <c r="H18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I18" t="str">
         <v>Onder minimum grenswaarde</v>
@@ -1950,13 +1899,13 @@
         <v>&lt; 6</v>
       </c>
       <c r="M18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/zuurtegraadwaswater</v>
       </c>
       <c r="N18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/zuurtegraadwaswater</v>
+        <v>6</v>
       </c>
       <c r="O18" t="str">
-        <v>6</v>
+        <v>null</v>
       </c>
       <c r="P18" t="str">
         <v>null</v>
@@ -1995,15 +1944,12 @@
         <v>null</v>
       </c>
       <c r="AB18" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC18" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_10</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_10</v>
       </c>
       <c r="B19" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2015,7 +1961,7 @@
         <v>null</v>
       </c>
       <c r="E19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F19" t="str">
         <v>null</v>
@@ -2024,7 +1970,7 @@
         <v>Waswaterdebiet afwijking naar beneden &gt; 20% (S2 systeem)</v>
       </c>
       <c r="H19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I19" t="str">
         <v>Onder minimum grenswaarde</v>
@@ -2039,16 +1985,16 @@
         <v>&lt; 0,8 x waarde technische fiche (afwijking &gt; 20%)</v>
       </c>
       <c r="M19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebiet</v>
       </c>
       <c r="N19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebiet</v>
+        <v>0.8</v>
       </c>
       <c r="O19" t="str">
-        <v>0.8</v>
+        <v>product</v>
       </c>
       <c r="P19" t="str">
-        <v>product</v>
+        <v>null</v>
       </c>
       <c r="Q19" t="str">
         <v>null</v>
@@ -2084,15 +2030,12 @@
         <v>null</v>
       </c>
       <c r="AB19" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC19" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_11</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_11</v>
       </c>
       <c r="B20" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2104,7 +2047,7 @@
         <v>null</v>
       </c>
       <c r="E20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F20" t="str">
         <v>null</v>
@@ -2113,7 +2056,7 @@
         <v>Spuiwaterdebiet afwijking naar beneden &gt; 10% (S2 systeem)</v>
       </c>
       <c r="H20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I20" t="str">
         <v>Onder minimum grenswaarde</v>
@@ -2128,16 +2071,16 @@
         <v>&lt; 0,9 x waarde technische fiche (afwijking &gt; 10%)</v>
       </c>
       <c r="M20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/spuiwaterproductie</v>
       </c>
       <c r="N20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/spuiwaterproductie</v>
+        <v>0.9</v>
       </c>
       <c r="O20" t="str">
-        <v>0.9</v>
+        <v>product</v>
       </c>
       <c r="P20" t="str">
-        <v>product</v>
+        <v>null</v>
       </c>
       <c r="Q20" t="str">
         <v>null</v>
@@ -2173,15 +2116,12 @@
         <v>null</v>
       </c>
       <c r="AB20" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC20" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_12</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_12</v>
       </c>
       <c r="B21" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2193,7 +2133,7 @@
         <v>null</v>
       </c>
       <c r="E21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F21" t="str">
         <v>null</v>
@@ -2202,7 +2142,7 @@
         <v>Drukval afwijking naar beneden &gt; 40% (S2 systeem)</v>
       </c>
       <c r="H21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I21" t="str">
         <v>Onder minimum grenswaarde</v>
@@ -2217,16 +2157,16 @@
         <v>&lt; 0,6 x waarde technische fiche (afwijking &gt; 40%)</v>
       </c>
       <c r="M21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/drukvaloverhetsysteem</v>
       </c>
       <c r="N21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem</v>
+        <v>0.6</v>
       </c>
       <c r="O21" t="str">
-        <v>0.6</v>
+        <v>product</v>
       </c>
       <c r="P21" t="str">
-        <v>product</v>
+        <v>null</v>
       </c>
       <c r="Q21" t="str">
         <v>null</v>
@@ -2262,15 +2202,12 @@
         <v>null</v>
       </c>
       <c r="AB21" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC21" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_13</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_13</v>
       </c>
       <c r="B22" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2282,7 +2219,7 @@
         <v>null</v>
       </c>
       <c r="E22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F22" t="str">
         <v>null</v>
@@ -2291,7 +2228,7 @@
         <v>Drukval afwijking naar boven &gt; 40% (S2 systeem)</v>
       </c>
       <c r="H22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I22" t="str">
         <v>Boven maximum grenswaarde</v>
@@ -2306,19 +2243,19 @@
         <v>&gt; 1,4 x waarde technische fiche (afwijking &gt; 40%)</v>
       </c>
       <c r="M22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/drukvaloverhetsysteem</v>
       </c>
       <c r="N22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem</v>
+        <v>null</v>
       </c>
       <c r="O22" t="str">
-        <v>null</v>
+        <v>product</v>
       </c>
       <c r="P22" t="str">
-        <v>product</v>
+        <v>1.4</v>
       </c>
       <c r="Q22" t="str">
-        <v>1.4</v>
+        <v>null</v>
       </c>
       <c r="R22" t="str">
         <v>null</v>
@@ -2351,15 +2288,12 @@
         <v>null</v>
       </c>
       <c r="AB22" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC22" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_14</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_14</v>
       </c>
       <c r="B23" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2371,7 +2305,7 @@
         <v>null</v>
       </c>
       <c r="E23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F23" t="str">
         <v>null</v>
@@ -2380,7 +2314,7 @@
         <v>Waswaterdebiet voorbevochtiging afwijking naar beneden &gt; 20% (S3 systeem)</v>
       </c>
       <c r="H23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I23" t="str">
         <v>Onder minimum grenswaarde</v>
@@ -2395,16 +2329,16 @@
         <v>&lt; 0,8 x waarde technische fiche (afwijking &gt; 20%)</v>
       </c>
       <c r="M23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebietvoorbevochtiging</v>
       </c>
       <c r="N23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebietvoorbevochtiging</v>
+        <v>0.8</v>
       </c>
       <c r="O23" t="str">
-        <v>0.8</v>
+        <v>product</v>
       </c>
       <c r="P23" t="str">
-        <v>product</v>
+        <v>null</v>
       </c>
       <c r="Q23" t="str">
         <v>null</v>
@@ -2440,15 +2374,12 @@
         <v>null</v>
       </c>
       <c r="AB23" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC23" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_15</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_15</v>
       </c>
       <c r="B24" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2460,7 +2391,7 @@
         <v>null</v>
       </c>
       <c r="E24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F24" t="str">
         <v>null</v>
@@ -2469,7 +2400,7 @@
         <v>Waswaterdebiet bevloeiing afwijking naar beneden &gt; 20% (S3 systeem)</v>
       </c>
       <c r="H24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I24" t="str">
         <v>Onder minimum grenswaarde</v>
@@ -2484,16 +2415,16 @@
         <v>&lt; 0,8 x waarde technische fiche (afwijking &gt; 20%)</v>
       </c>
       <c r="M24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebietbevloeiing</v>
       </c>
       <c r="N24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebietbevloeiing</v>
+        <v>0.8</v>
       </c>
       <c r="O24" t="str">
-        <v>0.8</v>
+        <v>product</v>
       </c>
       <c r="P24" t="str">
-        <v>product</v>
+        <v>null</v>
       </c>
       <c r="Q24" t="str">
         <v>null</v>
@@ -2529,15 +2460,12 @@
         <v>null</v>
       </c>
       <c r="AB24" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC24" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_16</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_16</v>
       </c>
       <c r="B25" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2549,7 +2477,7 @@
         <v>null</v>
       </c>
       <c r="E25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F25" t="str">
         <v>null</v>
@@ -2558,7 +2486,7 @@
         <v>Drukval afwijking naar boven &gt; 50 Pa (S3 systeem)</v>
       </c>
       <c r="H25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I25" t="str">
         <v>Boven maximum grenswaarde</v>
@@ -2573,19 +2501,19 @@
         <v>&gt; 50 Pa + waarde technische fiche (afwijking &gt; 50 Pa)</v>
       </c>
       <c r="M25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/drukvaloverhetsysteem</v>
       </c>
       <c r="N25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem</v>
+        <v>null</v>
       </c>
       <c r="O25" t="str">
-        <v>null</v>
+        <v>som</v>
       </c>
       <c r="P25" t="str">
-        <v>som</v>
+        <v>50</v>
       </c>
       <c r="Q25" t="str">
-        <v>50</v>
+        <v>null</v>
       </c>
       <c r="R25" t="str">
         <v>null</v>
@@ -2618,15 +2546,12 @@
         <v>null</v>
       </c>
       <c r="AB25" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC25" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_2</v>
       </c>
       <c r="B26" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2638,7 +2563,7 @@
         <v>null</v>
       </c>
       <c r="E26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F26" t="str">
         <v>null</v>
@@ -2647,7 +2572,7 @@
         <v>Zuurtegraad waswater &gt; 8,5 (S1 systeem)</v>
       </c>
       <c r="H26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I26" t="str">
         <v>Boven maximum grenswaarde</v>
@@ -2662,19 +2587,19 @@
         <v>&gt; 8,5</v>
       </c>
       <c r="M26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/zuurtegraadwaswater</v>
       </c>
       <c r="N26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/zuurtegraadwaswater</v>
+        <v>null</v>
       </c>
       <c r="O26" t="str">
         <v>null</v>
       </c>
       <c r="P26" t="str">
-        <v>null</v>
+        <v>8.5</v>
       </c>
       <c r="Q26" t="str">
-        <v>8.5</v>
+        <v>null</v>
       </c>
       <c r="R26" t="str">
         <v>null</v>
@@ -2707,15 +2632,12 @@
         <v>null</v>
       </c>
       <c r="AB26" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC26" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_3</v>
       </c>
       <c r="B27" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2727,7 +2649,7 @@
         <v>null</v>
       </c>
       <c r="E27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F27" t="str">
         <v>null</v>
@@ -2736,7 +2658,7 @@
         <v>Geleidbaarheid waswater &gt; maximale waarde (S1 systeem)</v>
       </c>
       <c r="H27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I27" t="str">
         <v>Boven maximum grenswaarde</v>
@@ -2751,19 +2673,19 @@
         <v>&gt; waarde technische fiche</v>
       </c>
       <c r="M27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/geleidbaarheidvanhetwaswater</v>
       </c>
       <c r="N27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/geleidbaarheidvanhetwaswater</v>
+        <v>null</v>
       </c>
       <c r="O27" t="str">
-        <v>null</v>
+        <v>som</v>
       </c>
       <c r="P27" t="str">
-        <v>som</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R27" t="str">
         <v>null</v>
@@ -2796,15 +2718,12 @@
         <v>null</v>
       </c>
       <c r="AB27" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC27" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_4</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_4</v>
       </c>
       <c r="B28" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2816,7 +2735,7 @@
         <v>null</v>
       </c>
       <c r="E28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F28" t="str">
         <v>null</v>
@@ -2825,7 +2744,7 @@
         <v>Waswaterdebiet afwijking naar beneden &gt; 20% (S1 systeem)</v>
       </c>
       <c r="H28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I28" t="str">
         <v>Onder minimum grenswaarde</v>
@@ -2840,16 +2759,16 @@
         <v>&lt; 0,8 x waarde technische fiche (afwijking &gt; 20%)</v>
       </c>
       <c r="M28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebiet</v>
       </c>
       <c r="N28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebiet</v>
+        <v>0.8</v>
       </c>
       <c r="O28" t="str">
-        <v>0.8</v>
+        <v>product</v>
       </c>
       <c r="P28" t="str">
-        <v>product</v>
+        <v>null</v>
       </c>
       <c r="Q28" t="str">
         <v>null</v>
@@ -2885,15 +2804,12 @@
         <v>null</v>
       </c>
       <c r="AB28" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC28" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_5</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_5</v>
       </c>
       <c r="B29" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2905,7 +2821,7 @@
         <v>null</v>
       </c>
       <c r="E29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F29" t="str">
         <v>null</v>
@@ -2914,7 +2830,7 @@
         <v>Spuiwaterdebiet afwijking naar beneden &gt; 10% (S1 systeem)</v>
       </c>
       <c r="H29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I29" t="str">
         <v>Onder minimum grenswaarde</v>
@@ -2929,16 +2845,16 @@
         <v>&lt; 0,9 x waarde technische fiche (afwijking &gt; 10%)</v>
       </c>
       <c r="M29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/spuiwaterproductie</v>
       </c>
       <c r="N29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/spuiwaterproductie</v>
+        <v>0.9</v>
       </c>
       <c r="O29" t="str">
-        <v>0.9</v>
+        <v>product</v>
       </c>
       <c r="P29" t="str">
-        <v>product</v>
+        <v>null</v>
       </c>
       <c r="Q29" t="str">
         <v>null</v>
@@ -2974,15 +2890,12 @@
         <v>null</v>
       </c>
       <c r="AB29" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC29" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_6</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_6</v>
       </c>
       <c r="B30" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2994,7 +2907,7 @@
         <v>null</v>
       </c>
       <c r="E30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F30" t="str">
         <v>null</v>
@@ -3003,7 +2916,7 @@
         <v>Drukval afwijking naar beneden &gt; 40% (S1 systeem)</v>
       </c>
       <c r="H30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I30" t="str">
         <v>Onder minimum grenswaarde</v>
@@ -3018,16 +2931,16 @@
         <v>&lt; 0,6 x waarde technische fiche (afwijking &gt; 40%)</v>
       </c>
       <c r="M30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/drukvaloverhetsysteem</v>
       </c>
       <c r="N30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem</v>
+        <v>0.6</v>
       </c>
       <c r="O30" t="str">
-        <v>0.6</v>
+        <v>product</v>
       </c>
       <c r="P30" t="str">
-        <v>product</v>
+        <v>null</v>
       </c>
       <c r="Q30" t="str">
         <v>null</v>
@@ -3063,15 +2976,12 @@
         <v>null</v>
       </c>
       <c r="AB30" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC30" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_7</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_7</v>
       </c>
       <c r="B31" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -3083,7 +2993,7 @@
         <v>null</v>
       </c>
       <c r="E31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F31" t="str">
         <v>null</v>
@@ -3092,7 +3002,7 @@
         <v>Drukval afwijking naar boven &gt; 40% (S1 systeem)</v>
       </c>
       <c r="H31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I31" t="str">
         <v>Boven maximum grenswaarde</v>
@@ -3107,19 +3017,19 @@
         <v>&gt; 1,4 x waarde technische fiche (afwijking &gt; 40%)</v>
       </c>
       <c r="M31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/drukvaloverhetsysteem</v>
       </c>
       <c r="N31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem</v>
+        <v>null</v>
       </c>
       <c r="O31" t="str">
-        <v>null</v>
+        <v>product</v>
       </c>
       <c r="P31" t="str">
-        <v>product</v>
+        <v>1.4</v>
       </c>
       <c r="Q31" t="str">
-        <v>1.4</v>
+        <v>null</v>
       </c>
       <c r="R31" t="str">
         <v>null</v>
@@ -3152,15 +3062,12 @@
         <v>null</v>
       </c>
       <c r="AB31" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC31" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_8</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_8</v>
       </c>
       <c r="B32" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -3172,7 +3079,7 @@
         <v>null</v>
       </c>
       <c r="E32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F32" t="str">
         <v>null</v>
@@ -3181,7 +3088,7 @@
         <v>Zuurtegraad waswater afwijking naar boven &gt; 1 pH-eenheid (S2 systeem)</v>
       </c>
       <c r="H32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I32" t="str">
         <v>Boven maximum grenswaarde</v>
@@ -3196,19 +3103,19 @@
         <v>&gt; 1 pH + waarde technische fiche (afwijking &gt; 1pH)</v>
       </c>
       <c r="M32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/zuurtegraadwaswater</v>
       </c>
       <c r="N32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/zuurtegraadwaswater</v>
+        <v>null</v>
       </c>
       <c r="O32" t="str">
-        <v>null</v>
+        <v>som</v>
       </c>
       <c r="P32" t="str">
-        <v>som</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="str">
-        <v>1</v>
+        <v>null</v>
       </c>
       <c r="R32" t="str">
         <v>null</v>
@@ -3241,15 +3148,12 @@
         <v>null</v>
       </c>
       <c r="AB32" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC32" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_9</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_9</v>
       </c>
       <c r="B33" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -3261,7 +3165,7 @@
         <v>null</v>
       </c>
       <c r="E33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="F33" t="str">
         <v>null</v>
@@ -3270,7 +3174,7 @@
         <v>Geleidbaarheid waswater &gt; maximale waarde (S2 systeem)</v>
       </c>
       <c r="H33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="I33" t="str">
         <v>Boven maximum grenswaarde</v>
@@ -3285,19 +3189,19 @@
         <v>&gt; waarde technische fiche</v>
       </c>
       <c r="M33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/geleidbaarheidvanhetwaswater</v>
       </c>
       <c r="N33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/geleidbaarheidvanhetwaswater</v>
+        <v>null</v>
       </c>
       <c r="O33" t="str">
-        <v>null</v>
+        <v>som</v>
       </c>
       <c r="P33" t="str">
-        <v>som</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R33" t="str">
         <v>null</v>
@@ -3330,15 +3234,12 @@
         <v>null</v>
       </c>
       <c r="AB33" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC33" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/biobedspoelwaterproductie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/biobedspoelwaterproductie</v>
       </c>
       <c r="B34" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -3350,7 +3251,7 @@
         <v>null</v>
       </c>
       <c r="E34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F34" t="str">
         <v>null</v>
@@ -3359,7 +3260,7 @@
         <v>Biobedspoelwaterproductie</v>
       </c>
       <c r="H34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I34" t="str">
         <v>null</v>
@@ -3374,7 +3275,7 @@
         <v>null</v>
       </c>
       <c r="M34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>null</v>
       </c>
       <c r="N34" t="str">
         <v>null</v>
@@ -3386,16 +3287,16 @@
         <v>null</v>
       </c>
       <c r="Q34" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/waswater</v>
       </c>
       <c r="R34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/waswater</v>
+        <v>http://qudt.org/vocab/quantitykind/Volume</v>
       </c>
       <c r="S34" t="str">
-        <v>http://qudt.org/vocab/quantitykind/Volume</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0053</v>
       </c>
       <c r="T34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0053</v>
+        <v>null</v>
       </c>
       <c r="U34" t="str">
         <v>null</v>
@@ -3419,15 +3320,12 @@
         <v>null</v>
       </c>
       <c r="AB34" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC34" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/biobedspuiwaterproductie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/biobedspuiwaterproductie</v>
       </c>
       <c r="B35" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -3439,7 +3337,7 @@
         <v>null</v>
       </c>
       <c r="E35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F35" t="str">
         <v>null</v>
@@ -3448,7 +3346,7 @@
         <v>Biobedspuiwaterproductie</v>
       </c>
       <c r="H35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I35" t="str">
         <v>null</v>
@@ -3463,7 +3361,7 @@
         <v>null</v>
       </c>
       <c r="M35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>null</v>
       </c>
       <c r="N35" t="str">
         <v>null</v>
@@ -3475,16 +3373,16 @@
         <v>null</v>
       </c>
       <c r="Q35" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/spuiwater</v>
       </c>
       <c r="R35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/spuiwater</v>
+        <v>http://qudt.org/vocab/quantitykind/Volume</v>
       </c>
       <c r="S35" t="str">
-        <v>http://qudt.org/vocab/quantitykind/Volume</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0050</v>
       </c>
       <c r="T35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0050</v>
+        <v>null</v>
       </c>
       <c r="U35" t="str">
         <v>null</v>
@@ -3508,15 +3406,12 @@
         <v>null</v>
       </c>
       <c r="AB35" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC35" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/drukvaloverhetsysteem</v>
       </c>
       <c r="B36" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -3528,7 +3423,7 @@
         <v>null</v>
       </c>
       <c r="E36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F36" t="str">
         <v>null</v>
@@ -3537,7 +3432,7 @@
         <v>Drukval over het systeem</v>
       </c>
       <c r="H36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I36" t="str">
         <v>null</v>
@@ -3552,7 +3447,7 @@
         <v>null</v>
       </c>
       <c r="M36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>null</v>
       </c>
       <c r="N36" t="str">
         <v>null</v>
@@ -3564,16 +3459,16 @@
         <v>null</v>
       </c>
       <c r="Q36" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/lucht</v>
       </c>
       <c r="R36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/lucht</v>
+        <v>http://qudt.org/vocab/quantitykind/VaporPressure</v>
       </c>
       <c r="S36" t="str">
-        <v>http://qudt.org/vocab/quantitykind/VaporPressure</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0329</v>
       </c>
       <c r="T36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0329</v>
+        <v>null</v>
       </c>
       <c r="U36" t="str">
         <v>null</v>
@@ -3597,15 +3492,12 @@
         <v>null</v>
       </c>
       <c r="AB36" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC36" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/elektriciteitsverbruikwaterpompen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/elektriciteitsverbruikwaterpompen</v>
       </c>
       <c r="B37" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -3617,7 +3509,7 @@
         <v>null</v>
       </c>
       <c r="E37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F37" t="str">
         <v>null</v>
@@ -3626,7 +3518,7 @@
         <v>Elektriciteitsverbruik van de waswaterpomp(en)</v>
       </c>
       <c r="H37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I37" t="str">
         <v>null</v>
@@ -3641,7 +3533,7 @@
         <v>null</v>
       </c>
       <c r="M37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere</v>
+        <v>null</v>
       </c>
       <c r="N37" t="str">
         <v>null</v>
@@ -3656,10 +3548,10 @@
         <v>null</v>
       </c>
       <c r="R37" t="str">
-        <v>null</v>
+        <v>http://qudt.org/vocab/quantitykind/Energy</v>
       </c>
       <c r="S37" t="str">
-        <v>http://qudt.org/vocab/quantitykind/Energy</v>
+        <v>null</v>
       </c>
       <c r="T37" t="str">
         <v>null</v>
@@ -3686,15 +3578,12 @@
         <v>null</v>
       </c>
       <c r="AB37" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC37" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/geleidbaarheidvanhetwaswater</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/geleidbaarheidvanhetwaswater</v>
       </c>
       <c r="B38" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -3706,7 +3595,7 @@
         <v>null</v>
       </c>
       <c r="E38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F38" t="str">
         <v>null</v>
@@ -3715,7 +3604,7 @@
         <v>Geleidbaarheid van het waswater</v>
       </c>
       <c r="H38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I38" t="str">
         <v>null</v>
@@ -3730,7 +3619,7 @@
         <v>null</v>
       </c>
       <c r="M38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere</v>
+        <v>null</v>
       </c>
       <c r="N38" t="str">
         <v>null</v>
@@ -3742,16 +3631,16 @@
         <v>null</v>
       </c>
       <c r="Q38" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/waswater</v>
       </c>
       <c r="R38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/waswater</v>
+        <v>http://qudt.org/vocab/quantitykind/Conductivity</v>
       </c>
       <c r="S38" t="str">
-        <v>http://qudt.org/vocab/quantitykind/Conductivity</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0010</v>
       </c>
       <c r="T38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0010</v>
+        <v>null</v>
       </c>
       <c r="U38" t="str">
         <v>null</v>
@@ -3775,15 +3664,12 @@
         <v>null</v>
       </c>
       <c r="AB38" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC38" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/spuiwaterproductie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/spuiwaterproductie</v>
       </c>
       <c r="B39" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -3795,7 +3681,7 @@
         <v>null</v>
       </c>
       <c r="E39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F39" t="str">
         <v>null</v>
@@ -3804,7 +3690,7 @@
         <v>Spuiwaterproductie</v>
       </c>
       <c r="H39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I39" t="str">
         <v>null</v>
@@ -3819,7 +3705,7 @@
         <v>null</v>
       </c>
       <c r="M39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere</v>
+        <v>null</v>
       </c>
       <c r="N39" t="str">
         <v>null</v>
@@ -3831,16 +3717,16 @@
         <v>null</v>
       </c>
       <c r="Q39" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/spuiwater</v>
       </c>
       <c r="R39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/spuiwater</v>
+        <v>http://qudt.org/vocab/quantitykind/Volume</v>
       </c>
       <c r="S39" t="str">
-        <v>http://qudt.org/vocab/quantitykind/Volume</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0050</v>
       </c>
       <c r="T39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0050</v>
+        <v>null</v>
       </c>
       <c r="U39" t="str">
         <v>null</v>
@@ -3864,15 +3750,12 @@
         <v>null</v>
       </c>
       <c r="AB39" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC39" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/stalbezetting</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/stalbezetting</v>
       </c>
       <c r="B40" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -3884,7 +3767,7 @@
         <v>null</v>
       </c>
       <c r="E40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F40" t="str">
         <v>null</v>
@@ -3893,7 +3776,7 @@
         <v>Stalbezetting</v>
       </c>
       <c r="H40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I40" t="str">
         <v>null</v>
@@ -3908,7 +3791,7 @@
         <v>null</v>
       </c>
       <c r="M40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>null</v>
       </c>
       <c r="N40" t="str">
         <v>null</v>
@@ -3920,19 +3803,19 @@
         <v>null</v>
       </c>
       <c r="Q40" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/stal</v>
       </c>
       <c r="R40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/stal</v>
+        <v>null</v>
       </c>
       <c r="S40" t="str">
         <v>null</v>
       </c>
       <c r="T40" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/stalbezetting</v>
       </c>
       <c r="U40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/stalbezetting</v>
+        <v>null</v>
       </c>
       <c r="V40" t="str">
         <v>null</v>
@@ -3953,15 +3836,12 @@
         <v>null</v>
       </c>
       <c r="AB40" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC40" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/systeemstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/systeemstatus</v>
       </c>
       <c r="B41" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -3973,7 +3853,7 @@
         <v>null</v>
       </c>
       <c r="E41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F41" t="str">
         <v>null</v>
@@ -3982,7 +3862,7 @@
         <v>SysteemStatus</v>
       </c>
       <c r="H41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I41" t="str">
         <v>null</v>
@@ -3997,7 +3877,7 @@
         <v>null</v>
       </c>
       <c r="M41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>null</v>
       </c>
       <c r="N41" t="str">
         <v>null</v>
@@ -4009,19 +3889,19 @@
         <v>null</v>
       </c>
       <c r="Q41" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/hetelektronischmonitoringssysteem</v>
       </c>
       <c r="R41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/hetelektronischmonitoringssysteem</v>
+        <v>null</v>
       </c>
       <c r="S41" t="str">
         <v>null</v>
       </c>
       <c r="T41" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemstatus</v>
       </c>
       <c r="U41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemstatus</v>
+        <v>null</v>
       </c>
       <c r="V41" t="str">
         <v>null</v>
@@ -4042,15 +3922,12 @@
         <v>null</v>
       </c>
       <c r="AB41" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC41" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebiet</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebiet</v>
       </c>
       <c r="B42" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -4062,7 +3939,7 @@
         <v>null</v>
       </c>
       <c r="E42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F42" t="str">
         <v>null</v>
@@ -4071,7 +3948,7 @@
         <v>Waswaterdebiet over het waspakket</v>
       </c>
       <c r="H42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I42" t="str">
         <v>null</v>
@@ -4086,7 +3963,7 @@
         <v>null</v>
       </c>
       <c r="M42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere</v>
+        <v>null</v>
       </c>
       <c r="N42" t="str">
         <v>null</v>
@@ -4098,16 +3975,16 @@
         <v>null</v>
       </c>
       <c r="Q42" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/waswater</v>
       </c>
       <c r="R42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/waswater</v>
+        <v>http://qudt.org/vocab/quantitykind/VolumeFlowRate</v>
       </c>
       <c r="S42" t="str">
-        <v>http://qudt.org/vocab/quantitykind/VolumeFlowRate</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0053</v>
       </c>
       <c r="T42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0053</v>
+        <v>null</v>
       </c>
       <c r="U42" t="str">
         <v>null</v>
@@ -4131,15 +4008,12 @@
         <v>null</v>
       </c>
       <c r="AB42" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC42" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebietbevloeiing</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebietbevloeiing</v>
       </c>
       <c r="B43" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -4151,7 +4025,7 @@
         <v>null</v>
       </c>
       <c r="E43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F43" t="str">
         <v>null</v>
@@ -4160,7 +4034,7 @@
         <v>Waswaterdebiet van de bevloeiing van het vulmateriaal</v>
       </c>
       <c r="H43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I43" t="str">
         <v>null</v>
@@ -4175,7 +4049,7 @@
         <v>null</v>
       </c>
       <c r="M43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>null</v>
       </c>
       <c r="N43" t="str">
         <v>null</v>
@@ -4187,16 +4061,16 @@
         <v>null</v>
       </c>
       <c r="Q43" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/waswater</v>
       </c>
       <c r="R43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/waswater</v>
+        <v>http://qudt.org/vocab/quantitykind/VolumeFlowRate</v>
       </c>
       <c r="S43" t="str">
-        <v>http://qudt.org/vocab/quantitykind/VolumeFlowRate</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0053</v>
       </c>
       <c r="T43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0053</v>
+        <v>null</v>
       </c>
       <c r="U43" t="str">
         <v>null</v>
@@ -4220,15 +4094,12 @@
         <v>null</v>
       </c>
       <c r="AB43" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC43" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebietvoorbevochtiging</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebietvoorbevochtiging</v>
       </c>
       <c r="B44" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -4240,7 +4111,7 @@
         <v>null</v>
       </c>
       <c r="E44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F44" t="str">
         <v>null</v>
@@ -4249,7 +4120,7 @@
         <v>Waswaterdebiet van de voorbevochtiging van de ingaande stallucht</v>
       </c>
       <c r="H44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I44" t="str">
         <v>null</v>
@@ -4264,7 +4135,7 @@
         <v>null</v>
       </c>
       <c r="M44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>null</v>
       </c>
       <c r="N44" t="str">
         <v>null</v>
@@ -4276,16 +4147,16 @@
         <v>null</v>
       </c>
       <c r="Q44" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/waswater</v>
       </c>
       <c r="R44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/waswater</v>
+        <v>http://qudt.org/vocab/quantitykind/VolumeFlowRate</v>
       </c>
       <c r="S44" t="str">
-        <v>http://qudt.org/vocab/quantitykind/VolumeFlowRate</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0053</v>
       </c>
       <c r="T44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0053</v>
+        <v>null</v>
       </c>
       <c r="U44" t="str">
         <v>null</v>
@@ -4309,15 +4180,12 @@
         <v>null</v>
       </c>
       <c r="AB44" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC44" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/zuurtegraadwaswater</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/zuurtegraadwaswater</v>
       </c>
       <c r="B45" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/ns/ssn/Property</v>
@@ -4329,7 +4197,7 @@
         <v>null</v>
       </c>
       <c r="E45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="F45" t="str">
         <v>null</v>
@@ -4338,7 +4206,7 @@
         <v>Zuurtegraad van het waswater</v>
       </c>
       <c r="H45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="I45" t="str">
         <v>null</v>
@@ -4353,7 +4221,7 @@
         <v>null</v>
       </c>
       <c r="M45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>null</v>
       </c>
       <c r="N45" t="str">
         <v>null</v>
@@ -4365,16 +4233,16 @@
         <v>null</v>
       </c>
       <c r="Q45" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/waswater</v>
       </c>
       <c r="R45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/waswater</v>
+        <v>http://qudt.org/vocab/quantitykind/Acidity</v>
       </c>
       <c r="S45" t="str">
-        <v>http://qudt.org/vocab/quantitykind/Acidity</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0076</v>
       </c>
       <c r="T45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/fysico-chemisch/0076</v>
+        <v>null</v>
       </c>
       <c r="U45" t="str">
         <v>null</v>
@@ -4398,15 +4266,12 @@
         <v>null</v>
       </c>
       <c r="AB45" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC45" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_1</v>
       </c>
       <c r="B46" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -4418,7 +4283,7 @@
         <v>null</v>
       </c>
       <c r="E46" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F46" t="str">
         <v>null</v>
@@ -4427,7 +4292,7 @@
         <v>Zuurtegraad waswater S1 systeem</v>
       </c>
       <c r="H46" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I46" t="str">
         <v>null</v>
@@ -4442,19 +4307,19 @@
         <v>null</v>
       </c>
       <c r="M46" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/zuurtegraadwaswater</v>
       </c>
       <c r="N46" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/zuurtegraadwaswater</v>
+        <v>8.5</v>
       </c>
       <c r="O46" t="str">
-        <v>8.5</v>
+        <v>null</v>
       </c>
       <c r="P46" t="str">
-        <v>null</v>
+        <v>6</v>
       </c>
       <c r="Q46" t="str">
-        <v>6</v>
+        <v>null</v>
       </c>
       <c r="R46" t="str">
         <v>null</v>
@@ -4466,13 +4331,13 @@
         <v>null</v>
       </c>
       <c r="U46" t="str">
-        <v>null</v>
+        <v>maximum</v>
       </c>
       <c r="V46" t="str">
-        <v>maximum</v>
+        <v>true</v>
       </c>
       <c r="W46" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X46" t="str">
         <v>null</v>
@@ -4487,15 +4352,12 @@
         <v>null</v>
       </c>
       <c r="AB46" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC46" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_10</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_10</v>
       </c>
       <c r="B47" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -4507,7 +4369,7 @@
         <v>null</v>
       </c>
       <c r="E47" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F47" t="str">
         <v>null</v>
@@ -4516,7 +4378,7 @@
         <v>Drukval S2 systeem</v>
       </c>
       <c r="H47" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I47" t="str">
         <v>null</v>
@@ -4531,19 +4393,19 @@
         <v>null</v>
       </c>
       <c r="M47" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/drukvaloverhetsysteem</v>
       </c>
       <c r="N47" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem</v>
+        <v>500</v>
       </c>
       <c r="O47" t="str">
-        <v>500</v>
+        <v>null</v>
       </c>
       <c r="P47" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R47" t="str">
         <v>null</v>
@@ -4555,13 +4417,13 @@
         <v>null</v>
       </c>
       <c r="U47" t="str">
-        <v>null</v>
+        <v>exact</v>
       </c>
       <c r="V47" t="str">
-        <v>exact</v>
+        <v>true</v>
       </c>
       <c r="W47" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X47" t="str">
         <v>null</v>
@@ -4576,15 +4438,12 @@
         <v>null</v>
       </c>
       <c r="AB47" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC47" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_11</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_11</v>
       </c>
       <c r="B48" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -4596,7 +4455,7 @@
         <v>null</v>
       </c>
       <c r="E48" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F48" t="str">
         <v>null</v>
@@ -4605,7 +4464,7 @@
         <v>Waswaterdebiet voorbevochtiging S3 systeem</v>
       </c>
       <c r="H48" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I48" t="str">
         <v>null</v>
@@ -4620,19 +4479,19 @@
         <v>null</v>
       </c>
       <c r="M48" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebietvoorbevochtiging</v>
       </c>
       <c r="N48" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebietvoorbevochtiging</v>
+        <v>null</v>
       </c>
       <c r="O48" t="str">
         <v>null</v>
       </c>
       <c r="P48" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R48" t="str">
         <v>null</v>
@@ -4644,13 +4503,13 @@
         <v>null</v>
       </c>
       <c r="U48" t="str">
-        <v>null</v>
+        <v>minimum</v>
       </c>
       <c r="V48" t="str">
-        <v>minimum</v>
+        <v>true</v>
       </c>
       <c r="W48" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X48" t="str">
         <v>null</v>
@@ -4665,15 +4524,12 @@
         <v>null</v>
       </c>
       <c r="AB48" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC48" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_12</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_12</v>
       </c>
       <c r="B49" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -4685,7 +4541,7 @@
         <v>null</v>
       </c>
       <c r="E49" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F49" t="str">
         <v>null</v>
@@ -4694,7 +4550,7 @@
         <v>Waswaterdebiet bevloeiing S3 systeem</v>
       </c>
       <c r="H49" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I49" t="str">
         <v>null</v>
@@ -4709,19 +4565,19 @@
         <v>null</v>
       </c>
       <c r="M49" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebietbevloeiing</v>
       </c>
       <c r="N49" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebietbevloeiing</v>
+        <v>null</v>
       </c>
       <c r="O49" t="str">
         <v>null</v>
       </c>
       <c r="P49" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R49" t="str">
         <v>null</v>
@@ -4733,13 +4589,13 @@
         <v>null</v>
       </c>
       <c r="U49" t="str">
-        <v>null</v>
+        <v>minimum</v>
       </c>
       <c r="V49" t="str">
-        <v>minimum</v>
+        <v>true</v>
       </c>
       <c r="W49" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X49" t="str">
         <v>null</v>
@@ -4754,15 +4610,12 @@
         <v>null</v>
       </c>
       <c r="AB49" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC49" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_13</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_13</v>
       </c>
       <c r="B50" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -4774,7 +4627,7 @@
         <v>null</v>
       </c>
       <c r="E50" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F50" t="str">
         <v>null</v>
@@ -4783,7 +4636,7 @@
         <v>Biobedspuiwaterproductie S3 systeem</v>
       </c>
       <c r="H50" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I50" t="str">
         <v>null</v>
@@ -4798,19 +4651,19 @@
         <v>null</v>
       </c>
       <c r="M50" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/biobedspuiwaterproductie</v>
       </c>
       <c r="N50" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/biobedspuiwaterproductie</v>
+        <v>null</v>
       </c>
       <c r="O50" t="str">
         <v>null</v>
       </c>
       <c r="P50" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R50" t="str">
         <v>null</v>
@@ -4822,13 +4675,13 @@
         <v>null</v>
       </c>
       <c r="U50" t="str">
-        <v>null</v>
+        <v>minimum</v>
       </c>
       <c r="V50" t="str">
-        <v>minimum</v>
+        <v>true</v>
       </c>
       <c r="W50" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X50" t="str">
         <v>null</v>
@@ -4843,15 +4696,12 @@
         <v>null</v>
       </c>
       <c r="AB50" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC50" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_14</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_14</v>
       </c>
       <c r="B51" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -4863,7 +4713,7 @@
         <v>null</v>
       </c>
       <c r="E51" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F51" t="str">
         <v>null</v>
@@ -4872,7 +4722,7 @@
         <v>Biobedspoelwaterproductie S3 systeem</v>
       </c>
       <c r="H51" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I51" t="str">
         <v>null</v>
@@ -4887,19 +4737,19 @@
         <v>null</v>
       </c>
       <c r="M51" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/biobedspoelwaterproductie</v>
       </c>
       <c r="N51" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/biobedspoelwaterproductie</v>
+        <v>null</v>
       </c>
       <c r="O51" t="str">
         <v>null</v>
       </c>
       <c r="P51" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R51" t="str">
         <v>null</v>
@@ -4911,13 +4761,13 @@
         <v>null</v>
       </c>
       <c r="U51" t="str">
-        <v>null</v>
+        <v>minimum</v>
       </c>
       <c r="V51" t="str">
-        <v>minimum</v>
+        <v>true</v>
       </c>
       <c r="W51" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X51" t="str">
         <v>null</v>
@@ -4932,15 +4782,12 @@
         <v>null</v>
       </c>
       <c r="AB51" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC51" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_15</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_15</v>
       </c>
       <c r="B52" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -4952,7 +4799,7 @@
         <v>null</v>
       </c>
       <c r="E52" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F52" t="str">
         <v>null</v>
@@ -4961,7 +4808,7 @@
         <v>Drukval S3 systeem</v>
       </c>
       <c r="H52" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I52" t="str">
         <v>null</v>
@@ -4976,19 +4823,19 @@
         <v>null</v>
       </c>
       <c r="M52" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/drukvaloverhetsysteem</v>
       </c>
       <c r="N52" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem</v>
+        <v>500</v>
       </c>
       <c r="O52" t="str">
-        <v>500</v>
+        <v>null</v>
       </c>
       <c r="P52" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R52" t="str">
         <v>null</v>
@@ -5000,13 +4847,13 @@
         <v>null</v>
       </c>
       <c r="U52" t="str">
-        <v>null</v>
+        <v>maximum</v>
       </c>
       <c r="V52" t="str">
-        <v>maximum</v>
+        <v>true</v>
       </c>
       <c r="W52" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X52" t="str">
         <v>null</v>
@@ -5021,15 +4868,12 @@
         <v>null</v>
       </c>
       <c r="AB52" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC52" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_16</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_16</v>
       </c>
       <c r="B53" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -5041,7 +4885,7 @@
         <v>null</v>
       </c>
       <c r="E53" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F53" t="str">
         <v>null</v>
@@ -5050,7 +4894,7 @@
         <v>Geleidbaarheid waswater Lely Sphere systeem</v>
       </c>
       <c r="H53" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I53" t="str">
         <v>null</v>
@@ -5065,19 +4909,19 @@
         <v>null</v>
       </c>
       <c r="M53" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/geleidbaarheidvanhetwaswater</v>
       </c>
       <c r="N53" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/geleidbaarheidvanhetwaswater</v>
+        <v>null</v>
       </c>
       <c r="O53" t="str">
         <v>null</v>
       </c>
       <c r="P53" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R53" t="str">
         <v>null</v>
@@ -5089,13 +4933,13 @@
         <v>null</v>
       </c>
       <c r="U53" t="str">
-        <v>null</v>
+        <v>maximum</v>
       </c>
       <c r="V53" t="str">
-        <v>maximum</v>
+        <v>true</v>
       </c>
       <c r="W53" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X53" t="str">
         <v>null</v>
@@ -5110,15 +4954,12 @@
         <v>null</v>
       </c>
       <c r="AB53" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC53" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_17</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_17</v>
       </c>
       <c r="B54" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -5130,7 +4971,7 @@
         <v>null</v>
       </c>
       <c r="E54" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F54" t="str">
         <v>null</v>
@@ -5139,7 +4980,7 @@
         <v>Waswaterdebiet Lely Sphere systeem</v>
       </c>
       <c r="H54" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I54" t="str">
         <v>null</v>
@@ -5154,19 +4995,19 @@
         <v>null</v>
       </c>
       <c r="M54" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebiet</v>
       </c>
       <c r="N54" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebiet</v>
+        <v>null</v>
       </c>
       <c r="O54" t="str">
         <v>null</v>
       </c>
       <c r="P54" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R54" t="str">
         <v>null</v>
@@ -5178,13 +5019,13 @@
         <v>null</v>
       </c>
       <c r="U54" t="str">
-        <v>null</v>
+        <v>minimum</v>
       </c>
       <c r="V54" t="str">
-        <v>minimum</v>
+        <v>true</v>
       </c>
       <c r="W54" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X54" t="str">
         <v>null</v>
@@ -5199,15 +5040,12 @@
         <v>null</v>
       </c>
       <c r="AB54" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC54" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_18</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_18</v>
       </c>
       <c r="B55" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -5219,7 +5057,7 @@
         <v>null</v>
       </c>
       <c r="E55" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F55" t="str">
         <v>null</v>
@@ -5228,7 +5066,7 @@
         <v>Spuiwaterdebiet Lely Sphere systeem</v>
       </c>
       <c r="H55" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I55" t="str">
         <v>null</v>
@@ -5243,19 +5081,19 @@
         <v>null</v>
       </c>
       <c r="M55" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/spuiwaterproductie</v>
       </c>
       <c r="N55" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/spuiwaterproductie</v>
+        <v>null</v>
       </c>
       <c r="O55" t="str">
         <v>null</v>
       </c>
       <c r="P55" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R55" t="str">
         <v>null</v>
@@ -5267,13 +5105,13 @@
         <v>null</v>
       </c>
       <c r="U55" t="str">
-        <v>null</v>
+        <v>minimum</v>
       </c>
       <c r="V55" t="str">
-        <v>minimum</v>
+        <v>true</v>
       </c>
       <c r="W55" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X55" t="str">
         <v>null</v>
@@ -5288,15 +5126,12 @@
         <v>null</v>
       </c>
       <c r="AB55" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC55" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_19</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_19</v>
       </c>
       <c r="B56" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -5308,7 +5143,7 @@
         <v>null</v>
       </c>
       <c r="E56" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F56" t="str">
         <v>null</v>
@@ -5317,7 +5152,7 @@
         <v>Elektriciteitsverbruik van de waswaterpomp(en) Lely Sphere systeem</v>
       </c>
       <c r="H56" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I56" t="str">
         <v>null</v>
@@ -5332,19 +5167,19 @@
         <v>null</v>
       </c>
       <c r="M56" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/elektriciteitsverbruikwaterpompen</v>
       </c>
       <c r="N56" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/elektriciteitsverbruikwaterpompen</v>
+        <v>null</v>
       </c>
       <c r="O56" t="str">
         <v>null</v>
       </c>
       <c r="P56" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R56" t="str">
         <v>null</v>
@@ -5356,13 +5191,13 @@
         <v>null</v>
       </c>
       <c r="U56" t="str">
-        <v>null</v>
+        <v>minimum</v>
       </c>
       <c r="V56" t="str">
-        <v>minimum</v>
+        <v>true</v>
       </c>
       <c r="W56" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X56" t="str">
         <v>null</v>
@@ -5377,15 +5212,12 @@
         <v>null</v>
       </c>
       <c r="AB56" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC56" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_2</v>
       </c>
       <c r="B57" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -5397,7 +5229,7 @@
         <v>null</v>
       </c>
       <c r="E57" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F57" t="str">
         <v>null</v>
@@ -5406,7 +5238,7 @@
         <v>Geleidbaarheid waswater S1 systeem</v>
       </c>
       <c r="H57" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I57" t="str">
         <v>null</v>
@@ -5421,19 +5253,19 @@
         <v>null</v>
       </c>
       <c r="M57" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/geleidbaarheidvanhetwaswater</v>
       </c>
       <c r="N57" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/geleidbaarheidvanhetwaswater</v>
+        <v>30</v>
       </c>
       <c r="O57" t="str">
-        <v>30</v>
+        <v>null</v>
       </c>
       <c r="P57" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R57" t="str">
         <v>null</v>
@@ -5445,13 +5277,13 @@
         <v>null</v>
       </c>
       <c r="U57" t="str">
-        <v>null</v>
+        <v>maximum</v>
       </c>
       <c r="V57" t="str">
-        <v>maximum</v>
+        <v>true</v>
       </c>
       <c r="W57" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X57" t="str">
         <v>null</v>
@@ -5466,15 +5298,12 @@
         <v>null</v>
       </c>
       <c r="AB57" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC57" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_3</v>
       </c>
       <c r="B58" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -5486,7 +5315,7 @@
         <v>null</v>
       </c>
       <c r="E58" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F58" t="str">
         <v>null</v>
@@ -5495,7 +5324,7 @@
         <v>Waswaterdebiet S1 systeem</v>
       </c>
       <c r="H58" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I58" t="str">
         <v>null</v>
@@ -5510,19 +5339,19 @@
         <v>null</v>
       </c>
       <c r="M58" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebiet</v>
       </c>
       <c r="N58" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebiet</v>
+        <v>null</v>
       </c>
       <c r="O58" t="str">
         <v>null</v>
       </c>
       <c r="P58" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R58" t="str">
         <v>null</v>
@@ -5534,13 +5363,13 @@
         <v>null</v>
       </c>
       <c r="U58" t="str">
-        <v>null</v>
+        <v>minimum</v>
       </c>
       <c r="V58" t="str">
-        <v>minimum</v>
+        <v>true</v>
       </c>
       <c r="W58" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X58" t="str">
         <v>null</v>
@@ -5555,15 +5384,12 @@
         <v>null</v>
       </c>
       <c r="AB58" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC58" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_4</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_4</v>
       </c>
       <c r="B59" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -5575,7 +5401,7 @@
         <v>null</v>
       </c>
       <c r="E59" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F59" t="str">
         <v>null</v>
@@ -5584,7 +5410,7 @@
         <v>Spuiwaterdebiet S1 systeem</v>
       </c>
       <c r="H59" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I59" t="str">
         <v>null</v>
@@ -5599,19 +5425,19 @@
         <v>null</v>
       </c>
       <c r="M59" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/spuiwaterproductie</v>
       </c>
       <c r="N59" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/spuiwaterproductie</v>
+        <v>null</v>
       </c>
       <c r="O59" t="str">
         <v>null</v>
       </c>
       <c r="P59" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R59" t="str">
         <v>null</v>
@@ -5623,13 +5449,13 @@
         <v>null</v>
       </c>
       <c r="U59" t="str">
-        <v>null</v>
+        <v>minimum</v>
       </c>
       <c r="V59" t="str">
-        <v>minimum</v>
+        <v>true</v>
       </c>
       <c r="W59" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X59" t="str">
         <v>null</v>
@@ -5644,15 +5470,12 @@
         <v>null</v>
       </c>
       <c r="AB59" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC59" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_5</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_5</v>
       </c>
       <c r="B60" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -5664,7 +5487,7 @@
         <v>null</v>
       </c>
       <c r="E60" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F60" t="str">
         <v>null</v>
@@ -5673,7 +5496,7 @@
         <v>Drukval S1 systeem</v>
       </c>
       <c r="H60" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I60" t="str">
         <v>null</v>
@@ -5688,19 +5511,19 @@
         <v>null</v>
       </c>
       <c r="M60" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/drukvaloverhetsysteem</v>
       </c>
       <c r="N60" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem</v>
+        <v>500</v>
       </c>
       <c r="O60" t="str">
-        <v>500</v>
+        <v>null</v>
       </c>
       <c r="P60" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R60" t="str">
         <v>null</v>
@@ -5712,13 +5535,13 @@
         <v>null</v>
       </c>
       <c r="U60" t="str">
-        <v>null</v>
+        <v>exact</v>
       </c>
       <c r="V60" t="str">
-        <v>exact</v>
+        <v>true</v>
       </c>
       <c r="W60" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X60" t="str">
         <v>null</v>
@@ -5733,15 +5556,12 @@
         <v>null</v>
       </c>
       <c r="AB60" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC60" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_6</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_6</v>
       </c>
       <c r="B61" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -5753,7 +5573,7 @@
         <v>null</v>
       </c>
       <c r="E61" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F61" t="str">
         <v>null</v>
@@ -5762,7 +5582,7 @@
         <v>Zuurtegraad waswater S2 systeem</v>
       </c>
       <c r="H61" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I61" t="str">
         <v>null</v>
@@ -5777,19 +5597,19 @@
         <v>null</v>
       </c>
       <c r="M61" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/zuurtegraadwaswater</v>
       </c>
       <c r="N61" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/zuurtegraadwaswater</v>
+        <v>14</v>
       </c>
       <c r="O61" t="str">
-        <v>14</v>
+        <v>null</v>
       </c>
       <c r="P61" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R61" t="str">
         <v>null</v>
@@ -5801,13 +5621,13 @@
         <v>null</v>
       </c>
       <c r="U61" t="str">
-        <v>null</v>
+        <v>maximum</v>
       </c>
       <c r="V61" t="str">
-        <v>maximum</v>
+        <v>true</v>
       </c>
       <c r="W61" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X61" t="str">
         <v>null</v>
@@ -5822,15 +5642,12 @@
         <v>null</v>
       </c>
       <c r="AB61" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC61" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_7</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_7</v>
       </c>
       <c r="B62" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -5842,7 +5659,7 @@
         <v>null</v>
       </c>
       <c r="E62" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F62" t="str">
         <v>null</v>
@@ -5851,7 +5668,7 @@
         <v>Geleidbaarheid waswater S2 systeem</v>
       </c>
       <c r="H62" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I62" t="str">
         <v>null</v>
@@ -5866,19 +5683,19 @@
         <v>null</v>
       </c>
       <c r="M62" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/geleidbaarheidvanhetwaswater</v>
       </c>
       <c r="N62" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/geleidbaarheidvanhetwaswater</v>
+        <v>500</v>
       </c>
       <c r="O62" t="str">
-        <v>500</v>
+        <v>null</v>
       </c>
       <c r="P62" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R62" t="str">
         <v>null</v>
@@ -5890,13 +5707,13 @@
         <v>null</v>
       </c>
       <c r="U62" t="str">
-        <v>null</v>
+        <v>maximum</v>
       </c>
       <c r="V62" t="str">
-        <v>maximum</v>
+        <v>true</v>
       </c>
       <c r="W62" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X62" t="str">
         <v>null</v>
@@ -5911,15 +5728,12 @@
         <v>null</v>
       </c>
       <c r="AB62" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC62" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_8</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_8</v>
       </c>
       <c r="B63" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -5931,7 +5745,7 @@
         <v>null</v>
       </c>
       <c r="E63" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F63" t="str">
         <v>null</v>
@@ -5940,7 +5754,7 @@
         <v>Waswaterdebiet S2 systeem</v>
       </c>
       <c r="H63" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I63" t="str">
         <v>null</v>
@@ -5955,19 +5769,19 @@
         <v>null</v>
       </c>
       <c r="M63" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebiet</v>
       </c>
       <c r="N63" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebiet</v>
+        <v>null</v>
       </c>
       <c r="O63" t="str">
         <v>null</v>
       </c>
       <c r="P63" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R63" t="str">
         <v>null</v>
@@ -5979,13 +5793,13 @@
         <v>null</v>
       </c>
       <c r="U63" t="str">
-        <v>null</v>
+        <v>minimum</v>
       </c>
       <c r="V63" t="str">
-        <v>minimum</v>
+        <v>true</v>
       </c>
       <c r="W63" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X63" t="str">
         <v>null</v>
@@ -6000,15 +5814,12 @@
         <v>null</v>
       </c>
       <c r="AB63" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC63" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_9</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_9</v>
       </c>
       <c r="B64" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6020,7 +5831,7 @@
         <v>null</v>
       </c>
       <c r="E64" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="F64" t="str">
         <v>null</v>
@@ -6029,7 +5840,7 @@
         <v>Spuiwaterdebiet S2 systeem</v>
       </c>
       <c r="H64" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="I64" t="str">
         <v>null</v>
@@ -6044,19 +5855,19 @@
         <v>null</v>
       </c>
       <c r="M64" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/spuiwaterproductie</v>
       </c>
       <c r="N64" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/spuiwaterproductie</v>
+        <v>null</v>
       </c>
       <c r="O64" t="str">
         <v>null</v>
       </c>
       <c r="P64" t="str">
-        <v>null</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="R64" t="str">
         <v>null</v>
@@ -6068,13 +5879,13 @@
         <v>null</v>
       </c>
       <c r="U64" t="str">
-        <v>null</v>
+        <v>minimum</v>
       </c>
       <c r="V64" t="str">
-        <v>minimum</v>
+        <v>true</v>
       </c>
       <c r="W64" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="X64" t="str">
         <v>null</v>
@@ -6089,15 +5900,12 @@
         <v>null</v>
       </c>
       <c r="AB64" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC64" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/stalbezetting/in_gebruik</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/stalbezetting/in_gebruik</v>
       </c>
       <c r="B65" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6109,7 +5917,7 @@
         <v>null</v>
       </c>
       <c r="E65" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/stalbezetting</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/stalbezetting</v>
       </c>
       <c r="F65" t="str">
         <v>null</v>
@@ -6118,7 +5926,7 @@
         <v>Stal in gebruik, dieren aanwezig.</v>
       </c>
       <c r="H65" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/stalbezetting</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/stalbezetting</v>
       </c>
       <c r="I65" t="str">
         <v>null</v>
@@ -6178,15 +5986,12 @@
         <v>null</v>
       </c>
       <c r="AB65" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC65" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/stalbezetting/leeg</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/stalbezetting/leeg</v>
       </c>
       <c r="B66" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6198,7 +6003,7 @@
         <v>null</v>
       </c>
       <c r="E66" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/stalbezetting</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/stalbezetting</v>
       </c>
       <c r="F66" t="str">
         <v>null</v>
@@ -6207,7 +6012,7 @@
         <v>Lege stal</v>
       </c>
       <c r="H66" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/stalbezetting</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/stalbezetting</v>
       </c>
       <c r="I66" t="str">
         <v>null</v>
@@ -6267,15 +6072,12 @@
         <v>null</v>
       </c>
       <c r="AB66" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC66" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/status/gereinigd</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status/gereinigd</v>
       </c>
       <c r="B67" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6287,7 +6089,7 @@
         <v>null</v>
       </c>
       <c r="E67" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemstatus</v>
       </c>
       <c r="F67" t="str">
         <v>null</v>
@@ -6296,7 +6098,7 @@
         <v>Gereinigd</v>
       </c>
       <c r="H67" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemstatus</v>
       </c>
       <c r="I67" t="str">
         <v>null</v>
@@ -6356,15 +6158,12 @@
         <v>null</v>
       </c>
       <c r="AB67" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC67" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/status/onderhoud</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status/onderhoud</v>
       </c>
       <c r="B68" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6376,7 +6175,7 @@
         <v>null</v>
       </c>
       <c r="E68" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemstatus</v>
       </c>
       <c r="F68" t="str">
         <v>null</v>
@@ -6385,7 +6184,7 @@
         <v>In onderhoud</v>
       </c>
       <c r="H68" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemstatus</v>
       </c>
       <c r="I68" t="str">
         <v>null</v>
@@ -6445,15 +6244,12 @@
         <v>null</v>
       </c>
       <c r="AB68" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC68" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/status/operationeel</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status/operationeel</v>
       </c>
       <c r="B69" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6465,7 +6261,7 @@
         <v>null</v>
       </c>
       <c r="E69" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemstatus</v>
       </c>
       <c r="F69" t="str">
         <v>null</v>
@@ -6474,7 +6270,7 @@
         <v>Operationeel</v>
       </c>
       <c r="H69" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemstatus</v>
       </c>
       <c r="I69" t="str">
         <v>null</v>
@@ -6534,15 +6330,12 @@
         <v>null</v>
       </c>
       <c r="AB69" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC69" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/status/storing</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status/storing</v>
       </c>
       <c r="B70" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6554,7 +6347,7 @@
         <v>null</v>
       </c>
       <c r="E70" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemstatus</v>
       </c>
       <c r="F70" t="str">
         <v>null</v>
@@ -6563,7 +6356,7 @@
         <v>Storing</v>
       </c>
       <c r="H70" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemstatus</v>
       </c>
       <c r="I70" t="str">
         <v>null</v>
@@ -6623,15 +6416,12 @@
         <v>null</v>
       </c>
       <c r="AB70" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC70" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/systeemopstelling/enkelvoudig</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/systeemopstelling/enkelvoudig</v>
       </c>
       <c r="B71" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6643,7 +6433,7 @@
         <v>null</v>
       </c>
       <c r="E71" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemopstelling</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemopstelling</v>
       </c>
       <c r="F71" t="str">
         <v>null</v>
@@ -6652,7 +6442,7 @@
         <v>Enkelvoudige opstelling</v>
       </c>
       <c r="H71" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemopstelling</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemopstelling</v>
       </c>
       <c r="I71" t="str">
         <v>null</v>
@@ -6712,15 +6502,12 @@
         <v>null</v>
       </c>
       <c r="AB71" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC71" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/systeemopstelling/gecombineerd</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/systeemopstelling/gecombineerd</v>
       </c>
       <c r="B72" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6732,7 +6519,7 @@
         <v>null</v>
       </c>
       <c r="E72" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemopstelling</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemopstelling</v>
       </c>
       <c r="F72" t="str">
         <v>null</v>
@@ -6741,7 +6528,7 @@
         <v>Gecombineerde opstelling</v>
       </c>
       <c r="H72" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemopstelling</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemopstelling</v>
       </c>
       <c r="I72" t="str">
         <v>null</v>
@@ -6801,15 +6588,12 @@
         <v>null</v>
       </c>
       <c r="AB72" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC72" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/lelysphere</v>
       </c>
       <c r="B73" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6821,7 +6605,7 @@
         <v>null</v>
       </c>
       <c r="E73" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemtype</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemtype</v>
       </c>
       <c r="F73" t="str">
         <v>Lelysphere</v>
@@ -6848,7 +6632,7 @@
         <v>null</v>
       </c>
       <c r="N73" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebiet|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/spuiwaterproductie|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/geleidbaarheidvanhetwaswater|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/elektriciteitsverbruikwaterpompen</v>
+        <v>null</v>
       </c>
       <c r="O73" t="str">
         <v>null</v>
@@ -6875,30 +6659,27 @@
         <v>null</v>
       </c>
       <c r="W73" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem</v>
       </c>
       <c r="X73" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="Y73" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="Z73" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>null</v>
       </c>
       <c r="AA73" t="str">
         <v>null</v>
       </c>
       <c r="AB73" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC73" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem</v>
       </c>
       <c r="B74" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6910,7 +6691,7 @@
         <v>null</v>
       </c>
       <c r="E74" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemtype</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemtype</v>
       </c>
       <c r="F74" t="str">
         <v>null</v>
@@ -6964,30 +6745,27 @@
         <v>null</v>
       </c>
       <c r="W74" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="X74" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="Y74" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/lelysphere|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s1|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s2</v>
       </c>
       <c r="Z74" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/lelysphere|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s1|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s2</v>
       </c>
       <c r="AA74" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/lelysphere|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s1|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s2</v>
       </c>
       <c r="AB74" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere</v>
-      </c>
-      <c r="AC74" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="B75" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -6999,7 +6777,7 @@
         <v>null</v>
       </c>
       <c r="E75" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemtype</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemtype</v>
       </c>
       <c r="F75" t="str">
         <v>null</v>
@@ -7008,7 +6786,7 @@
         <v>Luchtzuiveringssysteem</v>
       </c>
       <c r="H75" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemtype</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemtype</v>
       </c>
       <c r="I75" t="str">
         <v>null</v>
@@ -7059,24 +6837,21 @@
         <v>null</v>
       </c>
       <c r="Y75" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/lelysphere|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s1|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s2|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s3</v>
       </c>
       <c r="Z75" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s3</v>
       </c>
       <c r="AA75" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/lelysphere|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s1|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s2|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s3</v>
       </c>
       <c r="AB75" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/lelysphere|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem</v>
-      </c>
-      <c r="AC75" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s1</v>
       </c>
       <c r="B76" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -7088,7 +6863,7 @@
         <v>null</v>
       </c>
       <c r="E76" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemtype</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemtype</v>
       </c>
       <c r="F76" t="str">
         <v>S1</v>
@@ -7115,7 +6890,7 @@
         <v>null</v>
       </c>
       <c r="N76" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebiet|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/spuiwaterproductie|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/zuurtegraadwaswater|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/geleidbaarheidvanhetwaswater|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/stalbezetting|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/systeemstatus</v>
+        <v>null</v>
       </c>
       <c r="O76" t="str">
         <v>null</v>
@@ -7142,30 +6917,27 @@
         <v>null</v>
       </c>
       <c r="W76" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem</v>
       </c>
       <c r="X76" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="Y76" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="Z76" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>null</v>
       </c>
       <c r="AA76" t="str">
         <v>null</v>
       </c>
       <c r="AB76" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC76" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s2</v>
       </c>
       <c r="B77" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -7177,7 +6949,7 @@
         <v>null</v>
       </c>
       <c r="E77" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemtype</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemtype</v>
       </c>
       <c r="F77" t="str">
         <v>S2</v>
@@ -7204,7 +6976,7 @@
         <v>null</v>
       </c>
       <c r="N77" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebiet|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/spuiwaterproductie|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/zuurtegraadwaswater|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/geleidbaarheidvanhetwaswater|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/stalbezetting|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/systeemstatus</v>
+        <v>null</v>
       </c>
       <c r="O77" t="str">
         <v>null</v>
@@ -7231,30 +7003,27 @@
         <v>null</v>
       </c>
       <c r="W77" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem</v>
       </c>
       <c r="X77" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="Y77" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="Z77" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtwassysteem|https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>null</v>
       </c>
       <c r="AA77" t="str">
         <v>null</v>
       </c>
       <c r="AB77" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC77" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/s3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/s3</v>
       </c>
       <c r="B78" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -7266,7 +7035,7 @@
         <v>null</v>
       </c>
       <c r="E78" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemtype</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemtype</v>
       </c>
       <c r="F78" t="str">
         <v>S3</v>
@@ -7293,7 +7062,7 @@
         <v>null</v>
       </c>
       <c r="N78" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebietvoorbevochtiging|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebietbevloeiing|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/biobedspoelwaterproductie|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/biobedspuiwaterproductie|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/stalbezetting|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/systeemstatus</v>
+        <v>null</v>
       </c>
       <c r="O78" t="str">
         <v>null</v>
@@ -7320,24 +7089,21 @@
         <v>null</v>
       </c>
       <c r="W78" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="X78" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="Y78" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
       <c r="Z78" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>null</v>
       </c>
       <c r="AA78" t="str">
         <v>null</v>
       </c>
       <c r="AB78" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC78" t="str">
         <v>null</v>
       </c>
     </row>
@@ -7426,9 +7192,6 @@
       <c r="AB79" t="str">
         <v>null</v>
       </c>
-      <c r="AC79" t="str">
-        <v>null</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -7515,9 +7278,6 @@
       <c r="AB80" t="str">
         <v>null</v>
       </c>
-      <c r="AC80" t="str">
-        <v>null</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -7604,13 +7364,10 @@
       <c r="AB81" t="str">
         <v>null</v>
       </c>
-      <c r="AC81" t="str">
-        <v>null</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/dataleverancierstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/dataleverancierstatus</v>
       </c>
       <c r="B82" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -7691,15 +7448,12 @@
         <v>null</v>
       </c>
       <c r="AB82" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC82" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/dataleverancierstatus/gevalideerd|https://data.omgeving.vlaanderen.be/id/concept/lzs/dataleverancierstatus/geweigerd|https://data.omgeving.vlaanderen.be/id/concept/lzs/dataleverancierstatus/ingetrokken|https://data.omgeving.vlaanderen.be/id/concept/lzs/dataleverancierstatus/nietgevalideerd</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/dataleverancierstatus/gevalideerd|https://data.omgeving.vlaanderen.be/id/concept/riepr/dataleverancierstatus/geweigerd|https://data.omgeving.vlaanderen.be/id/concept/riepr/dataleverancierstatus/ingetrokken|https://data.omgeving.vlaanderen.be/id/concept/riepr/dataleverancierstatus/nietgevalideerd</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/medium</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/medium</v>
       </c>
       <c r="B83" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -7780,15 +7534,12 @@
         <v>null</v>
       </c>
       <c r="AB83" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC83" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/hetelektronischmonitoringssysteem|https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/lucht|https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/spuiwater|https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/stal|https://data.omgeving.vlaanderen.be/id/concept/lzs/medium/waswater</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/hetelektronischmonitoringssysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/lucht|https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/spuiwater|https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/stal|https://data.omgeving.vlaanderen.be/id/concept/riepr/medium/waswater</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/norm-bandbreedte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/norm-bandbreedte</v>
       </c>
       <c r="B84" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -7869,15 +7620,12 @@
         <v>null</v>
       </c>
       <c r="AB84" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC84" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_10|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_11|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_12|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_13|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_14|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_15|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_16|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_1|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_2|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_3|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_4|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_5|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_6|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_7|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_8|https://data.omgeving.vlaanderen.be/id/concept/lzs/norm_bandbreedte/_9</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_10|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_11|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_12|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_13|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_14|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_15|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_16|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_1|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_2|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_3|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_4|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_5|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_6|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_7|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_8|https://data.omgeving.vlaanderen.be/id/concept/riepr/norm_bandbreedte/_9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter</v>
       </c>
       <c r="B85" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -7958,15 +7706,12 @@
         <v>null</v>
       </c>
       <c r="AB85" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC85" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebiet|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/spuiwaterproductie|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/drukvaloverhetsysteem|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebietvoorbevochtiging|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/waswaterdebietbevloeiing|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/zuurtegraadwaswater|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/geleidbaarheidvanhetwaswater|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/biobedspoelwaterproductie|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/biobedspuiwaterproductie|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/elektriciteitsverbruikwaterpompen|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/stalbezetting|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter/systeemstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebiet|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/spuiwaterproductie|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/drukvaloverhetsysteem|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebietvoorbevochtiging|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/waswaterdebietbevloeiing|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/zuurtegraadwaswater|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/geleidbaarheidvanhetwaswater|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/biobedspoelwaterproductie|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/biobedspuiwaterproductie|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/elektriciteitsverbruikwaterpompen|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/stalbezetting|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter/systeemstatus</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/parameter-norm</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/parameter-norm</v>
       </c>
       <c r="B86" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -8047,15 +7792,12 @@
         <v>null</v>
       </c>
       <c r="AB86" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC86" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_10|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_11|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_12|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_13|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_14|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_15|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_16|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_17|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_18|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_19|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_1|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_2|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_3|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_4|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_5|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_6|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_7|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_8|https://data.omgeving.vlaanderen.be/id/concept/lzs/parameter_norm/_9</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_10|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_11|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_12|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_13|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_14|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_15|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_16|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_17|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_18|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_19|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_1|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_2|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_3|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_4|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_5|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_6|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_7|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_8|https://data.omgeving.vlaanderen.be/id/concept/riepr/parameter_norm/_9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/stalbezetting</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/stalbezetting</v>
       </c>
       <c r="B87" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -8136,15 +7878,12 @@
         <v>null</v>
       </c>
       <c r="AB87" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC87" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/stalbezetting/in_gebruik|https://data.omgeving.vlaanderen.be/id/concept/lzs/stalbezetting/leeg</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/stalbezetting/in_gebruik|https://data.omgeving.vlaanderen.be/id/concept/riepr/stalbezetting/leeg</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemopstelling</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemopstelling</v>
       </c>
       <c r="B88" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -8225,15 +7964,12 @@
         <v>null</v>
       </c>
       <c r="AB88" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC88" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/systeemopstelling/enkelvoudig|https://data.omgeving.vlaanderen.be/id/concept/lzs/systeemopstelling/gecombineerd</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/systeemopstelling/enkelvoudig|https://data.omgeving.vlaanderen.be/id/concept/riepr/systeemopstelling/gecombineerd</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemstatus</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemstatus</v>
       </c>
       <c r="B89" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -8314,15 +8050,12 @@
         <v>null</v>
       </c>
       <c r="AB89" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC89" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/status/gereinigd|https://data.omgeving.vlaanderen.be/id/concept/lzs/status/onderhoud|https://data.omgeving.vlaanderen.be/id/concept/lzs/status/operationeel|https://data.omgeving.vlaanderen.be/id/concept/lzs/status/storing</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status/gereinigd|https://data.omgeving.vlaanderen.be/id/concept/riepr/status/onderhoud|https://data.omgeving.vlaanderen.be/id/concept/riepr/status/operationeel|https://data.omgeving.vlaanderen.be/id/concept/riepr/status/storing</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/lzs/systeemtype</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeemtype</v>
       </c>
       <c r="B90" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -8403,10 +8136,7 @@
         <v>null</v>
       </c>
       <c r="AB90" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC90" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/lzs/type/luchtzuiveringssysteem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/type/luchtzuiveringssysteem</v>
       </c>
     </row>
     <row r="91">
@@ -8492,15 +8222,12 @@
         <v>null</v>
       </c>
       <c r="AB91" t="str">
-        <v>null</v>
-      </c>
-      <c r="AC91" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k1|https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k2|https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB91"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -407,60 +407,60 @@
         <v>_type</v>
       </c>
       <c r="C1" t="str">
+        <v>inScheme</v>
+      </c>
+      <c r="D1" t="str">
+        <v>code</v>
+      </c>
+      <c r="E1" t="str">
+        <v>prefLabel</v>
+      </c>
+      <c r="F1" t="str">
+        <v>topConceptOf</v>
+      </c>
+      <c r="G1" t="str">
+        <v>relevantriepr</v>
+      </c>
+      <c r="H1" t="str">
+        <v>definition</v>
+      </c>
+      <c r="I1" t="str">
+        <v>note</v>
+      </c>
+      <c r="J1" t="str">
+        <v>subject</v>
+      </c>
+      <c r="K1" t="str">
         <v>altLabel</v>
       </c>
-      <c r="D1" t="str">
-        <v>definition</v>
-      </c>
-      <c r="E1" t="str">
-        <v>inScheme</v>
-      </c>
-      <c r="F1" t="str">
-        <v>note</v>
-      </c>
-      <c r="G1" t="str">
-        <v>prefLabel</v>
-      </c>
-      <c r="H1" t="str">
-        <v>topConceptOf</v>
-      </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>hasTopConcept</v>
-      </c>
-      <c r="J1" t="str">
-        <v>code</v>
-      </c>
-      <c r="K1" t="str">
-        <v>subject</v>
-      </c>
-      <c r="L1" t="str">
-        <v>relevantCodeList</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-attribuut/schouw-diameter</v>
       </c>
       <c r="B2" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C2" t="str">
-        <v>VLAREM klasse 1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
       </c>
       <c r="D2" t="str">
-        <v>Indelingsklasse voor inrichtingen met de grootste milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 1 (zwaarste procedure).</v>
+        <v>diameter</v>
       </c>
       <c r="E2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>Diameter van de schouw</v>
       </c>
       <c r="F2" t="str">
-        <v>Indelingsklasse voor inrichtingen met de grootste milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 1 (zwaarste procedure).</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
       </c>
       <c r="G2" t="str">
-        <v>Klasse 1</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="H2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>null</v>
       </c>
       <c r="I2" t="str">
         <v>null</v>
@@ -477,28 +477,28 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-attribuut/schouw-hoogte</v>
       </c>
       <c r="B3" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C3" t="str">
-        <v>VLAREM klasse 2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
       </c>
       <c r="D3" t="str">
-        <v>Indelingsklasse voor inrichtingen met een middelgrote milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 2.</v>
+        <v>hoogte</v>
       </c>
       <c r="E3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>Hoogte van de schouw</v>
       </c>
       <c r="F3" t="str">
-        <v>Indelingsklasse voor inrichtingen met een middelgrote milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 2.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
       </c>
       <c r="G3" t="str">
-        <v>Klasse 2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="H3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>null</v>
       </c>
       <c r="I3" t="str">
         <v>null</v>
@@ -515,28 +515,28 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
       </c>
       <c r="B4" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C4" t="str">
-        <v>VLAREM klasse 3</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D4" t="str">
-        <v>Indelingsklasse voor inrichtingen met een beperkte milieu-impact. Voor deze activiteiten geldt een meldingsplicht (klasse 3).</v>
+        <v>emissiepunt</v>
       </c>
       <c r="E4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>Emissiepunt</v>
       </c>
       <c r="F4" t="str">
-        <v>Indelingsklasse voor inrichtingen met een beperkte milieu-impact. Voor deze activiteiten geldt een meldingsplicht (klasse 3).</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G4" t="str">
-        <v>Klasse 3</v>
+        <v>null</v>
       </c>
       <c r="H4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>null</v>
       </c>
       <c r="I4" t="str">
         <v>null</v>
@@ -553,31 +553,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/fakkel</v>
       </c>
       <c r="B5" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C5" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D5" t="str">
-        <v>Een lijst die een koppeling maakt tussen soorten emissiepunten en de attributen die van toepassing zijn.</v>
+        <v>fakkel</v>
       </c>
       <c r="E5" t="str">
-        <v>null</v>
+        <v>Fakkel</v>
       </c>
       <c r="F5" t="str">
-        <v>Een lijst die een koppeling maakt tussen soorten emissiepunten en de attributen die van toepassing zijn.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G5" t="str">
-        <v>Emissiepunt attributen</v>
+        <v>null</v>
       </c>
       <c r="H5" t="str">
         <v>null</v>
       </c>
       <c r="I5" t="str">
-        <v>riepr-emissiepunt-attr:schouw-diameter|riepr-emissiepunt-attr:schouw-hoogte</v>
+        <v>null</v>
       </c>
       <c r="J5" t="str">
         <v>null</v>
@@ -591,31 +591,31 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
+      </c>
+      <c r="B6" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C6" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
-      <c r="B6" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C6" t="str">
-        <v>null</v>
-      </c>
       <c r="D6" t="str">
-        <v>Een lijst van verschillende soorten emissiepunten met mogelijke opsplitsing in subtyperingen.</v>
+        <v>lozingspunt</v>
       </c>
       <c r="E6" t="str">
-        <v>null</v>
+        <v>Lozingspunt</v>
       </c>
       <c r="F6" t="str">
-        <v>Een lijst van verschillende soorten emissiepunten met mogelijke opsplitsing in subtyperingen.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G6" t="str">
-        <v>Emissiepunt types</v>
+        <v>null</v>
       </c>
       <c r="H6" t="str">
         <v>null</v>
       </c>
       <c r="I6" t="str">
-        <v>riepr-emissiepunt-type:emissiepunt|riepr-emissiepunt-type:fakkel|riepr-emissiepunt-type:lozingspunt|riepr-emissiepunt-type:schouw</v>
+        <v>null</v>
       </c>
       <c r="J6" t="str">
         <v>null</v>
@@ -629,31 +629,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="B7" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C7" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D7" t="str">
-        <v>Een lijst van verschillende types van filters en de objecten waarop van toepassing.</v>
+        <v>schouw</v>
       </c>
       <c r="E7" t="str">
-        <v>null</v>
+        <v>Schouw</v>
       </c>
       <c r="F7" t="str">
-        <v>Een lijst van verschillende types van filters en de objecten waarop van toepassing.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G7" t="str">
-        <v>Filter types</v>
+        <v>null</v>
       </c>
       <c r="H7" t="str">
         <v>null</v>
       </c>
       <c r="I7" t="str">
-        <v>riepr-filter-type:peilfilter</v>
+        <v>null</v>
       </c>
       <c r="J7" t="str">
         <v>null</v>
@@ -667,31 +667,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peilfilter</v>
       </c>
       <c r="B8" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C8" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
       </c>
       <c r="D8" t="str">
-        <v>Een lijst van verschillende types van installaties met eventueel subtyperingen.</v>
+        <v>peilfilter</v>
       </c>
       <c r="E8" t="str">
-        <v>null</v>
+        <v>Peilfilter</v>
       </c>
       <c r="F8" t="str">
-        <v>Een lijst van verschillende types van installaties met eventueel subtyperingen.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
       </c>
       <c r="G8" t="str">
-        <v>Installatie types</v>
+        <v>null</v>
       </c>
       <c r="H8" t="str">
-        <v>null</v>
+        <v>Filter voor het meten van het grondwaterpeil.</v>
       </c>
       <c r="I8" t="str">
-        <v>riepr-installatie-type:gpbv|riepr-installatie-type:iepr|riepr-installatie-type:oven|riepr-installatie-type:zuiveringsinstallatie</v>
+        <v>Filter voor het meten van het grondwaterpeil.</v>
       </c>
       <c r="J8" t="str">
         <v>null</v>
@@ -705,31 +705,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetinstrument_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/gpbv</v>
       </c>
       <c r="B9" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C9" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D9" t="str">
-        <v>Een lijst van verschillende soorten meetinstrumenten.</v>
+        <v>GPBV</v>
       </c>
       <c r="E9" t="str">
-        <v>null</v>
+        <v>GPBV installatie</v>
       </c>
       <c r="F9" t="str">
-        <v>Een lijst van verschillende soorten meetinstrumenten.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G9" t="str">
-        <v>Meetinstrument types</v>
+        <v>null</v>
       </c>
       <c r="H9" t="str">
-        <v>null</v>
+        <v>Installatie die valt onder de richtlijn industriële emissies (IED/GPBV).</v>
       </c>
       <c r="I9" t="str">
-        <v>riepr-meetinstrument-type:debietmeter</v>
+        <v>Installatie die valt onder de richtlijn industriële emissies (IED/GPBV).</v>
       </c>
       <c r="J9" t="str">
         <v>null</v>
@@ -743,31 +743,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/iepr</v>
       </c>
       <c r="B10" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C10" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D10" t="str">
-        <v>Een lijst van verschillende soorten meetpunten.</v>
+        <v>IEPR</v>
       </c>
       <c r="E10" t="str">
-        <v>null</v>
+        <v>IEPR installatie</v>
       </c>
       <c r="F10" t="str">
-        <v>Een lijst van verschillende soorten meetpunten.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G10" t="str">
-        <v>Meetpunt types</v>
+        <v>null</v>
       </c>
       <c r="H10" t="str">
-        <v>null</v>
+        <v>Installatie in het kader van IEPR rapportering.</v>
       </c>
       <c r="I10" t="str">
-        <v>riepr-meetpunt-type:controle-inrichting|riepr-meetpunt-type:meetput</v>
+        <v>Installatie in het kader van IEPR rapportering.</v>
       </c>
       <c r="J10" t="str">
         <v>null</v>
@@ -781,31 +781,31 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/oven</v>
       </c>
       <c r="B11" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C11" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D11" t="str">
-        <v>Een lijst van verschillende soorten onttrekkingspunten met mogelijke opsplitsing in subtyperingen.</v>
+        <v>oven</v>
       </c>
       <c r="E11" t="str">
-        <v>null</v>
+        <v>Oven</v>
       </c>
       <c r="F11" t="str">
-        <v>Een lijst van verschillende soorten onttrekkingspunten met mogelijke opsplitsing in subtyperingen.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G11" t="str">
-        <v>Onttrekkingspunt types</v>
+        <v>null</v>
       </c>
       <c r="H11" t="str">
         <v>null</v>
       </c>
       <c r="I11" t="str">
-        <v>riepr-onttrekkingspunt-type:grondwaterput</v>
+        <v>null</v>
       </c>
       <c r="J11" t="str">
         <v>null</v>
@@ -819,31 +819,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/zuiveringsinstallatie</v>
       </c>
       <c r="B12" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C12" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D12" t="str">
-        <v>Een lijst van verschillende hoofdtyperingen van procedures in een procesplan.</v>
+        <v>zuiveringsinstallatie</v>
       </c>
       <c r="E12" t="str">
-        <v>null</v>
+        <v>Zuiveringsinstallatie</v>
       </c>
       <c r="F12" t="str">
-        <v>Een lijst van verschillende hoofdtyperingen van procedures in een procesplan.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G12" t="str">
-        <v>Procedure types</v>
+        <v>null</v>
       </c>
       <c r="H12" t="str">
         <v>null</v>
       </c>
       <c r="I12" t="str">
-        <v>riepr-procedure-type:emissie|riepr-procedure-type:meet|riepr-procedure-type:overbrenging|riepr-procedure-type:verbruik|riepr-procedure-type:verwerking</v>
+        <v>null</v>
       </c>
       <c r="J12" t="str">
         <v>null</v>
@@ -857,31 +857,31 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetinstrument-type/debietmeter</v>
       </c>
       <c r="B13" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C13" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetinstrument_type</v>
       </c>
       <c r="D13" t="str">
-        <v>Een lijst die verschillende types geeft voor stoffen die aangeduid mogen worden bij bepaalde procedure types.</v>
+        <v>debietmeter</v>
       </c>
       <c r="E13" t="str">
-        <v>null</v>
+        <v>Debietmeter</v>
       </c>
       <c r="F13" t="str">
-        <v>Een lijst die verschillende types geeft voor stoffen die aangeduid mogen worden bij bepaalde procedure types.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetinstrument_type</v>
       </c>
       <c r="G13" t="str">
-        <v>Proces variabele types</v>
+        <v>null</v>
       </c>
       <c r="H13" t="str">
         <v>null</v>
       </c>
       <c r="I13" t="str">
-        <v>riepr-procesvariabele-type:aardgas|riepr-procesvariabele-type:co2|riepr-procesvariabele-type:grondstof</v>
+        <v>null</v>
       </c>
       <c r="J13" t="str">
         <v>null</v>
@@ -895,31 +895,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/controle-inrichting</v>
       </c>
       <c r="B14" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C14" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="D14" t="str">
-        <v>Een typering van verschillende rubrieken (VLAREM rubriektype EGW ...).</v>
+        <v>controle_inrichting</v>
       </c>
       <c r="E14" t="str">
-        <v>null</v>
+        <v>Controle inrichting</v>
       </c>
       <c r="F14" t="str">
-        <v>Een typering van verschillende rubrieken (VLAREM rubriektype EGW ...).</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="G14" t="str">
-        <v>Rubriek types</v>
+        <v>null</v>
       </c>
       <c r="H14" t="str">
         <v>null</v>
       </c>
       <c r="I14" t="str">
-        <v>riepr-rubriek-type:egw|riepr-rubriek-type:vlarem</v>
+        <v>null</v>
       </c>
       <c r="J14" t="str">
         <v>null</v>
@@ -933,22 +933,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
       </c>
       <c r="B15" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C15" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="D15" t="str">
-        <v>null</v>
+        <v>meetput</v>
       </c>
       <c r="E15" t="str">
-        <v>null</v>
+        <v>Meetput</v>
       </c>
       <c r="F15" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="G15" t="str">
         <v>null</v>
@@ -957,7 +957,7 @@
         <v>null</v>
       </c>
       <c r="I15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k1|https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k2|https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k3</v>
+        <v>null</v>
       </c>
       <c r="J15" t="str">
         <v>null</v>
@@ -971,34 +971,34 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>riepr-emissiepunt-attr:schouw-diameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
       </c>
       <c r="B16" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C16" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="D16" t="str">
-        <v>null</v>
+        <v>grondwaterput</v>
       </c>
       <c r="E16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
+        <v>Grondwaterput</v>
       </c>
       <c r="F16" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="G16" t="str">
-        <v>Diameter van de schouw</v>
+        <v>null</v>
       </c>
       <c r="H16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
+        <v>Een put voor de onttrekking van grondwater.</v>
       </c>
       <c r="I16" t="str">
-        <v>null</v>
+        <v>Een put voor de onttrekking van grondwater.</v>
       </c>
       <c r="J16" t="str">
-        <v>diameter</v>
+        <v>null</v>
       </c>
       <c r="K16" t="str">
         <v>null</v>
@@ -1009,34 +1009,34 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>riepr-emissiepunt-attr:schouw-hoogte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
       </c>
       <c r="B17" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
       </c>
       <c r="C17" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D17" t="str">
-        <v>null</v>
+        <v>EMISSIE</v>
       </c>
       <c r="E17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
+        <v>Emissie</v>
       </c>
       <c r="F17" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G17" t="str">
-        <v>Hoogte van de schouw</v>
+        <v>null</v>
       </c>
       <c r="H17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
+        <v>null</v>
       </c>
       <c r="I17" t="str">
         <v>null</v>
       </c>
       <c r="J17" t="str">
-        <v>hoogte</v>
+        <v>null</v>
       </c>
       <c r="K17" t="str">
         <v>null</v>
@@ -1047,34 +1047,34 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>riepr-emissiepunt-type:emissiepunt</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/meet</v>
       </c>
       <c r="B18" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D18" t="str">
-        <v>null</v>
+        <v>MEET</v>
       </c>
       <c r="E18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>Meet</v>
       </c>
       <c r="F18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G18" t="str">
-        <v>Emissiepunt</v>
+        <v>null</v>
       </c>
       <c r="H18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>null</v>
       </c>
       <c r="I18" t="str">
         <v>null</v>
       </c>
       <c r="J18" t="str">
-        <v>emissiepunt</v>
+        <v>null</v>
       </c>
       <c r="K18" t="str">
         <v>null</v>
@@ -1085,34 +1085,34 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>riepr-emissiepunt-type:fakkel</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/overbrenging</v>
       </c>
       <c r="B19" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C19" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D19" t="str">
-        <v>null</v>
+        <v>OVERBRENGING</v>
       </c>
       <c r="E19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>Overbrenging</v>
       </c>
       <c r="F19" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G19" t="str">
-        <v>Fakkel</v>
+        <v>null</v>
       </c>
       <c r="H19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>null</v>
       </c>
       <c r="I19" t="str">
         <v>null</v>
       </c>
       <c r="J19" t="str">
-        <v>fakkel</v>
+        <v>null</v>
       </c>
       <c r="K19" t="str">
         <v>null</v>
@@ -1123,34 +1123,34 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>riepr-emissiepunt-type:lozingspunt</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verbruik</v>
       </c>
       <c r="B20" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
       </c>
       <c r="C20" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D20" t="str">
-        <v>null</v>
+        <v>VERBRUIK</v>
       </c>
       <c r="E20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>Verbruik</v>
       </c>
       <c r="F20" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G20" t="str">
-        <v>Lozingspunt</v>
+        <v>null</v>
       </c>
       <c r="H20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>null</v>
       </c>
       <c r="I20" t="str">
         <v>null</v>
       </c>
       <c r="J20" t="str">
-        <v>lozingspunt</v>
+        <v>null</v>
       </c>
       <c r="K20" t="str">
         <v>null</v>
@@ -1161,34 +1161,34 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>riepr-emissiepunt-type:schouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
       </c>
       <c r="B21" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
       </c>
       <c r="C21" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D21" t="str">
-        <v>null</v>
+        <v>VERWERKING</v>
       </c>
       <c r="E21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>Verwerking</v>
       </c>
       <c r="F21" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G21" t="str">
-        <v>Schouw</v>
+        <v>null</v>
       </c>
       <c r="H21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>null</v>
       </c>
       <c r="I21" t="str">
         <v>null</v>
       </c>
       <c r="J21" t="str">
-        <v>schouw</v>
+        <v>null</v>
       </c>
       <c r="K21" t="str">
         <v>null</v>
@@ -1199,34 +1199,34 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>riepr-filter-type:peilfilter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/aardgas</v>
       </c>
       <c r="B22" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C22" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
       </c>
       <c r="D22" t="str">
-        <v>Filter voor het meten van het grondwaterpeil.</v>
+        <v>aardgas</v>
       </c>
       <c r="E22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
+        <v>Aardgas</v>
       </c>
       <c r="F22" t="str">
-        <v>Filter voor het meten van het grondwaterpeil.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
       </c>
       <c r="G22" t="str">
-        <v>Peilfilter</v>
+        <v>null</v>
       </c>
       <c r="H22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
+        <v>null</v>
       </c>
       <c r="I22" t="str">
         <v>null</v>
       </c>
       <c r="J22" t="str">
-        <v>peilfilter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verbruik</v>
       </c>
       <c r="K22" t="str">
         <v>null</v>
@@ -1237,34 +1237,34 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>riepr-installatie-type:gpbv</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/co2</v>
       </c>
       <c r="B23" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C23" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
       </c>
       <c r="D23" t="str">
-        <v>Installatie die valt onder de richtlijn industriële emissies (IED/GPBV).</v>
+        <v>co2</v>
       </c>
       <c r="E23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>CO2</v>
       </c>
       <c r="F23" t="str">
-        <v>Installatie die valt onder de richtlijn industriële emissies (IED/GPBV).</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
       </c>
       <c r="G23" t="str">
-        <v>GPBV installatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/stof/co2</v>
       </c>
       <c r="H23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>null</v>
       </c>
       <c r="I23" t="str">
         <v>null</v>
       </c>
       <c r="J23" t="str">
-        <v>GPBV</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
       </c>
       <c r="K23" t="str">
         <v>null</v>
@@ -1275,34 +1275,34 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>riepr-installatie-type:iepr</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/grondstof</v>
       </c>
       <c r="B24" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C24" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
       </c>
       <c r="D24" t="str">
-        <v>Installatie in het kader van IEPR rapportering.</v>
+        <v>grondstof</v>
       </c>
       <c r="E24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>Grondstof</v>
       </c>
       <c r="F24" t="str">
-        <v>Installatie in het kader van IEPR rapportering.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
       </c>
       <c r="G24" t="str">
-        <v>IEPR installatie</v>
+        <v>null</v>
       </c>
       <c r="H24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>Grondstof met vrije invoer subtypering.</v>
       </c>
       <c r="I24" t="str">
-        <v>null</v>
+        <v>Grondstof met vrije invoer subtypering.</v>
       </c>
       <c r="J24" t="str">
-        <v>IEPR</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
       </c>
       <c r="K24" t="str">
         <v>null</v>
@@ -1313,34 +1313,34 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>riepr-installatie-type:oven</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/rubriek-type/egw</v>
       </c>
       <c r="B25" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
       </c>
       <c r="D25" t="str">
-        <v>null</v>
+        <v>EGW</v>
       </c>
       <c r="E25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>EGW</v>
       </c>
       <c r="F25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
       </c>
       <c r="G25" t="str">
-        <v>Oven</v>
+        <v>null</v>
       </c>
       <c r="H25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>EGW rubriektype.</v>
       </c>
       <c r="I25" t="str">
-        <v>null</v>
+        <v>EGW rubriektype.</v>
       </c>
       <c r="J25" t="str">
-        <v>oven</v>
+        <v>null</v>
       </c>
       <c r="K25" t="str">
         <v>null</v>
@@ -1351,34 +1351,34 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>riepr-installatie-type:zuiveringsinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/rubriek-type/vlarem</v>
       </c>
       <c r="B26" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C26" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
       </c>
       <c r="D26" t="str">
-        <v>null</v>
+        <v>VLAREM</v>
       </c>
       <c r="E26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>VLAREM</v>
       </c>
       <c r="F26" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
       </c>
       <c r="G26" t="str">
-        <v>Zuiveringsinstallatie</v>
+        <v>null</v>
       </c>
       <c r="H26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>VLAREM rubriektype.</v>
       </c>
       <c r="I26" t="str">
-        <v>null</v>
+        <v>VLAREM rubriektype.</v>
       </c>
       <c r="J26" t="str">
-        <v>zuiveringsinstallatie</v>
+        <v>null</v>
       </c>
       <c r="K26" t="str">
         <v>null</v>
@@ -1389,37 +1389,37 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>riepr-meetinstrument-type:debietmeter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k1</v>
       </c>
       <c r="B27" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C27" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
       </c>
       <c r="D27" t="str">
         <v>null</v>
       </c>
       <c r="E27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetinstrument_type</v>
+        <v>Klasse 1</v>
       </c>
       <c r="F27" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
       </c>
       <c r="G27" t="str">
-        <v>Debietmeter</v>
+        <v>null</v>
       </c>
       <c r="H27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetinstrument_type</v>
+        <v>Indelingsklasse voor inrichtingen met de grootste milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 1 (zwaarste procedure).</v>
       </c>
       <c r="I27" t="str">
-        <v>null</v>
+        <v>Indelingsklasse voor inrichtingen met de grootste milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 1 (zwaarste procedure).</v>
       </c>
       <c r="J27" t="str">
-        <v>debietmeter</v>
+        <v>null</v>
       </c>
       <c r="K27" t="str">
-        <v>null</v>
+        <v>VLAREM klasse 1</v>
       </c>
       <c r="L27" t="str">
         <v>null</v>
@@ -1427,37 +1427,37 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>riepr-meetpunt-type:controle-inrichting</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k2</v>
       </c>
       <c r="B28" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C28" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
       </c>
       <c r="D28" t="str">
         <v>null</v>
       </c>
       <c r="E28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>Klasse 2</v>
       </c>
       <c r="F28" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
       </c>
       <c r="G28" t="str">
-        <v>Controle inrichting</v>
+        <v>null</v>
       </c>
       <c r="H28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>Indelingsklasse voor inrichtingen met een middelgrote milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 2.</v>
       </c>
       <c r="I28" t="str">
-        <v>null</v>
+        <v>Indelingsklasse voor inrichtingen met een middelgrote milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 2.</v>
       </c>
       <c r="J28" t="str">
-        <v>controle_inrichting</v>
+        <v>null</v>
       </c>
       <c r="K28" t="str">
-        <v>null</v>
+        <v>VLAREM klasse 2</v>
       </c>
       <c r="L28" t="str">
         <v>null</v>
@@ -1465,37 +1465,37 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>riepr-meetpunt-type:meetput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k3</v>
       </c>
       <c r="B29" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C29" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
       </c>
       <c r="D29" t="str">
         <v>null</v>
       </c>
       <c r="E29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>Klasse 3</v>
       </c>
       <c r="F29" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
       </c>
       <c r="G29" t="str">
-        <v>Meetput</v>
+        <v>null</v>
       </c>
       <c r="H29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>Indelingsklasse voor inrichtingen met een beperkte milieu-impact. Voor deze activiteiten geldt een meldingsplicht (klasse 3).</v>
       </c>
       <c r="I29" t="str">
-        <v>null</v>
+        <v>Indelingsklasse voor inrichtingen met een beperkte milieu-impact. Voor deze activiteiten geldt een meldingsplicht (klasse 3).</v>
       </c>
       <c r="J29" t="str">
-        <v>meetput</v>
+        <v>null</v>
       </c>
       <c r="K29" t="str">
-        <v>null</v>
+        <v>VLAREM klasse 3</v>
       </c>
       <c r="L29" t="str">
         <v>null</v>
@@ -1503,48 +1503,48 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>riepr-onttrekkingspunt-type:grondwaterput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
       </c>
       <c r="B30" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C30" t="str">
         <v>null</v>
       </c>
       <c r="D30" t="str">
-        <v>Een put voor de onttrekking van grondwater.</v>
+        <v>null</v>
       </c>
       <c r="E30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>Emissiepunt attributen</v>
       </c>
       <c r="F30" t="str">
-        <v>Een put voor de onttrekking van grondwater.</v>
+        <v>null</v>
       </c>
       <c r="G30" t="str">
-        <v>Grondwaterput</v>
+        <v>null</v>
       </c>
       <c r="H30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>Een lijst die een koppeling maakt tussen soorten emissiepunten en de attributen die van toepassing zijn.</v>
       </c>
       <c r="I30" t="str">
-        <v>null</v>
+        <v>Een lijst die een koppeling maakt tussen soorten emissiepunten en de attributen die van toepassing zijn.</v>
       </c>
       <c r="J30" t="str">
-        <v>grondwaterput</v>
+        <v>null</v>
       </c>
       <c r="K30" t="str">
         <v>null</v>
       </c>
       <c r="L30" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-attribuut/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-attribuut/schouw-hoogte</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>riepr-procedure-type:emissie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="B31" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C31" t="str">
         <v>null</v>
@@ -1553,36 +1553,36 @@
         <v>null</v>
       </c>
       <c r="E31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Emissiepunt types</v>
       </c>
       <c r="F31" t="str">
         <v>null</v>
       </c>
       <c r="G31" t="str">
-        <v>Emissie</v>
+        <v>null</v>
       </c>
       <c r="H31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een lijst van verschillende soorten emissiepunten met mogelijke opsplitsing in subtyperingen.</v>
       </c>
       <c r="I31" t="str">
-        <v>null</v>
+        <v>Een lijst van verschillende soorten emissiepunten met mogelijke opsplitsing in subtyperingen.</v>
       </c>
       <c r="J31" t="str">
-        <v>EMISSIE</v>
+        <v>null</v>
       </c>
       <c r="K31" t="str">
         <v>null</v>
       </c>
       <c r="L31" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/fakkel|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>riepr-procedure-type:meet</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
       </c>
       <c r="B32" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C32" t="str">
         <v>null</v>
@@ -1591,36 +1591,36 @@
         <v>null</v>
       </c>
       <c r="E32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Filter types</v>
       </c>
       <c r="F32" t="str">
         <v>null</v>
       </c>
       <c r="G32" t="str">
-        <v>Meet</v>
+        <v>null</v>
       </c>
       <c r="H32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een lijst van verschillende types van filters en de objecten waarop van toepassing.</v>
       </c>
       <c r="I32" t="str">
-        <v>null</v>
+        <v>Een lijst van verschillende types van filters en de objecten waarop van toepassing.</v>
       </c>
       <c r="J32" t="str">
-        <v>MEET</v>
+        <v>null</v>
       </c>
       <c r="K32" t="str">
         <v>null</v>
       </c>
       <c r="L32" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peilfilter</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>riepr-procedure-type:overbrenging</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="B33" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C33" t="str">
         <v>null</v>
@@ -1629,36 +1629,36 @@
         <v>null</v>
       </c>
       <c r="E33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Installatie types</v>
       </c>
       <c r="F33" t="str">
         <v>null</v>
       </c>
       <c r="G33" t="str">
-        <v>Overbrenging</v>
+        <v>null</v>
       </c>
       <c r="H33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een lijst van verschillende types van installaties met eventueel subtyperingen.</v>
       </c>
       <c r="I33" t="str">
-        <v>null</v>
+        <v>Een lijst van verschillende types van installaties met eventueel subtyperingen.</v>
       </c>
       <c r="J33" t="str">
-        <v>OVERBRENGING</v>
+        <v>null</v>
       </c>
       <c r="K33" t="str">
         <v>null</v>
       </c>
       <c r="L33" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/gpbv|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/iepr|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/oven|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/zuiveringsinstallatie</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>riepr-procedure-type:verbruik</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetinstrument_type</v>
       </c>
       <c r="B34" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C34" t="str">
         <v>null</v>
@@ -1667,36 +1667,36 @@
         <v>null</v>
       </c>
       <c r="E34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Meetinstrument types</v>
       </c>
       <c r="F34" t="str">
         <v>null</v>
       </c>
       <c r="G34" t="str">
-        <v>Verbruik</v>
+        <v>null</v>
       </c>
       <c r="H34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een lijst van verschillende soorten meetinstrumenten.</v>
       </c>
       <c r="I34" t="str">
-        <v>null</v>
+        <v>Een lijst van verschillende soorten meetinstrumenten.</v>
       </c>
       <c r="J34" t="str">
-        <v>VERBRUIK</v>
+        <v>null</v>
       </c>
       <c r="K34" t="str">
         <v>null</v>
       </c>
       <c r="L34" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetinstrument-type/debietmeter</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>riepr-procedure-type:verwerking</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="B35" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C35" t="str">
         <v>null</v>
@@ -1705,36 +1705,36 @@
         <v>null</v>
       </c>
       <c r="E35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Meetpunt types</v>
       </c>
       <c r="F35" t="str">
         <v>null</v>
       </c>
       <c r="G35" t="str">
-        <v>Verwerking</v>
+        <v>null</v>
       </c>
       <c r="H35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een lijst van verschillende soorten meetpunten.</v>
       </c>
       <c r="I35" t="str">
-        <v>null</v>
+        <v>Een lijst van verschillende soorten meetpunten.</v>
       </c>
       <c r="J35" t="str">
-        <v>VERWERKING</v>
+        <v>null</v>
       </c>
       <c r="K35" t="str">
         <v>null</v>
       </c>
       <c r="L35" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/controle-inrichting|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>riepr-procesvariabele-type:aardgas</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="B36" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C36" t="str">
         <v>null</v>
@@ -1743,36 +1743,36 @@
         <v>null</v>
       </c>
       <c r="E36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>Onttrekkingspunt types</v>
       </c>
       <c r="F36" t="str">
         <v>null</v>
       </c>
       <c r="G36" t="str">
-        <v>Aardgas</v>
+        <v>null</v>
       </c>
       <c r="H36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>Een lijst van verschillende soorten onttrekkingspunten met mogelijke opsplitsing in subtyperingen.</v>
       </c>
       <c r="I36" t="str">
-        <v>null</v>
+        <v>Een lijst van verschillende soorten onttrekkingspunten met mogelijke opsplitsing in subtyperingen.</v>
       </c>
       <c r="J36" t="str">
-        <v>aardgas</v>
+        <v>null</v>
       </c>
       <c r="K36" t="str">
-        <v>riepr-procedure-type:verbruik</v>
+        <v>null</v>
       </c>
       <c r="L36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/stof/aardgas</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>riepr-procesvariabele-type:co2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="B37" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C37" t="str">
         <v>null</v>
@@ -1781,142 +1781,142 @@
         <v>null</v>
       </c>
       <c r="E37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>Procedure types</v>
       </c>
       <c r="F37" t="str">
         <v>null</v>
       </c>
       <c r="G37" t="str">
-        <v>CO2</v>
+        <v>null</v>
       </c>
       <c r="H37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>Een lijst van verschillende hoofdtyperingen van procedures in een procesplan.</v>
       </c>
       <c r="I37" t="str">
-        <v>null</v>
+        <v>Een lijst van verschillende hoofdtyperingen van procedures in een procesplan.</v>
       </c>
       <c r="J37" t="str">
-        <v>co2</v>
+        <v>null</v>
       </c>
       <c r="K37" t="str">
-        <v>riepr-procedure-type:emissie</v>
+        <v>null</v>
       </c>
       <c r="L37" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/meet|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/overbrenging|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verbruik|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>riepr-procesvariabele-type:grondstof</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
       </c>
       <c r="B38" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C38" t="str">
         <v>null</v>
       </c>
       <c r="D38" t="str">
-        <v>Grondstof met vrije invoer subtypering.</v>
+        <v>null</v>
       </c>
       <c r="E38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>Proces variabele types</v>
       </c>
       <c r="F38" t="str">
-        <v>Grondstof met vrije invoer subtypering.</v>
+        <v>null</v>
       </c>
       <c r="G38" t="str">
-        <v>Grondstof</v>
+        <v>null</v>
       </c>
       <c r="H38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>Een lijst die verschillende types geeft voor stoffen die aangeduid mogen worden bij bepaalde procedure types.</v>
       </c>
       <c r="I38" t="str">
-        <v>null</v>
+        <v>Een lijst die verschillende types geeft voor stoffen die aangeduid mogen worden bij bepaalde procedure types.</v>
       </c>
       <c r="J38" t="str">
-        <v>grondstof</v>
+        <v>null</v>
       </c>
       <c r="K38" t="str">
-        <v>riepr-procedure-type:verwerking</v>
+        <v>null</v>
       </c>
       <c r="L38" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/aardgas|https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/co2|https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/grondstof</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>riepr-rubriek-type:egw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
       </c>
       <c r="B39" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C39" t="str">
         <v>null</v>
       </c>
       <c r="D39" t="str">
-        <v>EGW rubriektype.</v>
+        <v>null</v>
       </c>
       <c r="E39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
+        <v>Rubriek types</v>
       </c>
       <c r="F39" t="str">
-        <v>EGW rubriektype.</v>
+        <v>null</v>
       </c>
       <c r="G39" t="str">
-        <v>EGW</v>
+        <v>null</v>
       </c>
       <c r="H39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
+        <v>Een typering van verschillende rubrieken (VLAREM rubriektype EGW ...).</v>
       </c>
       <c r="I39" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende rubrieken (VLAREM rubriektype EGW ...).</v>
       </c>
       <c r="J39" t="str">
-        <v>EGW</v>
+        <v>null</v>
       </c>
       <c r="K39" t="str">
         <v>null</v>
       </c>
       <c r="L39" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/rubriek-type/egw|https://data.omgeving.vlaanderen.be/id/concept/riepr/rubriek-type/vlarem</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>riepr-rubriek-type:vlarem</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
       </c>
       <c r="B40" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C40" t="str">
         <v>null</v>
       </c>
       <c r="D40" t="str">
-        <v>VLAREM rubriektype.</v>
+        <v>null</v>
       </c>
       <c r="E40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
+        <v>null</v>
       </c>
       <c r="F40" t="str">
-        <v>VLAREM rubriektype.</v>
+        <v>null</v>
       </c>
       <c r="G40" t="str">
-        <v>VLAREM</v>
+        <v>null</v>
       </c>
       <c r="H40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
+        <v>null</v>
       </c>
       <c r="I40" t="str">
         <v>null</v>
       </c>
       <c r="J40" t="str">
-        <v>VLAREM</v>
+        <v>null</v>
       </c>
       <c r="K40" t="str">
         <v>null</v>
       </c>
       <c r="L40" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k1|https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k2|https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k3</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:P29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,60 +407,72 @@
         <v>_type</v>
       </c>
       <c r="C1" t="str">
+        <v>definition</v>
+      </c>
+      <c r="D1" t="str">
         <v>inScheme</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>code</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>note</v>
+      </c>
+      <c r="G1" t="str">
         <v>prefLabel</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>topConceptOf</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
+        <v>narrower</v>
+      </c>
+      <c r="J1" t="str">
+        <v>narrowerTransitive</v>
+      </c>
+      <c r="K1" t="str">
+        <v>semanticRelation</v>
+      </c>
+      <c r="L1" t="str">
+        <v>broader</v>
+      </c>
+      <c r="M1" t="str">
+        <v>broaderTransitive</v>
+      </c>
+      <c r="N1" t="str">
+        <v>hasTopConcept</v>
+      </c>
+      <c r="O1" t="str">
         <v>relevantriepr</v>
       </c>
-      <c r="H1" t="str">
-        <v>definition</v>
-      </c>
-      <c r="I1" t="str">
-        <v>note</v>
-      </c>
-      <c r="J1" t="str">
-        <v>subject</v>
-      </c>
-      <c r="K1" t="str">
-        <v>altLabel</v>
-      </c>
-      <c r="L1" t="str">
-        <v>hasTopConcept</v>
+      <c r="P1" t="str">
+        <v>seeAlso</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-attribuut/schouw-diameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
       </c>
       <c r="B2" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
+        <v>Een regulier emissiepunt.</v>
       </c>
       <c r="D2" t="str">
-        <v>diameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="E2" t="str">
-        <v>Diameter van de schouw</v>
+        <v>emissiepunt</v>
       </c>
       <c r="F2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
+        <v>Een regulier emissiepunt.</v>
       </c>
       <c r="G2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>Emissiepunt</v>
       </c>
       <c r="H2" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="I2" t="str">
         <v>null</v>
@@ -472,33 +484,45 @@
         <v>null</v>
       </c>
       <c r="L2" t="str">
+        <v>null</v>
+      </c>
+      <c r="M2" t="str">
+        <v>null</v>
+      </c>
+      <c r="N2" t="str">
+        <v>null</v>
+      </c>
+      <c r="O2" t="str">
+        <v>null</v>
+      </c>
+      <c r="P2" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-attribuut/schouw-hoogte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
       </c>
       <c r="B3" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
+        <v>Een lozing naar water.</v>
       </c>
       <c r="D3" t="str">
-        <v>hoogte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="E3" t="str">
-        <v>Hoogte van de schouw</v>
+        <v>lozingspunt</v>
       </c>
       <c r="F3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
+        <v>Een lozing naar water.</v>
       </c>
       <c r="G3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>Lozingspunt</v>
       </c>
       <c r="H3" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="I3" t="str">
         <v>null</v>
@@ -510,72 +534,96 @@
         <v>null</v>
       </c>
       <c r="L3" t="str">
+        <v>null</v>
+      </c>
+      <c r="M3" t="str">
+        <v>null</v>
+      </c>
+      <c r="N3" t="str">
+        <v>null</v>
+      </c>
+      <c r="O3" t="str">
+        <v>null</v>
+      </c>
+      <c r="P3" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="B4" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C4" t="str">
+        <v>Een schoorsteen.</v>
+      </c>
+      <c r="D4" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
-      <c r="D4" t="str">
-        <v>emissiepunt</v>
-      </c>
       <c r="E4" t="str">
-        <v>Emissiepunt</v>
+        <v>schoorsteen</v>
       </c>
       <c r="F4" t="str">
+        <v>Een schoorsteen.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Schoorsteen</v>
+      </c>
+      <c r="H4" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
-      <c r="G4" t="str">
-        <v>null</v>
-      </c>
-      <c r="H4" t="str">
-        <v>null</v>
-      </c>
       <c r="I4" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
       </c>
       <c r="J4" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
       </c>
       <c r="K4" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
       </c>
       <c r="L4" t="str">
+        <v>null</v>
+      </c>
+      <c r="M4" t="str">
+        <v>null</v>
+      </c>
+      <c r="N4" t="str">
+        <v>null</v>
+      </c>
+      <c r="O4" t="str">
+        <v>null</v>
+      </c>
+      <c r="P4" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/fakkel</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="B5" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C5" t="str">
+        <v>null</v>
+      </c>
+      <c r="D5" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
-      <c r="D5" t="str">
-        <v>fakkel</v>
-      </c>
       <c r="E5" t="str">
-        <v>Fakkel</v>
+        <v>schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="F5" t="str">
+        <v>null</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Schoorsteen met horizontale uitstroom</v>
+      </c>
+      <c r="H5" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
-      <c r="G5" t="str">
-        <v>null</v>
-      </c>
-      <c r="H5" t="str">
-        <v>null</v>
-      </c>
       <c r="I5" t="str">
         <v>null</v>
       </c>
@@ -583,37 +631,49 @@
         <v>null</v>
       </c>
       <c r="K5" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="L5" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+      </c>
+      <c r="M5" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+      </c>
+      <c r="N5" t="str">
+        <v>null</v>
+      </c>
+      <c r="O5" t="str">
+        <v>null</v>
+      </c>
+      <c r="P5" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
       </c>
       <c r="B6" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C6" t="str">
+        <v>null</v>
+      </c>
+      <c r="D6" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
-      <c r="D6" t="str">
-        <v>lozingspunt</v>
-      </c>
       <c r="E6" t="str">
-        <v>Lozingspunt</v>
+        <v>schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="F6" t="str">
+        <v>null</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Schoorsteen met vertikale uitstroom</v>
+      </c>
+      <c r="H6" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
-      <c r="G6" t="str">
-        <v>null</v>
-      </c>
-      <c r="H6" t="str">
-        <v>null</v>
-      </c>
       <c r="I6" t="str">
         <v>null</v>
       </c>
@@ -621,9 +681,21 @@
         <v>null</v>
       </c>
       <c r="K6" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="L6" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+      </c>
+      <c r="M6" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+      </c>
+      <c r="N6" t="str">
+        <v>null</v>
+      </c>
+      <c r="O6" t="str">
+        <v>null</v>
+      </c>
+      <c r="P6" t="str">
         <v>null</v>
       </c>
     </row>
@@ -635,23 +707,23 @@
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C7" t="str">
+        <v>Een schouw.</v>
+      </c>
+      <c r="D7" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>schouw</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
+        <v>Een schouw.</v>
+      </c>
+      <c r="G7" t="str">
         <v>Schouw</v>
       </c>
-      <c r="F7" t="str">
+      <c r="H7" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
-      <c r="G7" t="str">
-        <v>null</v>
-      </c>
-      <c r="H7" t="str">
-        <v>null</v>
-      </c>
       <c r="I7" t="str">
         <v>null</v>
       </c>
@@ -662,36 +734,48 @@
         <v>null</v>
       </c>
       <c r="L7" t="str">
+        <v>null</v>
+      </c>
+      <c r="M7" t="str">
+        <v>null</v>
+      </c>
+      <c r="N7" t="str">
+        <v>null</v>
+      </c>
+      <c r="O7" t="str">
+        <v>null</v>
+      </c>
+      <c r="P7" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peilfilter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="B8" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
+        <v>null</v>
       </c>
       <c r="D8" t="str">
-        <v>peilfilter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="E8" t="str">
-        <v>Peilfilter</v>
+        <v>directe_stookinstallatie</v>
       </c>
       <c r="F8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
+        <v>null</v>
       </c>
       <c r="G8" t="str">
-        <v>null</v>
+        <v>Directe Stookinstallatie</v>
       </c>
       <c r="H8" t="str">
-        <v>Filter voor het meten van het grondwaterpeil.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="I8" t="str">
-        <v>Filter voor het meten van het grondwaterpeil.</v>
+        <v>null</v>
       </c>
       <c r="J8" t="str">
         <v>null</v>
@@ -700,36 +784,48 @@
         <v>null</v>
       </c>
       <c r="L8" t="str">
+        <v>null</v>
+      </c>
+      <c r="M8" t="str">
+        <v>null</v>
+      </c>
+      <c r="N8" t="str">
+        <v>null</v>
+      </c>
+      <c r="O8" t="str">
+        <v>null</v>
+      </c>
+      <c r="P8" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/gpbv</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="B9" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C9" t="str">
+        <v>null</v>
+      </c>
+      <c r="D9" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
-      <c r="D9" t="str">
-        <v>GPBV</v>
-      </c>
       <c r="E9" t="str">
-        <v>GPBV installatie</v>
+        <v>stookinstallatie</v>
       </c>
       <c r="F9" t="str">
+        <v>null</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Stookinstallatie</v>
+      </c>
+      <c r="H9" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
-      <c r="G9" t="str">
-        <v>null</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Installatie die valt onder de richtlijn industriële emissies (IED/GPBV).</v>
-      </c>
       <c r="I9" t="str">
-        <v>Installatie die valt onder de richtlijn industriële emissies (IED/GPBV).</v>
+        <v>null</v>
       </c>
       <c r="J9" t="str">
         <v>null</v>
@@ -738,36 +834,48 @@
         <v>null</v>
       </c>
       <c r="L9" t="str">
+        <v>null</v>
+      </c>
+      <c r="M9" t="str">
+        <v>null</v>
+      </c>
+      <c r="N9" t="str">
+        <v>null</v>
+      </c>
+      <c r="O9" t="str">
+        <v>null</v>
+      </c>
+      <c r="P9" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/iepr</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
       </c>
       <c r="B10" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>null</v>
       </c>
       <c r="D10" t="str">
-        <v>IEPR</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="E10" t="str">
-        <v>IEPR installatie</v>
+        <v>meetput</v>
       </c>
       <c r="F10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>null</v>
       </c>
       <c r="G10" t="str">
-        <v>null</v>
+        <v>Meetput</v>
       </c>
       <c r="H10" t="str">
-        <v>Installatie in het kader van IEPR rapportering.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="I10" t="str">
-        <v>Installatie in het kader van IEPR rapportering.</v>
+        <v>null</v>
       </c>
       <c r="J10" t="str">
         <v>null</v>
@@ -776,33 +884,45 @@
         <v>null</v>
       </c>
       <c r="L10" t="str">
+        <v>null</v>
+      </c>
+      <c r="M10" t="str">
+        <v>null</v>
+      </c>
+      <c r="N10" t="str">
+        <v>null</v>
+      </c>
+      <c r="O10" t="str">
+        <v>null</v>
+      </c>
+      <c r="P10" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/oven</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
       </c>
       <c r="B11" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>null</v>
       </c>
       <c r="D11" t="str">
-        <v>oven</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="E11" t="str">
-        <v>Oven</v>
+        <v>grondwaterput</v>
       </c>
       <c r="F11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>null</v>
       </c>
       <c r="G11" t="str">
-        <v>null</v>
+        <v>Grondwaterput</v>
       </c>
       <c r="H11" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="I11" t="str">
         <v>null</v>
@@ -814,33 +934,45 @@
         <v>null</v>
       </c>
       <c r="L11" t="str">
+        <v>null</v>
+      </c>
+      <c r="M11" t="str">
+        <v>null</v>
+      </c>
+      <c r="N11" t="str">
+        <v>null</v>
+      </c>
+      <c r="O11" t="str">
+        <v>null</v>
+      </c>
+      <c r="P11" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/zuiveringsinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
       </c>
       <c r="B12" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="D12" t="str">
-        <v>zuiveringsinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="E12" t="str">
-        <v>Zuiveringsinstallatie</v>
+        <v>EMISSIE</v>
       </c>
       <c r="F12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="G12" t="str">
-        <v>null</v>
+        <v>Emissie</v>
       </c>
       <c r="H12" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="I12" t="str">
         <v>null</v>
@@ -852,33 +984,45 @@
         <v>null</v>
       </c>
       <c r="L12" t="str">
+        <v>null</v>
+      </c>
+      <c r="M12" t="str">
+        <v>null</v>
+      </c>
+      <c r="N12" t="str">
+        <v>null</v>
+      </c>
+      <c r="O12" t="str">
+        <v>null</v>
+      </c>
+      <c r="P12" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetinstrument-type/debietmeter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking</v>
       </c>
       <c r="B13" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetinstrument_type</v>
+        <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="D13" t="str">
-        <v>debietmeter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="E13" t="str">
-        <v>Debietmeter</v>
+        <v>ONTTREKKING</v>
       </c>
       <c r="F13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetinstrument_type</v>
+        <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="G13" t="str">
-        <v>null</v>
+        <v>Onttrekking</v>
       </c>
       <c r="H13" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="I13" t="str">
         <v>null</v>
@@ -890,33 +1034,45 @@
         <v>null</v>
       </c>
       <c r="L13" t="str">
+        <v>null</v>
+      </c>
+      <c r="M13" t="str">
+        <v>null</v>
+      </c>
+      <c r="N13" t="str">
+        <v>null</v>
+      </c>
+      <c r="O13" t="str">
+        <v>null</v>
+      </c>
+      <c r="P13" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/controle-inrichting</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport</v>
       </c>
       <c r="B14" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="D14" t="str">
-        <v>controle_inrichting</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="E14" t="str">
-        <v>Controle inrichting</v>
+        <v>TRANSPORT</v>
       </c>
       <c r="F14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="G14" t="str">
-        <v>null</v>
+        <v>Transport</v>
       </c>
       <c r="H14" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="I14" t="str">
         <v>null</v>
@@ -928,33 +1084,45 @@
         <v>null</v>
       </c>
       <c r="L14" t="str">
+        <v>null</v>
+      </c>
+      <c r="M14" t="str">
+        <v>null</v>
+      </c>
+      <c r="N14" t="str">
+        <v>null</v>
+      </c>
+      <c r="O14" t="str">
+        <v>null</v>
+      </c>
+      <c r="P14" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
       </c>
       <c r="B15" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="D15" t="str">
-        <v>meetput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="E15" t="str">
-        <v>Meetput</v>
+        <v>VERWERKING</v>
       </c>
       <c r="F15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="G15" t="str">
-        <v>null</v>
+        <v>Verwerking</v>
       </c>
       <c r="H15" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="I15" t="str">
         <v>null</v>
@@ -966,36 +1134,48 @@
         <v>null</v>
       </c>
       <c r="L15" t="str">
+        <v>null</v>
+      </c>
+      <c r="M15" t="str">
+        <v>null</v>
+      </c>
+      <c r="N15" t="str">
+        <v>null</v>
+      </c>
+      <c r="O15" t="str">
+        <v>null</v>
+      </c>
+      <c r="P15" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="B16" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="D16" t="str">
-        <v>grondwaterput</v>
+        <v>null</v>
       </c>
       <c r="E16" t="str">
-        <v>Grondwaterput</v>
+        <v>null</v>
       </c>
       <c r="F16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="G16" t="str">
-        <v>null</v>
+        <v>Emissiepunt eigenschappen</v>
       </c>
       <c r="H16" t="str">
-        <v>Een put voor de onttrekking van grondwater.</v>
+        <v>null</v>
       </c>
       <c r="I16" t="str">
-        <v>Een put voor de onttrekking van grondwater.</v>
+        <v>null</v>
       </c>
       <c r="J16" t="str">
         <v>null</v>
@@ -1004,30 +1184,42 @@
         <v>null</v>
       </c>
       <c r="L16" t="str">
+        <v>null</v>
+      </c>
+      <c r="M16" t="str">
+        <v>null</v>
+      </c>
+      <c r="N16" t="str">
+        <v>riepr-emissiepunt-eigenschappen:schouw-diameter|riepr-emissiepunt-eigenschappen:schouw-hoogte</v>
+      </c>
+      <c r="O16" t="str">
+        <v>null</v>
+      </c>
+      <c r="P16" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="B17" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="D17" t="str">
-        <v>EMISSIE</v>
+        <v>null</v>
       </c>
       <c r="E17" t="str">
-        <v>Emissie</v>
+        <v>null</v>
       </c>
       <c r="F17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="G17" t="str">
-        <v>null</v>
+        <v>Emissiepunt types</v>
       </c>
       <c r="H17" t="str">
         <v>null</v>
@@ -1042,30 +1234,42 @@
         <v>null</v>
       </c>
       <c r="L17" t="str">
+        <v>null</v>
+      </c>
+      <c r="M17" t="str">
+        <v>null</v>
+      </c>
+      <c r="N17" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+      </c>
+      <c r="O17" t="str">
+        <v>null</v>
+      </c>
+      <c r="P17" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/meet</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="B18" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="D18" t="str">
-        <v>MEET</v>
+        <v>null</v>
       </c>
       <c r="E18" t="str">
-        <v>Meet</v>
+        <v>null</v>
       </c>
       <c r="F18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="G18" t="str">
-        <v>null</v>
+        <v>Installatie types</v>
       </c>
       <c r="H18" t="str">
         <v>null</v>
@@ -1080,30 +1284,42 @@
         <v>null</v>
       </c>
       <c r="L18" t="str">
+        <v>null</v>
+      </c>
+      <c r="M18" t="str">
+        <v>null</v>
+      </c>
+      <c r="N18" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+      </c>
+      <c r="O18" t="str">
+        <v>null</v>
+      </c>
+      <c r="P18" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/overbrenging</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="B19" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>null</v>
       </c>
       <c r="D19" t="str">
-        <v>OVERBRENGING</v>
+        <v>null</v>
       </c>
       <c r="E19" t="str">
-        <v>Overbrenging</v>
+        <v>null</v>
       </c>
       <c r="F19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>null</v>
       </c>
       <c r="G19" t="str">
-        <v>null</v>
+        <v>Meetpunt types</v>
       </c>
       <c r="H19" t="str">
         <v>null</v>
@@ -1118,30 +1334,42 @@
         <v>null</v>
       </c>
       <c r="L19" t="str">
+        <v>null</v>
+      </c>
+      <c r="M19" t="str">
+        <v>null</v>
+      </c>
+      <c r="N19" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+      </c>
+      <c r="O19" t="str">
+        <v>null</v>
+      </c>
+      <c r="P19" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verbruik</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="B20" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="D20" t="str">
-        <v>VERBRUIK</v>
+        <v>null</v>
       </c>
       <c r="E20" t="str">
-        <v>Verbruik</v>
+        <v>null</v>
       </c>
       <c r="F20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="G20" t="str">
-        <v>null</v>
+        <v>Onttrekkingspunt types</v>
       </c>
       <c r="H20" t="str">
         <v>null</v>
@@ -1156,30 +1384,42 @@
         <v>null</v>
       </c>
       <c r="L20" t="str">
+        <v>null</v>
+      </c>
+      <c r="M20" t="str">
+        <v>null</v>
+      </c>
+      <c r="N20" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+      </c>
+      <c r="O20" t="str">
+        <v>null</v>
+      </c>
+      <c r="P20" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="B21" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2000/01/rdf-schema#Resource</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een typering van verschillende procedures.</v>
       </c>
       <c r="D21" t="str">
-        <v>VERWERKING</v>
+        <v>null</v>
       </c>
       <c r="E21" t="str">
-        <v>Verwerking</v>
+        <v>null</v>
       </c>
       <c r="F21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>Een typering van verschillende procedures.</v>
       </c>
       <c r="G21" t="str">
-        <v>null</v>
+        <v>Procedure types</v>
       </c>
       <c r="H21" t="str">
         <v>null</v>
@@ -1194,30 +1434,42 @@
         <v>null</v>
       </c>
       <c r="L21" t="str">
+        <v>null</v>
+      </c>
+      <c r="M21" t="str">
+        <v>null</v>
+      </c>
+      <c r="N21" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+      </c>
+      <c r="O21" t="str">
+        <v>null</v>
+      </c>
+      <c r="P21" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/aardgas</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="B22" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
       <c r="D22" t="str">
-        <v>aardgas</v>
+        <v>null</v>
       </c>
       <c r="E22" t="str">
-        <v>Aardgas</v>
+        <v>null</v>
       </c>
       <c r="F22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
       <c r="G22" t="str">
-        <v>null</v>
+        <v>Status types</v>
       </c>
       <c r="H22" t="str">
         <v>null</v>
@@ -1226,118 +1478,154 @@
         <v>null</v>
       </c>
       <c r="J22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verbruik</v>
+        <v>null</v>
       </c>
       <c r="K22" t="str">
         <v>null</v>
       </c>
       <c r="L22" t="str">
+        <v>null</v>
+      </c>
+      <c r="M22" t="str">
+        <v>null</v>
+      </c>
+      <c r="N22" t="str">
+        <v>riepr-status-type:definitief_uit_dienst|riepr-status-type:in_dienst|riepr-status-type:ontmanteld|riepr-status-type:tijdelijk_uit_dienst|riepr-status-type:voorgesteld</v>
+      </c>
+      <c r="O22" t="str">
+        <v>null</v>
+      </c>
+      <c r="P22" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/co2</v>
+        <v>riepr-emissiepunt-eigenschappen:schouw-diameter</v>
       </c>
       <c r="B23" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>null</v>
       </c>
       <c r="D23" t="str">
-        <v>co2</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="E23" t="str">
-        <v>CO2</v>
+        <v>diameter</v>
       </c>
       <c r="F23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>null</v>
       </c>
       <c r="G23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/stof/co2</v>
+        <v>Diameter van de schouw</v>
       </c>
       <c r="H23" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="I23" t="str">
         <v>null</v>
       </c>
       <c r="J23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
+        <v>null</v>
       </c>
       <c r="K23" t="str">
         <v>null</v>
       </c>
       <c r="L23" t="str">
+        <v>null</v>
+      </c>
+      <c r="M23" t="str">
+        <v>null</v>
+      </c>
+      <c r="N23" t="str">
+        <v>null</v>
+      </c>
+      <c r="O23" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+      </c>
+      <c r="P23" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/grondstof</v>
+        <v>riepr-emissiepunt-eigenschappen:schouw-hoogte</v>
       </c>
       <c r="B24" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>null</v>
       </c>
       <c r="D24" t="str">
-        <v>grondstof</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="E24" t="str">
-        <v>Grondstof</v>
+        <v>hoogte</v>
       </c>
       <c r="F24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
+        <v>null</v>
       </c>
       <c r="G24" t="str">
-        <v>null</v>
+        <v>Hoogte van de schouw</v>
       </c>
       <c r="H24" t="str">
-        <v>Grondstof met vrije invoer subtypering.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="I24" t="str">
-        <v>Grondstof met vrije invoer subtypering.</v>
+        <v>null</v>
       </c>
       <c r="J24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>null</v>
       </c>
       <c r="K24" t="str">
         <v>null</v>
       </c>
       <c r="L24" t="str">
+        <v>null</v>
+      </c>
+      <c r="M24" t="str">
+        <v>null</v>
+      </c>
+      <c r="N24" t="str">
+        <v>null</v>
+      </c>
+      <c r="O24" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+      </c>
+      <c r="P24" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/rubriek-type/egw</v>
+        <v>riepr-status-type:definitief_uit_dienst</v>
       </c>
       <c r="B25" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="D25" t="str">
-        <v>EGW</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="E25" t="str">
-        <v>EGW</v>
+        <v>DEFINITIEF_UIT_DIENST</v>
       </c>
       <c r="F25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="G25" t="str">
-        <v>null</v>
+        <v>Definitief uit dienst</v>
       </c>
       <c r="H25" t="str">
-        <v>EGW rubriektype.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="I25" t="str">
-        <v>EGW rubriektype.</v>
+        <v>null</v>
       </c>
       <c r="J25" t="str">
         <v>null</v>
@@ -1347,35 +1635,47 @@
       </c>
       <c r="L25" t="str">
         <v>null</v>
+      </c>
+      <c r="M25" t="str">
+        <v>null</v>
+      </c>
+      <c r="N25" t="str">
+        <v>null</v>
+      </c>
+      <c r="O25" t="str">
+        <v>null</v>
+      </c>
+      <c r="P25" t="str">
+        <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/rubriek-type/vlarem</v>
+        <v>riepr-status-type:in_dienst</v>
       </c>
       <c r="B26" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="D26" t="str">
-        <v>VLAREM</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="E26" t="str">
-        <v>VLAREM</v>
+        <v>IN_DIENST</v>
       </c>
       <c r="F26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="G26" t="str">
-        <v>null</v>
+        <v>In dienst</v>
       </c>
       <c r="H26" t="str">
-        <v>VLAREM rubriektype.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="I26" t="str">
-        <v>VLAREM rubriektype.</v>
+        <v>null</v>
       </c>
       <c r="J26" t="str">
         <v>null</v>
@@ -1385,543 +1685,173 @@
       </c>
       <c r="L26" t="str">
         <v>null</v>
+      </c>
+      <c r="M26" t="str">
+        <v>null</v>
+      </c>
+      <c r="N26" t="str">
+        <v>null</v>
+      </c>
+      <c r="O26" t="str">
+        <v>null</v>
+      </c>
+      <c r="P26" t="str">
+        <v>http://purl.org/adms/status/Completed</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k1</v>
+        <v>riepr-status-type:ontmanteld</v>
       </c>
       <c r="B27" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="D27" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="E27" t="str">
-        <v>Klasse 1</v>
+        <v>ONTMANTELD</v>
       </c>
       <c r="F27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="G27" t="str">
-        <v>null</v>
+        <v>Ontmanteld</v>
       </c>
       <c r="H27" t="str">
-        <v>Indelingsklasse voor inrichtingen met de grootste milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 1 (zwaarste procedure).</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="I27" t="str">
-        <v>Indelingsklasse voor inrichtingen met de grootste milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 1 (zwaarste procedure).</v>
+        <v>null</v>
       </c>
       <c r="J27" t="str">
         <v>null</v>
       </c>
       <c r="K27" t="str">
-        <v>VLAREM klasse 1</v>
+        <v>null</v>
       </c>
       <c r="L27" t="str">
         <v>null</v>
+      </c>
+      <c r="M27" t="str">
+        <v>null</v>
+      </c>
+      <c r="N27" t="str">
+        <v>null</v>
+      </c>
+      <c r="O27" t="str">
+        <v>null</v>
+      </c>
+      <c r="P27" t="str">
+        <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k2</v>
+        <v>riepr-status-type:tijdelijk_uit_dienst</v>
       </c>
       <c r="B28" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="D28" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="E28" t="str">
-        <v>Klasse 2</v>
+        <v>TIJDELIJK_UIT_DIENST</v>
       </c>
       <c r="F28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="G28" t="str">
-        <v>null</v>
+        <v>Tijdelijk uit dienst</v>
       </c>
       <c r="H28" t="str">
-        <v>Indelingsklasse voor inrichtingen met een middelgrote milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 2.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="I28" t="str">
-        <v>Indelingsklasse voor inrichtingen met een middelgrote milieu-impact. Voor deze activiteiten geldt een omgevingsvergunning klasse 2.</v>
+        <v>null</v>
       </c>
       <c r="J28" t="str">
         <v>null</v>
       </c>
       <c r="K28" t="str">
-        <v>VLAREM klasse 2</v>
+        <v>null</v>
       </c>
       <c r="L28" t="str">
         <v>null</v>
+      </c>
+      <c r="M28" t="str">
+        <v>null</v>
+      </c>
+      <c r="N28" t="str">
+        <v>null</v>
+      </c>
+      <c r="O28" t="str">
+        <v>null</v>
+      </c>
+      <c r="P28" t="str">
+        <v>http://purl.org/adms/status/Deprecated</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k3</v>
+        <v>riepr-status-type:voorgesteld</v>
       </c>
       <c r="B29" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="D29" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="E29" t="str">
-        <v>Klasse 3</v>
+        <v>VOORGESTELD</v>
       </c>
       <c r="F29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="G29" t="str">
-        <v>null</v>
+        <v>Voorgesteld Ontwerp</v>
       </c>
       <c r="H29" t="str">
-        <v>Indelingsklasse voor inrichtingen met een beperkte milieu-impact. Voor deze activiteiten geldt een meldingsplicht (klasse 3).</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="I29" t="str">
-        <v>Indelingsklasse voor inrichtingen met een beperkte milieu-impact. Voor deze activiteiten geldt een meldingsplicht (klasse 3).</v>
+        <v>null</v>
       </c>
       <c r="J29" t="str">
         <v>null</v>
       </c>
       <c r="K29" t="str">
-        <v>VLAREM klasse 3</v>
+        <v>null</v>
       </c>
       <c r="L29" t="str">
         <v>null</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_attributen</v>
-      </c>
-      <c r="B30" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C30" t="str">
-        <v>null</v>
-      </c>
-      <c r="D30" t="str">
-        <v>null</v>
-      </c>
-      <c r="E30" t="str">
-        <v>Emissiepunt attributen</v>
-      </c>
-      <c r="F30" t="str">
-        <v>null</v>
-      </c>
-      <c r="G30" t="str">
-        <v>null</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Een lijst die een koppeling maakt tussen soorten emissiepunten en de attributen die van toepassing zijn.</v>
-      </c>
-      <c r="I30" t="str">
-        <v>Een lijst die een koppeling maakt tussen soorten emissiepunten en de attributen die van toepassing zijn.</v>
-      </c>
-      <c r="J30" t="str">
-        <v>null</v>
-      </c>
-      <c r="K30" t="str">
-        <v>null</v>
-      </c>
-      <c r="L30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-attribuut/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-attribuut/schouw-hoogte</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
-      </c>
-      <c r="B31" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C31" t="str">
-        <v>null</v>
-      </c>
-      <c r="D31" t="str">
-        <v>null</v>
-      </c>
-      <c r="E31" t="str">
-        <v>Emissiepunt types</v>
-      </c>
-      <c r="F31" t="str">
-        <v>null</v>
-      </c>
-      <c r="G31" t="str">
-        <v>null</v>
-      </c>
-      <c r="H31" t="str">
-        <v>Een lijst van verschillende soorten emissiepunten met mogelijke opsplitsing in subtyperingen.</v>
-      </c>
-      <c r="I31" t="str">
-        <v>Een lijst van verschillende soorten emissiepunten met mogelijke opsplitsing in subtyperingen.</v>
-      </c>
-      <c r="J31" t="str">
-        <v>null</v>
-      </c>
-      <c r="K31" t="str">
-        <v>null</v>
-      </c>
-      <c r="L31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/fakkel|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/filter_type</v>
-      </c>
-      <c r="B32" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C32" t="str">
-        <v>null</v>
-      </c>
-      <c r="D32" t="str">
-        <v>null</v>
-      </c>
-      <c r="E32" t="str">
-        <v>Filter types</v>
-      </c>
-      <c r="F32" t="str">
-        <v>null</v>
-      </c>
-      <c r="G32" t="str">
-        <v>null</v>
-      </c>
-      <c r="H32" t="str">
-        <v>Een lijst van verschillende types van filters en de objecten waarop van toepassing.</v>
-      </c>
-      <c r="I32" t="str">
-        <v>Een lijst van verschillende types van filters en de objecten waarop van toepassing.</v>
-      </c>
-      <c r="J32" t="str">
-        <v>null</v>
-      </c>
-      <c r="K32" t="str">
-        <v>null</v>
-      </c>
-      <c r="L32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/filter-type/peilfilter</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
-      </c>
-      <c r="B33" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C33" t="str">
-        <v>null</v>
-      </c>
-      <c r="D33" t="str">
-        <v>null</v>
-      </c>
-      <c r="E33" t="str">
-        <v>Installatie types</v>
-      </c>
-      <c r="F33" t="str">
-        <v>null</v>
-      </c>
-      <c r="G33" t="str">
-        <v>null</v>
-      </c>
-      <c r="H33" t="str">
-        <v>Een lijst van verschillende types van installaties met eventueel subtyperingen.</v>
-      </c>
-      <c r="I33" t="str">
-        <v>Een lijst van verschillende types van installaties met eventueel subtyperingen.</v>
-      </c>
-      <c r="J33" t="str">
-        <v>null</v>
-      </c>
-      <c r="K33" t="str">
-        <v>null</v>
-      </c>
-      <c r="L33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/gpbv|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/iepr|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/oven|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/zuiveringsinstallatie</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetinstrument_type</v>
-      </c>
-      <c r="B34" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C34" t="str">
-        <v>null</v>
-      </c>
-      <c r="D34" t="str">
-        <v>null</v>
-      </c>
-      <c r="E34" t="str">
-        <v>Meetinstrument types</v>
-      </c>
-      <c r="F34" t="str">
-        <v>null</v>
-      </c>
-      <c r="G34" t="str">
-        <v>null</v>
-      </c>
-      <c r="H34" t="str">
-        <v>Een lijst van verschillende soorten meetinstrumenten.</v>
-      </c>
-      <c r="I34" t="str">
-        <v>Een lijst van verschillende soorten meetinstrumenten.</v>
-      </c>
-      <c r="J34" t="str">
-        <v>null</v>
-      </c>
-      <c r="K34" t="str">
-        <v>null</v>
-      </c>
-      <c r="L34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetinstrument-type/debietmeter</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
-      </c>
-      <c r="B35" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C35" t="str">
-        <v>null</v>
-      </c>
-      <c r="D35" t="str">
-        <v>null</v>
-      </c>
-      <c r="E35" t="str">
-        <v>Meetpunt types</v>
-      </c>
-      <c r="F35" t="str">
-        <v>null</v>
-      </c>
-      <c r="G35" t="str">
-        <v>null</v>
-      </c>
-      <c r="H35" t="str">
-        <v>Een lijst van verschillende soorten meetpunten.</v>
-      </c>
-      <c r="I35" t="str">
-        <v>Een lijst van verschillende soorten meetpunten.</v>
-      </c>
-      <c r="J35" t="str">
-        <v>null</v>
-      </c>
-      <c r="K35" t="str">
-        <v>null</v>
-      </c>
-      <c r="L35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/controle-inrichting|https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
-      </c>
-      <c r="B36" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C36" t="str">
-        <v>null</v>
-      </c>
-      <c r="D36" t="str">
-        <v>null</v>
-      </c>
-      <c r="E36" t="str">
-        <v>Onttrekkingspunt types</v>
-      </c>
-      <c r="F36" t="str">
-        <v>null</v>
-      </c>
-      <c r="G36" t="str">
-        <v>null</v>
-      </c>
-      <c r="H36" t="str">
-        <v>Een lijst van verschillende soorten onttrekkingspunten met mogelijke opsplitsing in subtyperingen.</v>
-      </c>
-      <c r="I36" t="str">
-        <v>Een lijst van verschillende soorten onttrekkingspunten met mogelijke opsplitsing in subtyperingen.</v>
-      </c>
-      <c r="J36" t="str">
-        <v>null</v>
-      </c>
-      <c r="K36" t="str">
-        <v>null</v>
-      </c>
-      <c r="L36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
-      </c>
-      <c r="B37" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C37" t="str">
-        <v>null</v>
-      </c>
-      <c r="D37" t="str">
-        <v>null</v>
-      </c>
-      <c r="E37" t="str">
-        <v>Procedure types</v>
-      </c>
-      <c r="F37" t="str">
-        <v>null</v>
-      </c>
-      <c r="G37" t="str">
-        <v>null</v>
-      </c>
-      <c r="H37" t="str">
-        <v>Een lijst van verschillende hoofdtyperingen van procedures in een procesplan.</v>
-      </c>
-      <c r="I37" t="str">
-        <v>Een lijst van verschillende hoofdtyperingen van procedures in een procesplan.</v>
-      </c>
-      <c r="J37" t="str">
-        <v>null</v>
-      </c>
-      <c r="K37" t="str">
-        <v>null</v>
-      </c>
-      <c r="L37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/meet|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/overbrenging|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verbruik|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procesvariabele_type</v>
-      </c>
-      <c r="B38" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C38" t="str">
-        <v>null</v>
-      </c>
-      <c r="D38" t="str">
-        <v>null</v>
-      </c>
-      <c r="E38" t="str">
-        <v>Proces variabele types</v>
-      </c>
-      <c r="F38" t="str">
-        <v>null</v>
-      </c>
-      <c r="G38" t="str">
-        <v>null</v>
-      </c>
-      <c r="H38" t="str">
-        <v>Een lijst die verschillende types geeft voor stoffen die aangeduid mogen worden bij bepaalde procedure types.</v>
-      </c>
-      <c r="I38" t="str">
-        <v>Een lijst die verschillende types geeft voor stoffen die aangeduid mogen worden bij bepaalde procedure types.</v>
-      </c>
-      <c r="J38" t="str">
-        <v>null</v>
-      </c>
-      <c r="K38" t="str">
-        <v>null</v>
-      </c>
-      <c r="L38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/aardgas|https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/co2|https://data.omgeving.vlaanderen.be/id/concept/riepr/procesvariabele-type/grondstof</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/rubriek_type</v>
-      </c>
-      <c r="B39" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C39" t="str">
-        <v>null</v>
-      </c>
-      <c r="D39" t="str">
-        <v>null</v>
-      </c>
-      <c r="E39" t="str">
-        <v>Rubriek types</v>
-      </c>
-      <c r="F39" t="str">
-        <v>null</v>
-      </c>
-      <c r="G39" t="str">
-        <v>null</v>
-      </c>
-      <c r="H39" t="str">
-        <v>Een typering van verschillende rubrieken (VLAREM rubriektype EGW ...).</v>
-      </c>
-      <c r="I39" t="str">
-        <v>Een typering van verschillende rubrieken (VLAREM rubriektype EGW ...).</v>
-      </c>
-      <c r="J39" t="str">
-        <v>null</v>
-      </c>
-      <c r="K39" t="str">
-        <v>null</v>
-      </c>
-      <c r="L39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/rubriek-type/egw|https://data.omgeving.vlaanderen.be/id/concept/riepr/rubriek-type/vlarem</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/vlarem-klasse</v>
-      </c>
-      <c r="B40" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C40" t="str">
-        <v>null</v>
-      </c>
-      <c r="D40" t="str">
-        <v>null</v>
-      </c>
-      <c r="E40" t="str">
-        <v>null</v>
-      </c>
-      <c r="F40" t="str">
-        <v>null</v>
-      </c>
-      <c r="G40" t="str">
-        <v>null</v>
-      </c>
-      <c r="H40" t="str">
-        <v>null</v>
-      </c>
-      <c r="I40" t="str">
-        <v>null</v>
-      </c>
-      <c r="J40" t="str">
-        <v>null</v>
-      </c>
-      <c r="K40" t="str">
-        <v>null</v>
-      </c>
-      <c r="L40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k1|https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k2|https://data.omgeving.vlaanderen.be/id/concept/vlarem-klasse/k3</v>
+      <c r="M29" t="str">
+        <v>null</v>
+      </c>
+      <c r="N29" t="str">
+        <v>null</v>
+      </c>
+      <c r="O29" t="str">
+        <v>null</v>
+      </c>
+      <c r="P29" t="str">
+        <v>http://purl.org/adms/status/UnderDevelopment</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,13 +440,13 @@
         <v>broaderTransitive</v>
       </c>
       <c r="N1" t="str">
+        <v>seeAlso</v>
+      </c>
+      <c r="O1" t="str">
         <v>hasTopConcept</v>
       </c>
-      <c r="O1" t="str">
-        <v>relevantriepr</v>
-      </c>
       <c r="P1" t="str">
-        <v>seeAlso</v>
+        <v>relevantRiepr</v>
       </c>
     </row>
     <row r="2">
@@ -781,13 +781,13 @@
         <v>null</v>
       </c>
       <c r="K8" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="L8" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="M8" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="N8" t="str">
         <v>null</v>
@@ -825,13 +825,13 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="I9" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="J9" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="K9" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="L9" t="str">
         <v>null</v>
@@ -1151,28 +1151,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
       </c>
       <c r="B16" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C16" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="D16" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="E16" t="str">
-        <v>null</v>
+        <v>DEFINITIEF_UIT_DIENST</v>
       </c>
       <c r="F16" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="G16" t="str">
-        <v>Emissiepunt eigenschappen</v>
+        <v>Definitief uit dienst</v>
       </c>
       <c r="H16" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="I16" t="str">
         <v>null</v>
@@ -1190,7 +1190,7 @@
         <v>null</v>
       </c>
       <c r="N16" t="str">
-        <v>riepr-emissiepunt-eigenschappen:schouw-diameter|riepr-emissiepunt-eigenschappen:schouw-hoogte</v>
+        <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
       <c r="O16" t="str">
         <v>null</v>
@@ -1201,28 +1201,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
       </c>
       <c r="B17" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C17" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="D17" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="E17" t="str">
-        <v>null</v>
+        <v>IN_DIENST</v>
       </c>
       <c r="F17" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="G17" t="str">
-        <v>Emissiepunt types</v>
+        <v>In dienst</v>
       </c>
       <c r="H17" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="I17" t="str">
         <v>null</v>
@@ -1240,7 +1240,7 @@
         <v>null</v>
       </c>
       <c r="N17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>http://purl.org/adms/status/Completed</v>
       </c>
       <c r="O17" t="str">
         <v>null</v>
@@ -1251,28 +1251,28 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
       </c>
       <c r="B18" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C18" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="D18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="E18" t="str">
-        <v>null</v>
+        <v>ONTMANTELD</v>
       </c>
       <c r="F18" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="G18" t="str">
-        <v>Installatie types</v>
+        <v>Ontmanteld</v>
       </c>
       <c r="H18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="I18" t="str">
         <v>null</v>
@@ -1290,7 +1290,7 @@
         <v>null</v>
       </c>
       <c r="N18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
       <c r="O18" t="str">
         <v>null</v>
@@ -1301,28 +1301,28 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
       </c>
       <c r="B19" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C19" t="str">
-        <v>null</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="D19" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="E19" t="str">
-        <v>null</v>
+        <v>TIJDELIJK_UIT_DIENST</v>
       </c>
       <c r="F19" t="str">
-        <v>null</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="G19" t="str">
-        <v>Meetpunt types</v>
+        <v>Tijdelijk uit dienst</v>
       </c>
       <c r="H19" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="I19" t="str">
         <v>null</v>
@@ -1340,7 +1340,7 @@
         <v>null</v>
       </c>
       <c r="N19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+        <v>http://purl.org/adms/status/Deprecated</v>
       </c>
       <c r="O19" t="str">
         <v>null</v>
@@ -1351,28 +1351,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
       <c r="B20" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C20" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="D20" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="E20" t="str">
-        <v>null</v>
+        <v>VOORGESTELD</v>
       </c>
       <c r="F20" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="G20" t="str">
-        <v>Onttrekkingspunt types</v>
+        <v>Voorgesteld Ontwerp</v>
       </c>
       <c r="H20" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="I20" t="str">
         <v>null</v>
@@ -1390,7 +1390,7 @@
         <v>null</v>
       </c>
       <c r="N20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+        <v>http://purl.org/adms/status/UnderDevelopment</v>
       </c>
       <c r="O20" t="str">
         <v>null</v>
@@ -1401,13 +1401,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="B21" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C21" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="D21" t="str">
         <v>null</v>
@@ -1416,10 +1416,10 @@
         <v>null</v>
       </c>
       <c r="F21" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="G21" t="str">
-        <v>Procedure types</v>
+        <v>Emissiepunt eigenschappen</v>
       </c>
       <c r="H21" t="str">
         <v>null</v>
@@ -1440,10 +1440,10 @@
         <v>null</v>
       </c>
       <c r="N21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>null</v>
       </c>
       <c r="O21" t="str">
-        <v>null</v>
+        <v>riepr-emissiepunt-eigenschappen:schouw-diameter|riepr-emissiepunt-eigenschappen:schouw-hoogte</v>
       </c>
       <c r="P21" t="str">
         <v>null</v>
@@ -1451,13 +1451,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="B22" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C22" t="str">
-        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="D22" t="str">
         <v>null</v>
@@ -1466,10 +1466,10 @@
         <v>null</v>
       </c>
       <c r="F22" t="str">
-        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="G22" t="str">
-        <v>Status types</v>
+        <v>Emissiepunt types</v>
       </c>
       <c r="H22" t="str">
         <v>null</v>
@@ -1490,10 +1490,10 @@
         <v>null</v>
       </c>
       <c r="N22" t="str">
-        <v>riepr-status-type:definitief_uit_dienst|riepr-status-type:in_dienst|riepr-status-type:ontmanteld|riepr-status-type:tijdelijk_uit_dienst|riepr-status-type:voorgesteld</v>
+        <v>null</v>
       </c>
       <c r="O22" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="P22" t="str">
         <v>null</v>
@@ -1501,28 +1501,28 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>riepr-emissiepunt-eigenschappen:schouw-diameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="B23" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C23" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="D23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="E23" t="str">
-        <v>diameter</v>
+        <v>null</v>
       </c>
       <c r="F23" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="G23" t="str">
-        <v>Diameter van de schouw</v>
+        <v>Installatie eigenschappen</v>
       </c>
       <c r="H23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="I23" t="str">
         <v>null</v>
@@ -1543,7 +1543,7 @@
         <v>null</v>
       </c>
       <c r="O23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>riepr-installatie-eigenschappen:geinstalleerd_vermogen</v>
       </c>
       <c r="P23" t="str">
         <v>null</v>
@@ -1551,28 +1551,28 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>riepr-emissiepunt-eigenschappen:schouw-hoogte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="B24" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C24" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="D24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="E24" t="str">
-        <v>hoogte</v>
+        <v>null</v>
       </c>
       <c r="F24" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="G24" t="str">
-        <v>Hoogte van de schouw</v>
+        <v>Installatie types</v>
       </c>
       <c r="H24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="I24" t="str">
         <v>null</v>
@@ -1593,7 +1593,7 @@
         <v>null</v>
       </c>
       <c r="O24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="P24" t="str">
         <v>null</v>
@@ -1601,28 +1601,28 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>riepr-status-type:definitief_uit_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="B25" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C25" t="str">
-        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="D25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>null</v>
       </c>
       <c r="E25" t="str">
-        <v>DEFINITIEF_UIT_DIENST</v>
+        <v>null</v>
       </c>
       <c r="F25" t="str">
-        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="G25" t="str">
-        <v>Definitief uit dienst</v>
+        <v>Meetpunt types</v>
       </c>
       <c r="H25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>null</v>
       </c>
       <c r="I25" t="str">
         <v>null</v>
@@ -1643,36 +1643,36 @@
         <v>null</v>
       </c>
       <c r="O25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
       </c>
       <c r="P25" t="str">
-        <v>http://purl.org/adms/status/Withdrawn</v>
+        <v>null</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>riepr-status-type:in_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="B26" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C26" t="str">
-        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="D26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>null</v>
       </c>
       <c r="E26" t="str">
-        <v>IN_DIENST</v>
+        <v>null</v>
       </c>
       <c r="F26" t="str">
-        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="G26" t="str">
-        <v>In dienst</v>
+        <v>Onttrekkingspunt types</v>
       </c>
       <c r="H26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>null</v>
       </c>
       <c r="I26" t="str">
         <v>null</v>
@@ -1693,36 +1693,36 @@
         <v>null</v>
       </c>
       <c r="O26" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
       </c>
       <c r="P26" t="str">
-        <v>http://purl.org/adms/status/Completed</v>
+        <v>null</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>riepr-status-type:ontmanteld</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="B27" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C27" t="str">
-        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+        <v>Een typering van verschillende procedures.</v>
       </c>
       <c r="D27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>null</v>
       </c>
       <c r="E27" t="str">
-        <v>ONTMANTELD</v>
+        <v>null</v>
       </c>
       <c r="F27" t="str">
-        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+        <v>Een typering van verschillende procedures.</v>
       </c>
       <c r="G27" t="str">
-        <v>Ontmanteld</v>
+        <v>Procedure types</v>
       </c>
       <c r="H27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>null</v>
       </c>
       <c r="I27" t="str">
         <v>null</v>
@@ -1743,36 +1743,36 @@
         <v>null</v>
       </c>
       <c r="O27" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
       </c>
       <c r="P27" t="str">
-        <v>http://purl.org/adms/status/Withdrawn</v>
+        <v>null</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>riepr-status-type:tijdelijk_uit_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="B28" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C28" t="str">
-        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
       <c r="D28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>null</v>
       </c>
       <c r="E28" t="str">
-        <v>TIJDELIJK_UIT_DIENST</v>
+        <v>null</v>
       </c>
       <c r="F28" t="str">
-        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
       <c r="G28" t="str">
-        <v>Tijdelijk uit dienst</v>
+        <v>Status types</v>
       </c>
       <c r="H28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>null</v>
       </c>
       <c r="I28" t="str">
         <v>null</v>
@@ -1793,36 +1793,36 @@
         <v>null</v>
       </c>
       <c r="O28" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
       <c r="P28" t="str">
-        <v>http://purl.org/adms/status/Deprecated</v>
+        <v>null</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>riepr-status-type:voorgesteld</v>
+        <v>riepr-emissiepunt-eigenschappen:schouw-diameter</v>
       </c>
       <c r="B29" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C29" t="str">
-        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+        <v>null</v>
       </c>
       <c r="D29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="E29" t="str">
-        <v>VOORGESTELD</v>
+        <v>diameter</v>
       </c>
       <c r="F29" t="str">
-        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+        <v>null</v>
       </c>
       <c r="G29" t="str">
-        <v>Voorgesteld Ontwerp</v>
+        <v>Diameter van de schouw</v>
       </c>
       <c r="H29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="I29" t="str">
         <v>null</v>
@@ -1846,12 +1846,112 @@
         <v>null</v>
       </c>
       <c r="P29" t="str">
-        <v>http://purl.org/adms/status/UnderDevelopment</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>riepr-emissiepunt-eigenschappen:schouw-hoogte</v>
+      </c>
+      <c r="B30" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C30" t="str">
+        <v>null</v>
+      </c>
+      <c r="D30" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+      </c>
+      <c r="E30" t="str">
+        <v>hoogte</v>
+      </c>
+      <c r="F30" t="str">
+        <v>null</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Hoogte van de schouw</v>
+      </c>
+      <c r="H30" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+      </c>
+      <c r="I30" t="str">
+        <v>null</v>
+      </c>
+      <c r="J30" t="str">
+        <v>null</v>
+      </c>
+      <c r="K30" t="str">
+        <v>null</v>
+      </c>
+      <c r="L30" t="str">
+        <v>null</v>
+      </c>
+      <c r="M30" t="str">
+        <v>null</v>
+      </c>
+      <c r="N30" t="str">
+        <v>null</v>
+      </c>
+      <c r="O30" t="str">
+        <v>null</v>
+      </c>
+      <c r="P30" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>riepr-installatie-eigenschappen:geinstalleerd_vermogen</v>
+      </c>
+      <c r="B31" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C31" t="str">
+        <v>null</v>
+      </c>
+      <c r="D31" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+      </c>
+      <c r="E31" t="str">
+        <v>GEINSTALLEERD_VERMOGEN</v>
+      </c>
+      <c r="F31" t="str">
+        <v>null</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Geinstalleerd vermogen</v>
+      </c>
+      <c r="H31" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+      </c>
+      <c r="I31" t="str">
+        <v>null</v>
+      </c>
+      <c r="J31" t="str">
+        <v>null</v>
+      </c>
+      <c r="K31" t="str">
+        <v>null</v>
+      </c>
+      <c r="L31" t="str">
+        <v>null</v>
+      </c>
+      <c r="M31" t="str">
+        <v>null</v>
+      </c>
+      <c r="N31" t="str">
+        <v>null</v>
+      </c>
+      <c r="O31" t="str">
+        <v>null</v>
+      </c>
+      <c r="P31" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:R34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,72 +407,78 @@
         <v>_type</v>
       </c>
       <c r="C1" t="str">
+        <v>inScheme</v>
+      </c>
+      <c r="D1" t="str">
+        <v>code</v>
+      </c>
+      <c r="E1" t="str">
+        <v>prefLabel</v>
+      </c>
+      <c r="F1" t="str">
+        <v>topConceptOf</v>
+      </c>
+      <c r="G1" t="str">
+        <v>relevantUnit</v>
+      </c>
+      <c r="H1" t="str">
+        <v>relevantDataType</v>
+      </c>
+      <c r="I1" t="str">
+        <v>relevantRiepr</v>
+      </c>
+      <c r="J1" t="str">
         <v>definition</v>
       </c>
-      <c r="D1" t="str">
-        <v>inScheme</v>
-      </c>
-      <c r="E1" t="str">
-        <v>code</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="K1" t="str">
         <v>note</v>
       </c>
-      <c r="G1" t="str">
-        <v>prefLabel</v>
-      </c>
-      <c r="H1" t="str">
-        <v>topConceptOf</v>
-      </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>narrower</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>narrowerTransitive</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>semanticRelation</v>
       </c>
-      <c r="L1" t="str">
+      <c r="O1" t="str">
         <v>broader</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>broaderTransitive</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>seeAlso</v>
       </c>
-      <c r="O1" t="str">
+      <c r="R1" t="str">
         <v>hasTopConcept</v>
-      </c>
-      <c r="P1" t="str">
-        <v>relevantRiepr</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
+        <v>http://qudt.org/vocab/unit/M</v>
       </c>
       <c r="B2" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C2" t="str">
-        <v>Een regulier emissiepunt.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>m</v>
       </c>
       <c r="E2" t="str">
-        <v>emissiepunt</v>
+        <v>Meter</v>
       </c>
       <c r="F2" t="str">
-        <v>Een regulier emissiepunt.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="G2" t="str">
-        <v>Emissiepunt</v>
+        <v>null</v>
       </c>
       <c r="H2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>null</v>
       </c>
       <c r="I2" t="str">
         <v>null</v>
@@ -496,33 +502,39 @@
         <v>null</v>
       </c>
       <c r="P2" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>null</v>
+      </c>
+      <c r="R2" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
+        <v>http://qudt.org/vocab/unit/MegaW</v>
       </c>
       <c r="B3" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C3" t="str">
-        <v>Een lozing naar water.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>MW</v>
       </c>
       <c r="E3" t="str">
-        <v>lozingspunt</v>
+        <v>Mega Watt</v>
       </c>
       <c r="F3" t="str">
-        <v>Een lozing naar water.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="G3" t="str">
-        <v>Lozingspunt</v>
+        <v>null</v>
       </c>
       <c r="H3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>null</v>
       </c>
       <c r="I3" t="str">
         <v>null</v>
@@ -546,42 +558,48 @@
         <v>null</v>
       </c>
       <c r="P3" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>null</v>
+      </c>
+      <c r="R3" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter</v>
       </c>
       <c r="B4" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C4" t="str">
-        <v>Een schoorsteen.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="D4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>diameter</v>
       </c>
       <c r="E4" t="str">
-        <v>schoorsteen</v>
+        <v>Diameter van de schouw</v>
       </c>
       <c r="F4" t="str">
-        <v>Een schoorsteen.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="G4" t="str">
-        <v>Schoorsteen</v>
+        <v>http://qudt.org/vocab/unit/M</v>
       </c>
       <c r="H4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="J4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
+        <v>null</v>
       </c>
       <c r="K4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
+        <v>null</v>
       </c>
       <c r="L4" t="str">
         <v>null</v>
@@ -596,48 +614,54 @@
         <v>null</v>
       </c>
       <c r="P4" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>null</v>
+      </c>
+      <c r="R4" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
       </c>
       <c r="B5" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C5" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="D5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>hoogte</v>
       </c>
       <c r="E5" t="str">
-        <v>schoorsteen_horizontale_uitstroom</v>
+        <v>Hoogte van de schouw</v>
       </c>
       <c r="F5" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="G5" t="str">
-        <v>Schoorsteen met horizontale uitstroom</v>
+        <v>http://qudt.org/vocab/unit/M</v>
       </c>
       <c r="H5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I5" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="J5" t="str">
         <v>null</v>
       </c>
       <c r="K5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="L5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="M5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="N5" t="str">
         <v>null</v>
@@ -646,48 +670,54 @@
         <v>null</v>
       </c>
       <c r="P5" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>null</v>
+      </c>
+      <c r="R5" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
       </c>
       <c r="B6" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C6" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D6" t="str">
+        <v>emissiepunt</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Emissiepunt</v>
+      </c>
+      <c r="F6" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
-      <c r="E6" t="str">
-        <v>schoorsteen_verticale_uitstroom</v>
-      </c>
-      <c r="F6" t="str">
-        <v>null</v>
-      </c>
       <c r="G6" t="str">
-        <v>Schoorsteen met vertikale uitstroom</v>
+        <v>null</v>
       </c>
       <c r="H6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>null</v>
       </c>
       <c r="I6" t="str">
         <v>null</v>
       </c>
       <c r="J6" t="str">
-        <v>null</v>
+        <v>Een regulier emissiepunt.</v>
       </c>
       <c r="K6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>Een regulier emissiepunt.</v>
       </c>
       <c r="L6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="M6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="N6" t="str">
         <v>null</v>
@@ -696,42 +726,48 @@
         <v>null</v>
       </c>
       <c r="P6" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>null</v>
+      </c>
+      <c r="R6" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
       </c>
       <c r="B7" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C7" t="str">
-        <v>Een schouw.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D7" t="str">
+        <v>lozingspunt</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Lozingspunt</v>
+      </c>
+      <c r="F7" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
-      <c r="E7" t="str">
-        <v>schouw</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Een schouw.</v>
-      </c>
       <c r="G7" t="str">
-        <v>Schouw</v>
+        <v>null</v>
       </c>
       <c r="H7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>null</v>
       </c>
       <c r="I7" t="str">
         <v>null</v>
       </c>
       <c r="J7" t="str">
-        <v>null</v>
+        <v>Een lozing naar water.</v>
       </c>
       <c r="K7" t="str">
-        <v>null</v>
+        <v>Een lozing naar water.</v>
       </c>
       <c r="L7" t="str">
         <v>null</v>
@@ -746,92 +782,104 @@
         <v>null</v>
       </c>
       <c r="P7" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>null</v>
+      </c>
+      <c r="R7" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="B8" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C8" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>schoorsteen</v>
       </c>
       <c r="E8" t="str">
-        <v>directe_stookinstallatie</v>
+        <v>Schoorsteen</v>
       </c>
       <c r="F8" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G8" t="str">
-        <v>Directe Stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="H8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>null</v>
       </c>
       <c r="I8" t="str">
         <v>null</v>
       </c>
       <c r="J8" t="str">
-        <v>null</v>
+        <v>Een schoorsteen.</v>
       </c>
       <c r="K8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>Een schoorsteen.</v>
       </c>
       <c r="L8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
       </c>
       <c r="M8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
       </c>
       <c r="N8" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
       </c>
       <c r="O8" t="str">
         <v>null</v>
       </c>
       <c r="P8" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>null</v>
+      </c>
+      <c r="R8" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="B9" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C9" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="E9" t="str">
-        <v>stookinstallatie</v>
+        <v>Schoorsteen met horizontale uitstroom</v>
       </c>
       <c r="F9" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G9" t="str">
-        <v>Stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="H9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>null</v>
       </c>
       <c r="I9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="J9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="K9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="L9" t="str">
         <v>null</v>
@@ -840,39 +888,45 @@
         <v>null</v>
       </c>
       <c r="N9" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="O9" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="P9" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>null</v>
+      </c>
+      <c r="R9" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
       </c>
       <c r="B10" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C10" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="E10" t="str">
-        <v>meetput</v>
+        <v>Schoorsteen met vertikale uitstroom</v>
       </c>
       <c r="F10" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G10" t="str">
-        <v>Meetput</v>
+        <v>null</v>
       </c>
       <c r="H10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>null</v>
       </c>
       <c r="I10" t="str">
         <v>null</v>
@@ -890,48 +944,54 @@
         <v>null</v>
       </c>
       <c r="N10" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="O10" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="P10" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>null</v>
+      </c>
+      <c r="R10" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="B11" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C11" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>schouw</v>
       </c>
       <c r="E11" t="str">
-        <v>grondwaterput</v>
+        <v>Schouw</v>
       </c>
       <c r="F11" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G11" t="str">
-        <v>Grondwaterput</v>
+        <v>null</v>
       </c>
       <c r="H11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>null</v>
       </c>
       <c r="I11" t="str">
         <v>null</v>
       </c>
       <c r="J11" t="str">
-        <v>null</v>
+        <v>Een schouw.</v>
       </c>
       <c r="K11" t="str">
-        <v>null</v>
+        <v>Een schouw.</v>
       </c>
       <c r="L11" t="str">
         <v>null</v>
@@ -946,36 +1006,42 @@
         <v>null</v>
       </c>
       <c r="P11" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>null</v>
+      </c>
+      <c r="R11" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen</v>
       </c>
       <c r="B12" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C12" t="str">
-        <v>De procedure emissie via een emissiepunt.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="D12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>GEINSTALLEERD_VERMOGEN</v>
       </c>
       <c r="E12" t="str">
-        <v>EMISSIE</v>
+        <v>Geinstalleerd vermogen</v>
       </c>
       <c r="F12" t="str">
-        <v>De procedure emissie via een emissiepunt.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="G12" t="str">
-        <v>Emissie</v>
+        <v>http://qudt.org/vocab/unit/MegaW</v>
       </c>
       <c r="H12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I12" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="J12" t="str">
         <v>null</v>
@@ -996,33 +1062,39 @@
         <v>null</v>
       </c>
       <c r="P12" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>null</v>
+      </c>
+      <c r="R12" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="B13" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C13" t="str">
-        <v>De procedure onttrekking via een onttrekingspunt.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>directe_stookinstallatie</v>
       </c>
       <c r="E13" t="str">
-        <v>ONTTREKKING</v>
+        <v>Directe Stookinstallatie</v>
       </c>
       <c r="F13" t="str">
-        <v>De procedure onttrekking via een onttrekingspunt.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G13" t="str">
-        <v>Onttrekking</v>
+        <v>null</v>
       </c>
       <c r="H13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>null</v>
       </c>
       <c r="I13" t="str">
         <v>null</v>
@@ -1040,39 +1112,45 @@
         <v>null</v>
       </c>
       <c r="N13" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="O13" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="P13" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>null</v>
+      </c>
+      <c r="R13" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="B14" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C14" t="str">
-        <v>De procedure transport tussen twee processen.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>stookinstallatie</v>
       </c>
       <c r="E14" t="str">
-        <v>TRANSPORT</v>
+        <v>Stookinstallatie</v>
       </c>
       <c r="F14" t="str">
-        <v>De procedure transport tussen twee processen.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G14" t="str">
-        <v>Transport</v>
+        <v>null</v>
       </c>
       <c r="H14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>null</v>
       </c>
       <c r="I14" t="str">
         <v>null</v>
@@ -1084,45 +1162,51 @@
         <v>null</v>
       </c>
       <c r="L14" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="M14" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="N14" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="O14" t="str">
         <v>null</v>
       </c>
       <c r="P14" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>null</v>
+      </c>
+      <c r="R14" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
       </c>
       <c r="B15" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C15" t="str">
-        <v>De procedure verwerking door een installatie.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="D15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>meetput</v>
       </c>
       <c r="E15" t="str">
-        <v>VERWERKING</v>
+        <v>Meetput</v>
       </c>
       <c r="F15" t="str">
-        <v>De procedure verwerking door een installatie.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="G15" t="str">
-        <v>Verwerking</v>
+        <v>null</v>
       </c>
       <c r="H15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>null</v>
       </c>
       <c r="I15" t="str">
         <v>null</v>
@@ -1146,33 +1230,39 @@
         <v>null</v>
       </c>
       <c r="P15" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>null</v>
+      </c>
+      <c r="R15" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
       </c>
       <c r="B16" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C16" t="str">
-        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="D16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>grondwaterput</v>
       </c>
       <c r="E16" t="str">
-        <v>DEFINITIEF_UIT_DIENST</v>
+        <v>Grondwaterput</v>
       </c>
       <c r="F16" t="str">
-        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="G16" t="str">
-        <v>Definitief uit dienst</v>
+        <v>null</v>
       </c>
       <c r="H16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>null</v>
       </c>
       <c r="I16" t="str">
         <v>null</v>
@@ -1190,48 +1280,54 @@
         <v>null</v>
       </c>
       <c r="N16" t="str">
-        <v>http://purl.org/adms/status/Withdrawn</v>
+        <v>null</v>
       </c>
       <c r="O16" t="str">
         <v>null</v>
       </c>
       <c r="P16" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>null</v>
+      </c>
+      <c r="R16" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
       </c>
       <c r="B17" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C17" t="str">
-        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>EMISSIE</v>
       </c>
       <c r="E17" t="str">
-        <v>IN_DIENST</v>
+        <v>Emissie</v>
       </c>
       <c r="F17" t="str">
-        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G17" t="str">
-        <v>In dienst</v>
+        <v>null</v>
       </c>
       <c r="H17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I17" t="str">
         <v>null</v>
       </c>
       <c r="J17" t="str">
-        <v>null</v>
+        <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="K17" t="str">
-        <v>null</v>
+        <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="L17" t="str">
         <v>null</v>
@@ -1240,48 +1336,54 @@
         <v>null</v>
       </c>
       <c r="N17" t="str">
-        <v>http://purl.org/adms/status/Completed</v>
+        <v>null</v>
       </c>
       <c r="O17" t="str">
         <v>null</v>
       </c>
       <c r="P17" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>null</v>
+      </c>
+      <c r="R17" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking</v>
       </c>
       <c r="B18" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C18" t="str">
-        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>ONTTREKKING</v>
       </c>
       <c r="E18" t="str">
-        <v>ONTMANTELD</v>
+        <v>Onttrekking</v>
       </c>
       <c r="F18" t="str">
-        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G18" t="str">
-        <v>Ontmanteld</v>
+        <v>null</v>
       </c>
       <c r="H18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I18" t="str">
         <v>null</v>
       </c>
       <c r="J18" t="str">
-        <v>null</v>
+        <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="K18" t="str">
-        <v>null</v>
+        <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="L18" t="str">
         <v>null</v>
@@ -1290,48 +1392,54 @@
         <v>null</v>
       </c>
       <c r="N18" t="str">
-        <v>http://purl.org/adms/status/Withdrawn</v>
+        <v>null</v>
       </c>
       <c r="O18" t="str">
         <v>null</v>
       </c>
       <c r="P18" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>null</v>
+      </c>
+      <c r="R18" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport</v>
       </c>
       <c r="B19" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C19" t="str">
-        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>TRANSPORT</v>
       </c>
       <c r="E19" t="str">
-        <v>TIJDELIJK_UIT_DIENST</v>
+        <v>Transport</v>
       </c>
       <c r="F19" t="str">
-        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G19" t="str">
-        <v>Tijdelijk uit dienst</v>
+        <v>null</v>
       </c>
       <c r="H19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I19" t="str">
         <v>null</v>
       </c>
       <c r="J19" t="str">
-        <v>null</v>
+        <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="K19" t="str">
-        <v>null</v>
+        <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="L19" t="str">
         <v>null</v>
@@ -1340,48 +1448,54 @@
         <v>null</v>
       </c>
       <c r="N19" t="str">
-        <v>http://purl.org/adms/status/Deprecated</v>
+        <v>null</v>
       </c>
       <c r="O19" t="str">
         <v>null</v>
       </c>
       <c r="P19" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>null</v>
+      </c>
+      <c r="R19" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
       </c>
       <c r="B20" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C20" t="str">
-        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>VERWERKING</v>
       </c>
       <c r="E20" t="str">
-        <v>VOORGESTELD</v>
+        <v>Verwerking</v>
       </c>
       <c r="F20" t="str">
-        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G20" t="str">
-        <v>Voorgesteld Ontwerp</v>
+        <v>null</v>
       </c>
       <c r="H20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I20" t="str">
         <v>null</v>
       </c>
       <c r="J20" t="str">
-        <v>null</v>
+        <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="K20" t="str">
-        <v>null</v>
+        <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="L20" t="str">
         <v>null</v>
@@ -1390,48 +1504,54 @@
         <v>null</v>
       </c>
       <c r="N20" t="str">
-        <v>http://purl.org/adms/status/UnderDevelopment</v>
+        <v>null</v>
       </c>
       <c r="O20" t="str">
         <v>null</v>
       </c>
       <c r="P20" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>null</v>
+      </c>
+      <c r="R20" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
       </c>
       <c r="B21" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C21" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D21" t="str">
-        <v>null</v>
+        <v>DEFINITIEF_UIT_DIENST</v>
       </c>
       <c r="E21" t="str">
-        <v>null</v>
+        <v>Definitief uit dienst</v>
       </c>
       <c r="F21" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G21" t="str">
-        <v>Emissiepunt eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="H21" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I21" t="str">
         <v>null</v>
       </c>
       <c r="J21" t="str">
-        <v>null</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="K21" t="str">
-        <v>null</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="L21" t="str">
         <v>null</v>
@@ -1443,45 +1563,51 @@
         <v>null</v>
       </c>
       <c r="O21" t="str">
-        <v>riepr-emissiepunt-eigenschappen:schouw-diameter|riepr-emissiepunt-eigenschappen:schouw-hoogte</v>
+        <v>null</v>
       </c>
       <c r="P21" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>http://purl.org/adms/status/Withdrawn</v>
+      </c>
+      <c r="R21" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
       </c>
       <c r="B22" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C22" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D22" t="str">
-        <v>null</v>
+        <v>IN_DIENST</v>
       </c>
       <c r="E22" t="str">
-        <v>null</v>
+        <v>In dienst</v>
       </c>
       <c r="F22" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G22" t="str">
-        <v>Emissiepunt types</v>
+        <v>null</v>
       </c>
       <c r="H22" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I22" t="str">
         <v>null</v>
       </c>
       <c r="J22" t="str">
-        <v>null</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="K22" t="str">
-        <v>null</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="L22" t="str">
         <v>null</v>
@@ -1493,45 +1619,51 @@
         <v>null</v>
       </c>
       <c r="O22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>null</v>
       </c>
       <c r="P22" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>http://purl.org/adms/status/Completed</v>
+      </c>
+      <c r="R22" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
       </c>
       <c r="B23" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C23" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D23" t="str">
-        <v>null</v>
+        <v>ONTMANTELD</v>
       </c>
       <c r="E23" t="str">
-        <v>null</v>
+        <v>Ontmanteld</v>
       </c>
       <c r="F23" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G23" t="str">
-        <v>Installatie eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="H23" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I23" t="str">
         <v>null</v>
       </c>
       <c r="J23" t="str">
-        <v>null</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="K23" t="str">
-        <v>null</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="L23" t="str">
         <v>null</v>
@@ -1543,45 +1675,51 @@
         <v>null</v>
       </c>
       <c r="O23" t="str">
-        <v>riepr-installatie-eigenschappen:geinstalleerd_vermogen</v>
+        <v>null</v>
       </c>
       <c r="P23" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>http://purl.org/adms/status/Withdrawn</v>
+      </c>
+      <c r="R23" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
       </c>
       <c r="B24" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C24" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D24" t="str">
-        <v>null</v>
+        <v>TIJDELIJK_UIT_DIENST</v>
       </c>
       <c r="E24" t="str">
-        <v>null</v>
+        <v>Tijdelijk uit dienst</v>
       </c>
       <c r="F24" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G24" t="str">
-        <v>Installatie types</v>
+        <v>null</v>
       </c>
       <c r="H24" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I24" t="str">
         <v>null</v>
       </c>
       <c r="J24" t="str">
-        <v>null</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="K24" t="str">
-        <v>null</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="L24" t="str">
         <v>null</v>
@@ -1593,45 +1731,51 @@
         <v>null</v>
       </c>
       <c r="O24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="P24" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>http://purl.org/adms/status/Deprecated</v>
+      </c>
+      <c r="R24" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
       <c r="B25" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D25" t="str">
-        <v>null</v>
+        <v>VOORGESTELD</v>
       </c>
       <c r="E25" t="str">
-        <v>null</v>
+        <v>Voorgesteld Ontwerp</v>
       </c>
       <c r="F25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G25" t="str">
-        <v>Meetpunt types</v>
+        <v>null</v>
       </c>
       <c r="H25" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I25" t="str">
         <v>null</v>
       </c>
       <c r="J25" t="str">
-        <v>null</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="K25" t="str">
-        <v>null</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="L25" t="str">
         <v>null</v>
@@ -1643,21 +1787,27 @@
         <v>null</v>
       </c>
       <c r="O25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+        <v>null</v>
       </c>
       <c r="P25" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>http://purl.org/adms/status/UnderDevelopment</v>
+      </c>
+      <c r="R25" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="B26" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C26" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>null</v>
       </c>
       <c r="D26" t="str">
         <v>null</v>
@@ -1666,10 +1816,10 @@
         <v>null</v>
       </c>
       <c r="F26" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>null</v>
       </c>
       <c r="G26" t="str">
-        <v>Onttrekkingspunt types</v>
+        <v>null</v>
       </c>
       <c r="H26" t="str">
         <v>null</v>
@@ -1693,33 +1843,39 @@
         <v>null</v>
       </c>
       <c r="O26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+        <v>null</v>
       </c>
       <c r="P26" t="str">
         <v>null</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>null</v>
+      </c>
+      <c r="R26" t="str">
+        <v>http://qudt.org/vocab/unit/M|http://qudt.org/vocab/unit/MegaW</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="B27" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C27" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>null</v>
       </c>
       <c r="D27" t="str">
         <v>null</v>
       </c>
       <c r="E27" t="str">
-        <v>null</v>
+        <v>Emissiepunt eigenschappen</v>
       </c>
       <c r="F27" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>null</v>
       </c>
       <c r="G27" t="str">
-        <v>Procedure types</v>
+        <v>null</v>
       </c>
       <c r="H27" t="str">
         <v>null</v>
@@ -1728,10 +1884,10 @@
         <v>null</v>
       </c>
       <c r="J27" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="K27" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="L27" t="str">
         <v>null</v>
@@ -1743,33 +1899,39 @@
         <v>null</v>
       </c>
       <c r="O27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>null</v>
       </c>
       <c r="P27" t="str">
         <v>null</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>null</v>
+      </c>
+      <c r="R27" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="B28" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C28" t="str">
-        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
+        <v>null</v>
       </c>
       <c r="D28" t="str">
         <v>null</v>
       </c>
       <c r="E28" t="str">
-        <v>null</v>
+        <v>Emissiepunt types</v>
       </c>
       <c r="F28" t="str">
-        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
+        <v>null</v>
       </c>
       <c r="G28" t="str">
-        <v>Status types</v>
+        <v>null</v>
       </c>
       <c r="H28" t="str">
         <v>null</v>
@@ -1778,10 +1940,10 @@
         <v>null</v>
       </c>
       <c r="J28" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="K28" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="L28" t="str">
         <v>null</v>
@@ -1793,45 +1955,51 @@
         <v>null</v>
       </c>
       <c r="O28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
+        <v>null</v>
       </c>
       <c r="P28" t="str">
         <v>null</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>null</v>
+      </c>
+      <c r="R28" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>riepr-emissiepunt-eigenschappen:schouw-diameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="B29" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C29" t="str">
         <v>null</v>
       </c>
       <c r="D29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="E29" t="str">
-        <v>diameter</v>
+        <v>Installatie eigenschappen</v>
       </c>
       <c r="F29" t="str">
         <v>null</v>
       </c>
       <c r="G29" t="str">
-        <v>Diameter van de schouw</v>
+        <v>null</v>
       </c>
       <c r="H29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="I29" t="str">
         <v>null</v>
       </c>
       <c r="J29" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="K29" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="L29" t="str">
         <v>null</v>
@@ -1846,42 +2014,48 @@
         <v>null</v>
       </c>
       <c r="P29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>null</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>null</v>
+      </c>
+      <c r="R29" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>riepr-emissiepunt-eigenschappen:schouw-hoogte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="B30" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C30" t="str">
         <v>null</v>
       </c>
       <c r="D30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="E30" t="str">
-        <v>hoogte</v>
+        <v>Installatie types</v>
       </c>
       <c r="F30" t="str">
         <v>null</v>
       </c>
       <c r="G30" t="str">
-        <v>Hoogte van de schouw</v>
+        <v>null</v>
       </c>
       <c r="H30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="I30" t="str">
         <v>null</v>
       </c>
       <c r="J30" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="K30" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="L30" t="str">
         <v>null</v>
@@ -1896,33 +2070,39 @@
         <v>null</v>
       </c>
       <c r="P30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>null</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>null</v>
+      </c>
+      <c r="R30" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>riepr-installatie-eigenschappen:geinstalleerd_vermogen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="B31" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C31" t="str">
         <v>null</v>
       </c>
       <c r="D31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="E31" t="str">
-        <v>GEINSTALLEERD_VERMOGEN</v>
+        <v>Meetpunt types</v>
       </c>
       <c r="F31" t="str">
         <v>null</v>
       </c>
       <c r="G31" t="str">
-        <v>Geinstalleerd vermogen</v>
+        <v>null</v>
       </c>
       <c r="H31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="I31" t="str">
         <v>null</v>
@@ -1946,12 +2126,186 @@
         <v>null</v>
       </c>
       <c r="P31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>null</v>
+      </c>
+      <c r="R31" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+      </c>
+      <c r="B32" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C32" t="str">
+        <v>null</v>
+      </c>
+      <c r="D32" t="str">
+        <v>null</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Onttrekkingspunt types</v>
+      </c>
+      <c r="F32" t="str">
+        <v>null</v>
+      </c>
+      <c r="G32" t="str">
+        <v>null</v>
+      </c>
+      <c r="H32" t="str">
+        <v>null</v>
+      </c>
+      <c r="I32" t="str">
+        <v>null</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+      </c>
+      <c r="L32" t="str">
+        <v>null</v>
+      </c>
+      <c r="M32" t="str">
+        <v>null</v>
+      </c>
+      <c r="N32" t="str">
+        <v>null</v>
+      </c>
+      <c r="O32" t="str">
+        <v>null</v>
+      </c>
+      <c r="P32" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>null</v>
+      </c>
+      <c r="R32" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+      </c>
+      <c r="B33" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C33" t="str">
+        <v>null</v>
+      </c>
+      <c r="D33" t="str">
+        <v>null</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Procedure types</v>
+      </c>
+      <c r="F33" t="str">
+        <v>null</v>
+      </c>
+      <c r="G33" t="str">
+        <v>null</v>
+      </c>
+      <c r="H33" t="str">
+        <v>null</v>
+      </c>
+      <c r="I33" t="str">
+        <v>null</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Een typering van verschillende procedures.</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Een typering van verschillende procedures.</v>
+      </c>
+      <c r="L33" t="str">
+        <v>null</v>
+      </c>
+      <c r="M33" t="str">
+        <v>null</v>
+      </c>
+      <c r="N33" t="str">
+        <v>null</v>
+      </c>
+      <c r="O33" t="str">
+        <v>null</v>
+      </c>
+      <c r="P33" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>null</v>
+      </c>
+      <c r="R33" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+      </c>
+      <c r="B34" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C34" t="str">
+        <v>null</v>
+      </c>
+      <c r="D34" t="str">
+        <v>null</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Status types</v>
+      </c>
+      <c r="F34" t="str">
+        <v>null</v>
+      </c>
+      <c r="G34" t="str">
+        <v>null</v>
+      </c>
+      <c r="H34" t="str">
+        <v>null</v>
+      </c>
+      <c r="I34" t="str">
+        <v>null</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
+      </c>
+      <c r="L34" t="str">
+        <v>null</v>
+      </c>
+      <c r="M34" t="str">
+        <v>null</v>
+      </c>
+      <c r="N34" t="str">
+        <v>null</v>
+      </c>
+      <c r="O34" t="str">
+        <v>null</v>
+      </c>
+      <c r="P34" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>null</v>
+      </c>
+      <c r="R34" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R34"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:S45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,15 +449,18 @@
         <v>broaderTransitive</v>
       </c>
       <c r="Q1" t="str">
+        <v>parameterDimensie</v>
+      </c>
+      <c r="R1" t="str">
         <v>seeAlso</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>hasTopConcept</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>http://qudt.org/vocab/unit/M</v>
+        <v>http://qudt.org/vocab/unit/DEG_C</v>
       </c>
       <c r="B2" t="str">
         <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -466,10 +469,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D2" t="str">
-        <v>m</v>
+        <v>°C</v>
       </c>
       <c r="E2" t="str">
-        <v>Meter</v>
+        <v>Graden celcius</v>
       </c>
       <c r="F2" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
@@ -510,10 +513,13 @@
       <c r="R2" t="str">
         <v>null</v>
       </c>
+      <c r="S2" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>http://qudt.org/vocab/unit/MegaW</v>
+        <v>http://qudt.org/vocab/unit/K</v>
       </c>
       <c r="B3" t="str">
         <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -522,10 +528,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D3" t="str">
-        <v>MW</v>
+        <v>K</v>
       </c>
       <c r="E3" t="str">
-        <v>Mega Watt</v>
+        <v>Kelvin</v>
       </c>
       <c r="F3" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
@@ -566,34 +572,37 @@
       <c r="R3" t="str">
         <v>null</v>
       </c>
+      <c r="S3" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter</v>
+        <v>http://qudt.org/vocab/unit/M</v>
       </c>
       <c r="B4" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D4" t="str">
-        <v>diameter</v>
+        <v>m</v>
       </c>
       <c r="E4" t="str">
-        <v>Diameter van de schouw</v>
+        <v>Meter</v>
       </c>
       <c r="F4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="G4" t="str">
-        <v>http://qudt.org/vocab/unit/M</v>
+        <v>null</v>
       </c>
       <c r="H4" t="str">
-        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
+        <v>null</v>
       </c>
       <c r="I4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>null</v>
       </c>
       <c r="J4" t="str">
         <v>null</v>
@@ -620,36 +629,39 @@
         <v>null</v>
       </c>
       <c r="R4" t="str">
+        <v>null</v>
+      </c>
+      <c r="S4" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
+        <v>http://qudt.org/vocab/unit/MegaW</v>
       </c>
       <c r="B5" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D5" t="str">
-        <v>hoogte</v>
+        <v>MW</v>
       </c>
       <c r="E5" t="str">
-        <v>Hoogte van de schouw</v>
+        <v>Mega Watt</v>
       </c>
       <c r="F5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="G5" t="str">
-        <v>http://qudt.org/vocab/unit/M</v>
+        <v>null</v>
       </c>
       <c r="H5" t="str">
-        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
+        <v>null</v>
       </c>
       <c r="I5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>null</v>
       </c>
       <c r="J5" t="str">
         <v>null</v>
@@ -676,27 +688,30 @@
         <v>null</v>
       </c>
       <c r="R5" t="str">
+        <v>null</v>
+      </c>
+      <c r="S5" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
+        <v>http://qudt.org/vocab/unit/MicroGM-PER-L</v>
       </c>
       <c r="B6" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D6" t="str">
-        <v>emissiepunt</v>
+        <v>µg/l</v>
       </c>
       <c r="E6" t="str">
-        <v>Emissiepunt</v>
+        <v>Microgram per liter</v>
       </c>
       <c r="F6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="G6" t="str">
         <v>null</v>
@@ -708,10 +723,10 @@
         <v>null</v>
       </c>
       <c r="J6" t="str">
-        <v>Een regulier emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="K6" t="str">
-        <v>Een regulier emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="L6" t="str">
         <v>null</v>
@@ -732,27 +747,30 @@
         <v>null</v>
       </c>
       <c r="R6" t="str">
+        <v>null</v>
+      </c>
+      <c r="S6" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
+        <v>http://qudt.org/vocab/unit/MilliGM-PER-L</v>
       </c>
       <c r="B7" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D7" t="str">
-        <v>lozingspunt</v>
+        <v>mg/l</v>
       </c>
       <c r="E7" t="str">
-        <v>Lozingspunt</v>
+        <v>Milligram per liter</v>
       </c>
       <c r="F7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="G7" t="str">
         <v>null</v>
@@ -764,10 +782,10 @@
         <v>null</v>
       </c>
       <c r="J7" t="str">
-        <v>Een lozing naar water.</v>
+        <v>null</v>
       </c>
       <c r="K7" t="str">
-        <v>Een lozing naar water.</v>
+        <v>null</v>
       </c>
       <c r="L7" t="str">
         <v>null</v>
@@ -788,27 +806,30 @@
         <v>null</v>
       </c>
       <c r="R7" t="str">
+        <v>null</v>
+      </c>
+      <c r="S7" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>http://qudt.org/vocab/unit/NanoGM-PER-L</v>
       </c>
       <c r="B8" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D8" t="str">
-        <v>schoorsteen</v>
+        <v>ng/l</v>
       </c>
       <c r="E8" t="str">
-        <v>Schoorsteen</v>
+        <v>Nanogram per liter</v>
       </c>
       <c r="F8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="G8" t="str">
         <v>null</v>
@@ -820,19 +841,19 @@
         <v>null</v>
       </c>
       <c r="J8" t="str">
-        <v>Een schoorsteen.</v>
+        <v>null</v>
       </c>
       <c r="K8" t="str">
-        <v>Een schoorsteen.</v>
+        <v>null</v>
       </c>
       <c r="L8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
+        <v>null</v>
       </c>
       <c r="M8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
+        <v>null</v>
       </c>
       <c r="N8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
+        <v>null</v>
       </c>
       <c r="O8" t="str">
         <v>null</v>
@@ -844,27 +865,30 @@
         <v>null</v>
       </c>
       <c r="R8" t="str">
+        <v>null</v>
+      </c>
+      <c r="S8" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom</v>
+        <v>http://qudt.org/vocab/unit/PERCENT</v>
       </c>
       <c r="B9" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D9" t="str">
-        <v>schoorsteen_horizontale_uitstroom</v>
+        <v>%</v>
       </c>
       <c r="E9" t="str">
-        <v>Schoorsteen met horizontale uitstroom</v>
+        <v>Pcent</v>
       </c>
       <c r="F9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="G9" t="str">
         <v>null</v>
@@ -888,39 +912,42 @@
         <v>null</v>
       </c>
       <c r="N9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="O9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="P9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="Q9" t="str">
         <v>null</v>
       </c>
       <c r="R9" t="str">
+        <v>null</v>
+      </c>
+      <c r="S9" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
+        <v>http://qudt.org/vocab/unit/PPB</v>
       </c>
       <c r="B10" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D10" t="str">
-        <v>schoorsteen_verticale_uitstroom</v>
+        <v>PPB</v>
       </c>
       <c r="E10" t="str">
-        <v>Schoorsteen met vertikale uitstroom</v>
+        <v>PB</v>
       </c>
       <c r="F10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="G10" t="str">
         <v>null</v>
@@ -944,39 +971,42 @@
         <v>null</v>
       </c>
       <c r="N10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="O10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="P10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="Q10" t="str">
         <v>null</v>
       </c>
       <c r="R10" t="str">
+        <v>null</v>
+      </c>
+      <c r="S10" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>http://qudt.org/vocab/unit/PPM</v>
       </c>
       <c r="B11" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://qudt.org/schema/qudt/Unit|http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="D11" t="str">
-        <v>schouw</v>
+        <v>PPM</v>
       </c>
       <c r="E11" t="str">
-        <v>Schouw</v>
+        <v>PPM</v>
       </c>
       <c r="F11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="G11" t="str">
         <v>null</v>
@@ -988,10 +1018,10 @@
         <v>null</v>
       </c>
       <c r="J11" t="str">
-        <v>Een schouw.</v>
+        <v>null</v>
       </c>
       <c r="K11" t="str">
-        <v>Een schouw.</v>
+        <v>null</v>
       </c>
       <c r="L11" t="str">
         <v>null</v>
@@ -1012,36 +1042,39 @@
         <v>null</v>
       </c>
       <c r="R11" t="str">
+        <v>null</v>
+      </c>
+      <c r="S11" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter</v>
       </c>
       <c r="B12" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="D12" t="str">
-        <v>GEINSTALLEERD_VERMOGEN</v>
+        <v>diameter</v>
       </c>
       <c r="E12" t="str">
-        <v>Geinstalleerd vermogen</v>
+        <v>Diameter van de schouw</v>
       </c>
       <c r="F12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="G12" t="str">
-        <v>http://qudt.org/vocab/unit/MegaW</v>
+        <v>http://qudt.org/vocab/unit/M</v>
       </c>
       <c r="H12" t="str">
         <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="J12" t="str">
         <v>null</v>
@@ -1068,36 +1101,39 @@
         <v>null</v>
       </c>
       <c r="R12" t="str">
+        <v>null</v>
+      </c>
+      <c r="S12" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
       </c>
       <c r="B13" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="D13" t="str">
-        <v>directe_stookinstallatie</v>
+        <v>hoogte</v>
       </c>
       <c r="E13" t="str">
-        <v>Directe Stookinstallatie</v>
+        <v>Hoogte van de schouw</v>
       </c>
       <c r="F13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="G13" t="str">
-        <v>null</v>
+        <v>http://qudt.org/vocab/unit/M</v>
       </c>
       <c r="H13" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I13" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="J13" t="str">
         <v>null</v>
@@ -1112,39 +1148,42 @@
         <v>null</v>
       </c>
       <c r="N13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="O13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="P13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="Q13" t="str">
         <v>null</v>
       </c>
       <c r="R13" t="str">
+        <v>null</v>
+      </c>
+      <c r="S13" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
       </c>
       <c r="B14" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D14" t="str">
-        <v>stookinstallatie</v>
+        <v>emissiepunt</v>
       </c>
       <c r="E14" t="str">
-        <v>Stookinstallatie</v>
+        <v>Emissiepunt</v>
       </c>
       <c r="F14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G14" t="str">
         <v>null</v>
@@ -1156,19 +1195,19 @@
         <v>null</v>
       </c>
       <c r="J14" t="str">
-        <v>null</v>
+        <v>Een regulier emissiepunt.</v>
       </c>
       <c r="K14" t="str">
-        <v>null</v>
+        <v>Een regulier emissiepunt.</v>
       </c>
       <c r="L14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="M14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="N14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="O14" t="str">
         <v>null</v>
@@ -1180,27 +1219,30 @@
         <v>null</v>
       </c>
       <c r="R14" t="str">
+        <v>null</v>
+      </c>
+      <c r="S14" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
       </c>
       <c r="B15" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D15" t="str">
-        <v>meetput</v>
+        <v>lozingspunt</v>
       </c>
       <c r="E15" t="str">
-        <v>Meetput</v>
+        <v>Lozingspunt</v>
       </c>
       <c r="F15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G15" t="str">
         <v>null</v>
@@ -1212,10 +1254,10 @@
         <v>null</v>
       </c>
       <c r="J15" t="str">
-        <v>null</v>
+        <v>Een lozing naar water.</v>
       </c>
       <c r="K15" t="str">
-        <v>null</v>
+        <v>Een lozing naar water.</v>
       </c>
       <c r="L15" t="str">
         <v>null</v>
@@ -1236,27 +1278,30 @@
         <v>null</v>
       </c>
       <c r="R15" t="str">
+        <v>null</v>
+      </c>
+      <c r="S15" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="B16" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D16" t="str">
-        <v>grondwaterput</v>
+        <v>schoorsteen</v>
       </c>
       <c r="E16" t="str">
-        <v>Grondwaterput</v>
+        <v>Schoorsteen</v>
       </c>
       <c r="F16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G16" t="str">
         <v>null</v>
@@ -1268,19 +1313,19 @@
         <v>null</v>
       </c>
       <c r="J16" t="str">
-        <v>null</v>
+        <v>Een schoorsteen.</v>
       </c>
       <c r="K16" t="str">
-        <v>null</v>
+        <v>Een schoorsteen.</v>
       </c>
       <c r="L16" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="M16" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="N16" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="O16" t="str">
         <v>null</v>
@@ -1292,42 +1337,45 @@
         <v>null</v>
       </c>
       <c r="R16" t="str">
+        <v>null</v>
+      </c>
+      <c r="S16" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="B17" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D17" t="str">
-        <v>EMISSIE</v>
+        <v>schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="E17" t="str">
-        <v>Emissie</v>
+        <v>Schoorsteen met horizontale uitstroom</v>
       </c>
       <c r="F17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G17" t="str">
         <v>null</v>
       </c>
       <c r="H17" t="str">
-        <v>http://www.w3.org/ns/sosa/Procedure</v>
+        <v>null</v>
       </c>
       <c r="I17" t="str">
         <v>null</v>
       </c>
       <c r="J17" t="str">
-        <v>De procedure emissie via een emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="K17" t="str">
-        <v>De procedure emissie via een emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="L17" t="str">
         <v>null</v>
@@ -1336,54 +1384,57 @@
         <v>null</v>
       </c>
       <c r="N17" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="O17" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="P17" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="Q17" t="str">
         <v>null</v>
       </c>
       <c r="R17" t="str">
+        <v>null</v>
+      </c>
+      <c r="S17" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="B18" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D18" t="str">
-        <v>ONTTREKKING</v>
+        <v>schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="E18" t="str">
-        <v>Onttrekking</v>
+        <v>Schoorsteen met verticale uitstroom</v>
       </c>
       <c r="F18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G18" t="str">
         <v>null</v>
       </c>
       <c r="H18" t="str">
-        <v>http://www.w3.org/ns/sosa/Procedure</v>
+        <v>null</v>
       </c>
       <c r="I18" t="str">
         <v>null</v>
       </c>
       <c r="J18" t="str">
-        <v>De procedure onttrekking via een onttrekingspunt.</v>
+        <v>null</v>
       </c>
       <c r="K18" t="str">
-        <v>De procedure onttrekking via een onttrekingspunt.</v>
+        <v>null</v>
       </c>
       <c r="L18" t="str">
         <v>null</v>
@@ -1392,54 +1443,57 @@
         <v>null</v>
       </c>
       <c r="N18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="O18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="P18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="Q18" t="str">
         <v>null</v>
       </c>
       <c r="R18" t="str">
+        <v>null</v>
+      </c>
+      <c r="S18" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="B19" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D19" t="str">
-        <v>TRANSPORT</v>
+        <v>schouw</v>
       </c>
       <c r="E19" t="str">
-        <v>Transport</v>
+        <v>Schouw</v>
       </c>
       <c r="F19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G19" t="str">
         <v>null</v>
       </c>
       <c r="H19" t="str">
-        <v>http://www.w3.org/ns/sosa/Procedure</v>
+        <v>null</v>
       </c>
       <c r="I19" t="str">
         <v>null</v>
       </c>
       <c r="J19" t="str">
-        <v>De procedure transport tussen twee processen.</v>
+        <v>Een schouw.</v>
       </c>
       <c r="K19" t="str">
-        <v>De procedure transport tussen twee processen.</v>
+        <v>Een schouw.</v>
       </c>
       <c r="L19" t="str">
         <v>null</v>
@@ -1460,42 +1514,45 @@
         <v>null</v>
       </c>
       <c r="R19" t="str">
+        <v>null</v>
+      </c>
+      <c r="S19" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen</v>
       </c>
       <c r="B20" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="D20" t="str">
-        <v>VERWERKING</v>
+        <v>GEINSTALLEERD_VERMOGEN</v>
       </c>
       <c r="E20" t="str">
-        <v>Verwerking</v>
+        <v>Geinstalleerd vermogen</v>
       </c>
       <c r="F20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="G20" t="str">
-        <v>null</v>
+        <v>http://qudt.org/vocab/unit/MegaW</v>
       </c>
       <c r="H20" t="str">
-        <v>http://www.w3.org/ns/sosa/Procedure</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I20" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="J20" t="str">
-        <v>De procedure verwerking door een installatie.</v>
+        <v>null</v>
       </c>
       <c r="K20" t="str">
-        <v>De procedure verwerking door een installatie.</v>
+        <v>null</v>
       </c>
       <c r="L20" t="str">
         <v>null</v>
@@ -1516,42 +1573,45 @@
         <v>null</v>
       </c>
       <c r="R20" t="str">
+        <v>null</v>
+      </c>
+      <c r="S20" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="B21" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="D21" t="str">
-        <v>DEFINITIEF_UIT_DIENST</v>
+        <v>VERWIJDERDINGS_RENDEMENT</v>
       </c>
       <c r="E21" t="str">
-        <v>Definitief uit dienst</v>
+        <v>Verwijderingsrendement</v>
       </c>
       <c r="F21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="G21" t="str">
-        <v>null</v>
+        <v>http://qudt.org/vocab/unit/PERCENT</v>
       </c>
       <c r="H21" t="str">
-        <v>http://www.w3.org/ns/adms#</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I21" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie</v>
       </c>
       <c r="J21" t="str">
-        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="K21" t="str">
-        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="L21" t="str">
         <v>null</v>
@@ -1569,45 +1629,48 @@
         <v>null</v>
       </c>
       <c r="Q21" t="str">
-        <v>http://purl.org/adms/status/Withdrawn</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/chemische_stof</v>
       </c>
       <c r="R21" t="str">
+        <v>null</v>
+      </c>
+      <c r="S21" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="B22" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D22" t="str">
-        <v>IN_DIENST</v>
+        <v>directe_stookinstallatie</v>
       </c>
       <c r="E22" t="str">
-        <v>In dienst</v>
+        <v>Directe Stookinstallatie</v>
       </c>
       <c r="F22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G22" t="str">
         <v>null</v>
       </c>
       <c r="H22" t="str">
-        <v>http://www.w3.org/ns/adms#</v>
+        <v>null</v>
       </c>
       <c r="I22" t="str">
         <v>null</v>
       </c>
       <c r="J22" t="str">
-        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="K22" t="str">
-        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="L22" t="str">
         <v>null</v>
@@ -1616,54 +1679,57 @@
         <v>null</v>
       </c>
       <c r="N22" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="O22" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="P22" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="Q22" t="str">
-        <v>http://purl.org/adms/status/Completed</v>
+        <v>null</v>
       </c>
       <c r="R22" t="str">
+        <v>null</v>
+      </c>
+      <c r="S22" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie</v>
       </c>
       <c r="B23" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D23" t="str">
-        <v>ONTMANTELD</v>
+        <v>filterinstallatie</v>
       </c>
       <c r="E23" t="str">
-        <v>Ontmanteld</v>
+        <v>Filter Installatie</v>
       </c>
       <c r="F23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G23" t="str">
         <v>null</v>
       </c>
       <c r="H23" t="str">
-        <v>http://www.w3.org/ns/adms#</v>
+        <v>null</v>
       </c>
       <c r="I23" t="str">
         <v>null</v>
       </c>
       <c r="J23" t="str">
-        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+        <v>null</v>
       </c>
       <c r="K23" t="str">
-        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+        <v>null</v>
       </c>
       <c r="L23" t="str">
         <v>null</v>
@@ -1681,45 +1747,48 @@
         <v>null</v>
       </c>
       <c r="Q23" t="str">
-        <v>http://purl.org/adms/status/Withdrawn</v>
+        <v>null</v>
       </c>
       <c r="R23" t="str">
+        <v>null</v>
+      </c>
+      <c r="S23" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
       </c>
       <c r="B24" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D24" t="str">
-        <v>TIJDELIJK_UIT_DIENST</v>
+        <v>installatie</v>
       </c>
       <c r="E24" t="str">
-        <v>Tijdelijk uit dienst</v>
+        <v>Installatie</v>
       </c>
       <c r="F24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G24" t="str">
         <v>null</v>
       </c>
       <c r="H24" t="str">
-        <v>http://www.w3.org/ns/adms#</v>
+        <v>null</v>
       </c>
       <c r="I24" t="str">
         <v>null</v>
       </c>
       <c r="J24" t="str">
-        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="K24" t="str">
-        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="L24" t="str">
         <v>null</v>
@@ -1737,54 +1806,57 @@
         <v>null</v>
       </c>
       <c r="Q24" t="str">
-        <v>http://purl.org/adms/status/Deprecated</v>
+        <v>null</v>
       </c>
       <c r="R24" t="str">
+        <v>null</v>
+      </c>
+      <c r="S24" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="B25" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D25" t="str">
-        <v>VOORGESTELD</v>
+        <v>stookinstallatie</v>
       </c>
       <c r="E25" t="str">
-        <v>Voorgesteld Ontwerp</v>
+        <v>Stookinstallatie</v>
       </c>
       <c r="F25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G25" t="str">
         <v>null</v>
       </c>
       <c r="H25" t="str">
-        <v>http://www.w3.org/ns/adms#</v>
+        <v>null</v>
       </c>
       <c r="I25" t="str">
         <v>null</v>
       </c>
       <c r="J25" t="str">
-        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+        <v>null</v>
       </c>
       <c r="K25" t="str">
-        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+        <v>null</v>
       </c>
       <c r="L25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="M25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="N25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="O25" t="str">
         <v>null</v>
@@ -1793,30 +1865,33 @@
         <v>null</v>
       </c>
       <c r="Q25" t="str">
-        <v>http://purl.org/adms/status/UnderDevelopment</v>
+        <v>null</v>
       </c>
       <c r="R25" t="str">
+        <v>null</v>
+      </c>
+      <c r="S25" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
       </c>
       <c r="B26" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C26" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="D26" t="str">
-        <v>null</v>
+        <v>meetput</v>
       </c>
       <c r="E26" t="str">
-        <v>null</v>
+        <v>Meetput</v>
       </c>
       <c r="F26" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="G26" t="str">
         <v>null</v>
@@ -1852,27 +1927,30 @@
         <v>null</v>
       </c>
       <c r="R26" t="str">
-        <v>http://qudt.org/vocab/unit/M|http://qudt.org/vocab/unit/MegaW</v>
+        <v>null</v>
+      </c>
+      <c r="S26" t="str">
+        <v>null</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
       </c>
       <c r="B27" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C27" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="D27" t="str">
-        <v>null</v>
+        <v>grondwaterput</v>
       </c>
       <c r="E27" t="str">
-        <v>Emissiepunt eigenschappen</v>
+        <v>Grondwaterput</v>
       </c>
       <c r="F27" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="G27" t="str">
         <v>null</v>
@@ -1884,10 +1962,10 @@
         <v>null</v>
       </c>
       <c r="J27" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="K27" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="L27" t="str">
         <v>null</v>
@@ -1908,42 +1986,45 @@
         <v>null</v>
       </c>
       <c r="R27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
+        <v>null</v>
+      </c>
+      <c r="S27" t="str">
+        <v>null</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
       </c>
       <c r="B28" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C28" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D28" t="str">
-        <v>null</v>
+        <v>EMISSIE</v>
       </c>
       <c r="E28" t="str">
-        <v>Emissiepunt types</v>
+        <v>Emissie</v>
       </c>
       <c r="F28" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G28" t="str">
         <v>null</v>
       </c>
       <c r="H28" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I28" t="str">
         <v>null</v>
       </c>
       <c r="J28" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="K28" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="L28" t="str">
         <v>null</v>
@@ -1964,42 +2045,45 @@
         <v>null</v>
       </c>
       <c r="R28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_vertikale_uitstroom</v>
+        <v>null</v>
+      </c>
+      <c r="S28" t="str">
+        <v>null</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking</v>
       </c>
       <c r="B29" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C29" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D29" t="str">
-        <v>null</v>
+        <v>ONTTREKKING</v>
       </c>
       <c r="E29" t="str">
-        <v>Installatie eigenschappen</v>
+        <v>Onttrekking</v>
       </c>
       <c r="F29" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G29" t="str">
         <v>null</v>
       </c>
       <c r="H29" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I29" t="str">
         <v>null</v>
       </c>
       <c r="J29" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="K29" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="L29" t="str">
         <v>null</v>
@@ -2020,42 +2104,45 @@
         <v>null</v>
       </c>
       <c r="R29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen</v>
+        <v>null</v>
+      </c>
+      <c r="S29" t="str">
+        <v>null</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport</v>
       </c>
       <c r="B30" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C30" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D30" t="str">
-        <v>null</v>
+        <v>TRANSPORT</v>
       </c>
       <c r="E30" t="str">
-        <v>Installatie types</v>
+        <v>Transport</v>
       </c>
       <c r="F30" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G30" t="str">
         <v>null</v>
       </c>
       <c r="H30" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I30" t="str">
         <v>null</v>
       </c>
       <c r="J30" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="K30" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="L30" t="str">
         <v>null</v>
@@ -2076,42 +2163,45 @@
         <v>null</v>
       </c>
       <c r="R30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
+      </c>
+      <c r="S30" t="str">
+        <v>null</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
       </c>
       <c r="B31" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C31" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D31" t="str">
-        <v>null</v>
+        <v>VERWERKING</v>
       </c>
       <c r="E31" t="str">
-        <v>Meetpunt types</v>
+        <v>Verwerking</v>
       </c>
       <c r="F31" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G31" t="str">
         <v>null</v>
       </c>
       <c r="H31" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I31" t="str">
         <v>null</v>
       </c>
       <c r="J31" t="str">
-        <v>null</v>
+        <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="K31" t="str">
-        <v>null</v>
+        <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="L31" t="str">
         <v>null</v>
@@ -2132,42 +2222,45 @@
         <v>null</v>
       </c>
       <c r="R31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+        <v>null</v>
+      </c>
+      <c r="S31" t="str">
+        <v>null</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
       </c>
       <c r="B32" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C32" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D32" t="str">
-        <v>null</v>
+        <v>DEFINITIEF_UIT_DIENST</v>
       </c>
       <c r="E32" t="str">
-        <v>Onttrekkingspunt types</v>
+        <v>Definitief uit dienst</v>
       </c>
       <c r="F32" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G32" t="str">
         <v>null</v>
       </c>
       <c r="H32" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I32" t="str">
         <v>null</v>
       </c>
       <c r="J32" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="K32" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="L32" t="str">
         <v>null</v>
@@ -2188,42 +2281,45 @@
         <v>null</v>
       </c>
       <c r="R32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+        <v>http://purl.org/adms/status/Withdrawn</v>
+      </c>
+      <c r="S32" t="str">
+        <v>null</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
       </c>
       <c r="B33" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C33" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D33" t="str">
-        <v>null</v>
+        <v>IN_DIENST</v>
       </c>
       <c r="E33" t="str">
-        <v>Procedure types</v>
+        <v>In dienst</v>
       </c>
       <c r="F33" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G33" t="str">
         <v>null</v>
       </c>
       <c r="H33" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I33" t="str">
         <v>null</v>
       </c>
       <c r="J33" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="K33" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="L33" t="str">
         <v>null</v>
@@ -2244,68 +2340,723 @@
         <v>null</v>
       </c>
       <c r="R33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>http://purl.org/adms/status/Completed</v>
+      </c>
+      <c r="S33" t="str">
+        <v>null</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
+      </c>
+      <c r="B34" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C34" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
-      <c r="B34" t="str">
+      <c r="D34" t="str">
+        <v>ONTMANTELD</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Ontmanteld</v>
+      </c>
+      <c r="F34" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+      </c>
+      <c r="G34" t="str">
+        <v>null</v>
+      </c>
+      <c r="H34" t="str">
+        <v>http://www.w3.org/ns/adms#</v>
+      </c>
+      <c r="I34" t="str">
+        <v>null</v>
+      </c>
+      <c r="J34" t="str">
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+      </c>
+      <c r="K34" t="str">
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+      </c>
+      <c r="L34" t="str">
+        <v>null</v>
+      </c>
+      <c r="M34" t="str">
+        <v>null</v>
+      </c>
+      <c r="N34" t="str">
+        <v>null</v>
+      </c>
+      <c r="O34" t="str">
+        <v>null</v>
+      </c>
+      <c r="P34" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>null</v>
+      </c>
+      <c r="R34" t="str">
+        <v>http://purl.org/adms/status/Withdrawn</v>
+      </c>
+      <c r="S34" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
+      </c>
+      <c r="B35" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C35" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+      </c>
+      <c r="D35" t="str">
+        <v>TIJDELIJK_UIT_DIENST</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Tijdelijk uit dienst</v>
+      </c>
+      <c r="F35" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+      </c>
+      <c r="G35" t="str">
+        <v>null</v>
+      </c>
+      <c r="H35" t="str">
+        <v>http://www.w3.org/ns/adms#</v>
+      </c>
+      <c r="I35" t="str">
+        <v>null</v>
+      </c>
+      <c r="J35" t="str">
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+      </c>
+      <c r="K35" t="str">
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+      </c>
+      <c r="L35" t="str">
+        <v>null</v>
+      </c>
+      <c r="M35" t="str">
+        <v>null</v>
+      </c>
+      <c r="N35" t="str">
+        <v>null</v>
+      </c>
+      <c r="O35" t="str">
+        <v>null</v>
+      </c>
+      <c r="P35" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q35" t="str">
+        <v>null</v>
+      </c>
+      <c r="R35" t="str">
+        <v>http://purl.org/adms/status/Deprecated</v>
+      </c>
+      <c r="S35" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
+      </c>
+      <c r="B36" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C36" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+      </c>
+      <c r="D36" t="str">
+        <v>VOORGESTELD</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Voorgesteld Ontwerp</v>
+      </c>
+      <c r="F36" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+      </c>
+      <c r="G36" t="str">
+        <v>null</v>
+      </c>
+      <c r="H36" t="str">
+        <v>http://www.w3.org/ns/adms#</v>
+      </c>
+      <c r="I36" t="str">
+        <v>null</v>
+      </c>
+      <c r="J36" t="str">
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+      </c>
+      <c r="K36" t="str">
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+      </c>
+      <c r="L36" t="str">
+        <v>null</v>
+      </c>
+      <c r="M36" t="str">
+        <v>null</v>
+      </c>
+      <c r="N36" t="str">
+        <v>null</v>
+      </c>
+      <c r="O36" t="str">
+        <v>null</v>
+      </c>
+      <c r="P36" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>null</v>
+      </c>
+      <c r="R36" t="str">
+        <v>http://purl.org/adms/status/UnderDevelopment</v>
+      </c>
+      <c r="S36" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
+      </c>
+      <c r="B37" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
-      <c r="C34" t="str">
-        <v>null</v>
-      </c>
-      <c r="D34" t="str">
-        <v>null</v>
-      </c>
-      <c r="E34" t="str">
+      <c r="C37" t="str">
+        <v>null</v>
+      </c>
+      <c r="D37" t="str">
+        <v>null</v>
+      </c>
+      <c r="E37" t="str">
+        <v>null</v>
+      </c>
+      <c r="F37" t="str">
+        <v>null</v>
+      </c>
+      <c r="G37" t="str">
+        <v>null</v>
+      </c>
+      <c r="H37" t="str">
+        <v>null</v>
+      </c>
+      <c r="I37" t="str">
+        <v>null</v>
+      </c>
+      <c r="J37" t="str">
+        <v>null</v>
+      </c>
+      <c r="K37" t="str">
+        <v>null</v>
+      </c>
+      <c r="L37" t="str">
+        <v>null</v>
+      </c>
+      <c r="M37" t="str">
+        <v>null</v>
+      </c>
+      <c r="N37" t="str">
+        <v>null</v>
+      </c>
+      <c r="O37" t="str">
+        <v>null</v>
+      </c>
+      <c r="P37" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q37" t="str">
+        <v>null</v>
+      </c>
+      <c r="R37" t="str">
+        <v>null</v>
+      </c>
+      <c r="S37" t="str">
+        <v>http://qudt.org/vocab/unit/DEG_C|http://qudt.org/vocab/unit/K|http://qudt.org/vocab/unit/M|http://qudt.org/vocab/unit/MegaW|http://qudt.org/vocab/unit/MicroGM-PER-L|http://qudt.org/vocab/unit/MilliGM-PER-L|http://qudt.org/vocab/unit/NanoGM-PER-L|http://qudt.org/vocab/unit/PERCENT|http://qudt.org/vocab/unit/PPB|http://qudt.org/vocab/unit/PPM</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+      </c>
+      <c r="B38" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C38" t="str">
+        <v>null</v>
+      </c>
+      <c r="D38" t="str">
+        <v>null</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Emissiepunt eigenschappen</v>
+      </c>
+      <c r="F38" t="str">
+        <v>null</v>
+      </c>
+      <c r="G38" t="str">
+        <v>null</v>
+      </c>
+      <c r="H38" t="str">
+        <v>null</v>
+      </c>
+      <c r="I38" t="str">
+        <v>null</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+      </c>
+      <c r="L38" t="str">
+        <v>null</v>
+      </c>
+      <c r="M38" t="str">
+        <v>null</v>
+      </c>
+      <c r="N38" t="str">
+        <v>null</v>
+      </c>
+      <c r="O38" t="str">
+        <v>null</v>
+      </c>
+      <c r="P38" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q38" t="str">
+        <v>null</v>
+      </c>
+      <c r="R38" t="str">
+        <v>null</v>
+      </c>
+      <c r="S38" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+      </c>
+      <c r="B39" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C39" t="str">
+        <v>null</v>
+      </c>
+      <c r="D39" t="str">
+        <v>null</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Emissiepunt types</v>
+      </c>
+      <c r="F39" t="str">
+        <v>null</v>
+      </c>
+      <c r="G39" t="str">
+        <v>null</v>
+      </c>
+      <c r="H39" t="str">
+        <v>null</v>
+      </c>
+      <c r="I39" t="str">
+        <v>null</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Een typering van verschillende soorten emissiepunten.</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Een typering van verschillende soorten emissiepunten.</v>
+      </c>
+      <c r="L39" t="str">
+        <v>null</v>
+      </c>
+      <c r="M39" t="str">
+        <v>null</v>
+      </c>
+      <c r="N39" t="str">
+        <v>null</v>
+      </c>
+      <c r="O39" t="str">
+        <v>null</v>
+      </c>
+      <c r="P39" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q39" t="str">
+        <v>null</v>
+      </c>
+      <c r="R39" t="str">
+        <v>null</v>
+      </c>
+      <c r="S39" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+      </c>
+      <c r="B40" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C40" t="str">
+        <v>null</v>
+      </c>
+      <c r="D40" t="str">
+        <v>null</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Installatie eigenschappen</v>
+      </c>
+      <c r="F40" t="str">
+        <v>null</v>
+      </c>
+      <c r="G40" t="str">
+        <v>null</v>
+      </c>
+      <c r="H40" t="str">
+        <v>null</v>
+      </c>
+      <c r="I40" t="str">
+        <v>null</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+      </c>
+      <c r="L40" t="str">
+        <v>null</v>
+      </c>
+      <c r="M40" t="str">
+        <v>null</v>
+      </c>
+      <c r="N40" t="str">
+        <v>null</v>
+      </c>
+      <c r="O40" t="str">
+        <v>null</v>
+      </c>
+      <c r="P40" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>null</v>
+      </c>
+      <c r="R40" t="str">
+        <v>null</v>
+      </c>
+      <c r="S40" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+      </c>
+      <c r="B41" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C41" t="str">
+        <v>null</v>
+      </c>
+      <c r="D41" t="str">
+        <v>null</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Installatie types</v>
+      </c>
+      <c r="F41" t="str">
+        <v>null</v>
+      </c>
+      <c r="G41" t="str">
+        <v>null</v>
+      </c>
+      <c r="H41" t="str">
+        <v>null</v>
+      </c>
+      <c r="I41" t="str">
+        <v>null</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Een typering van verschillende soorten installaties.</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Een typering van verschillende soorten installaties.</v>
+      </c>
+      <c r="L41" t="str">
+        <v>null</v>
+      </c>
+      <c r="M41" t="str">
+        <v>null</v>
+      </c>
+      <c r="N41" t="str">
+        <v>null</v>
+      </c>
+      <c r="O41" t="str">
+        <v>null</v>
+      </c>
+      <c r="P41" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>null</v>
+      </c>
+      <c r="R41" t="str">
+        <v>null</v>
+      </c>
+      <c r="S41" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+      </c>
+      <c r="B42" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C42" t="str">
+        <v>null</v>
+      </c>
+      <c r="D42" t="str">
+        <v>null</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Meetpunt types</v>
+      </c>
+      <c r="F42" t="str">
+        <v>null</v>
+      </c>
+      <c r="G42" t="str">
+        <v>null</v>
+      </c>
+      <c r="H42" t="str">
+        <v>null</v>
+      </c>
+      <c r="I42" t="str">
+        <v>null</v>
+      </c>
+      <c r="J42" t="str">
+        <v>null</v>
+      </c>
+      <c r="K42" t="str">
+        <v>null</v>
+      </c>
+      <c r="L42" t="str">
+        <v>null</v>
+      </c>
+      <c r="M42" t="str">
+        <v>null</v>
+      </c>
+      <c r="N42" t="str">
+        <v>null</v>
+      </c>
+      <c r="O42" t="str">
+        <v>null</v>
+      </c>
+      <c r="P42" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q42" t="str">
+        <v>null</v>
+      </c>
+      <c r="R42" t="str">
+        <v>null</v>
+      </c>
+      <c r="S42" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+      </c>
+      <c r="B43" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C43" t="str">
+        <v>null</v>
+      </c>
+      <c r="D43" t="str">
+        <v>null</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Onttrekkingspunt types</v>
+      </c>
+      <c r="F43" t="str">
+        <v>null</v>
+      </c>
+      <c r="G43" t="str">
+        <v>null</v>
+      </c>
+      <c r="H43" t="str">
+        <v>null</v>
+      </c>
+      <c r="I43" t="str">
+        <v>null</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+      </c>
+      <c r="L43" t="str">
+        <v>null</v>
+      </c>
+      <c r="M43" t="str">
+        <v>null</v>
+      </c>
+      <c r="N43" t="str">
+        <v>null</v>
+      </c>
+      <c r="O43" t="str">
+        <v>null</v>
+      </c>
+      <c r="P43" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q43" t="str">
+        <v>null</v>
+      </c>
+      <c r="R43" t="str">
+        <v>null</v>
+      </c>
+      <c r="S43" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+      </c>
+      <c r="B44" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C44" t="str">
+        <v>null</v>
+      </c>
+      <c r="D44" t="str">
+        <v>null</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Procedure types</v>
+      </c>
+      <c r="F44" t="str">
+        <v>null</v>
+      </c>
+      <c r="G44" t="str">
+        <v>null</v>
+      </c>
+      <c r="H44" t="str">
+        <v>null</v>
+      </c>
+      <c r="I44" t="str">
+        <v>null</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Een typering van verschillende procedures.</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Een typering van verschillende procedures.</v>
+      </c>
+      <c r="L44" t="str">
+        <v>null</v>
+      </c>
+      <c r="M44" t="str">
+        <v>null</v>
+      </c>
+      <c r="N44" t="str">
+        <v>null</v>
+      </c>
+      <c r="O44" t="str">
+        <v>null</v>
+      </c>
+      <c r="P44" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q44" t="str">
+        <v>null</v>
+      </c>
+      <c r="R44" t="str">
+        <v>null</v>
+      </c>
+      <c r="S44" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+      </c>
+      <c r="B45" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C45" t="str">
+        <v>null</v>
+      </c>
+      <c r="D45" t="str">
+        <v>null</v>
+      </c>
+      <c r="E45" t="str">
         <v>Status types</v>
       </c>
-      <c r="F34" t="str">
-        <v>null</v>
-      </c>
-      <c r="G34" t="str">
-        <v>null</v>
-      </c>
-      <c r="H34" t="str">
-        <v>null</v>
-      </c>
-      <c r="I34" t="str">
-        <v>null</v>
-      </c>
-      <c r="J34" t="str">
+      <c r="F45" t="str">
+        <v>null</v>
+      </c>
+      <c r="G45" t="str">
+        <v>null</v>
+      </c>
+      <c r="H45" t="str">
+        <v>null</v>
+      </c>
+      <c r="I45" t="str">
+        <v>null</v>
+      </c>
+      <c r="J45" t="str">
         <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
-      <c r="K34" t="str">
+      <c r="K45" t="str">
         <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
-      <c r="L34" t="str">
-        <v>null</v>
-      </c>
-      <c r="M34" t="str">
-        <v>null</v>
-      </c>
-      <c r="N34" t="str">
-        <v>null</v>
-      </c>
-      <c r="O34" t="str">
-        <v>null</v>
-      </c>
-      <c r="P34" t="str">
-        <v>null</v>
-      </c>
-      <c r="Q34" t="str">
-        <v>null</v>
-      </c>
-      <c r="R34" t="str">
+      <c r="L45" t="str">
+        <v>null</v>
+      </c>
+      <c r="M45" t="str">
+        <v>null</v>
+      </c>
+      <c r="N45" t="str">
+        <v>null</v>
+      </c>
+      <c r="O45" t="str">
+        <v>null</v>
+      </c>
+      <c r="P45" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>null</v>
+      </c>
+      <c r="R45" t="str">
+        <v>null</v>
+      </c>
+      <c r="S45" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:U45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,12 +449,18 @@
         <v>broaderTransitive</v>
       </c>
       <c r="Q1" t="str">
+        <v>isVerplicht</v>
+      </c>
+      <c r="R1" t="str">
+        <v>isMeervoudig</v>
+      </c>
+      <c r="S1" t="str">
         <v>parameterDimensie</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>seeAlso</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>hasTopConcept</v>
       </c>
     </row>
@@ -516,6 +522,12 @@
       <c r="S2" t="str">
         <v>null</v>
       </c>
+      <c r="T2" t="str">
+        <v>null</v>
+      </c>
+      <c r="U2" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -575,6 +587,12 @@
       <c r="S3" t="str">
         <v>null</v>
       </c>
+      <c r="T3" t="str">
+        <v>null</v>
+      </c>
+      <c r="U3" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -634,6 +652,12 @@
       <c r="S4" t="str">
         <v>null</v>
       </c>
+      <c r="T4" t="str">
+        <v>null</v>
+      </c>
+      <c r="U4" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -693,6 +717,12 @@
       <c r="S5" t="str">
         <v>null</v>
       </c>
+      <c r="T5" t="str">
+        <v>null</v>
+      </c>
+      <c r="U5" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -752,6 +782,12 @@
       <c r="S6" t="str">
         <v>null</v>
       </c>
+      <c r="T6" t="str">
+        <v>null</v>
+      </c>
+      <c r="U6" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -811,6 +847,12 @@
       <c r="S7" t="str">
         <v>null</v>
       </c>
+      <c r="T7" t="str">
+        <v>null</v>
+      </c>
+      <c r="U7" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -870,6 +912,12 @@
       <c r="S8" t="str">
         <v>null</v>
       </c>
+      <c r="T8" t="str">
+        <v>null</v>
+      </c>
+      <c r="U8" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -929,6 +977,12 @@
       <c r="S9" t="str">
         <v>null</v>
       </c>
+      <c r="T9" t="str">
+        <v>null</v>
+      </c>
+      <c r="U9" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -988,6 +1042,12 @@
       <c r="S10" t="str">
         <v>null</v>
       </c>
+      <c r="T10" t="str">
+        <v>null</v>
+      </c>
+      <c r="U10" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1047,6 +1107,12 @@
       <c r="S11" t="str">
         <v>null</v>
       </c>
+      <c r="T11" t="str">
+        <v>null</v>
+      </c>
+      <c r="U11" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1106,6 +1172,12 @@
       <c r="S12" t="str">
         <v>null</v>
       </c>
+      <c r="T12" t="str">
+        <v>null</v>
+      </c>
+      <c r="U12" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1165,6 +1237,12 @@
       <c r="S13" t="str">
         <v>null</v>
       </c>
+      <c r="T13" t="str">
+        <v>null</v>
+      </c>
+      <c r="U13" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1224,6 +1302,12 @@
       <c r="S14" t="str">
         <v>null</v>
       </c>
+      <c r="T14" t="str">
+        <v>null</v>
+      </c>
+      <c r="U14" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1283,6 +1367,12 @@
       <c r="S15" t="str">
         <v>null</v>
       </c>
+      <c r="T15" t="str">
+        <v>null</v>
+      </c>
+      <c r="U15" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1342,6 +1432,12 @@
       <c r="S16" t="str">
         <v>null</v>
       </c>
+      <c r="T16" t="str">
+        <v>null</v>
+      </c>
+      <c r="U16" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1401,6 +1497,12 @@
       <c r="S17" t="str">
         <v>null</v>
       </c>
+      <c r="T17" t="str">
+        <v>null</v>
+      </c>
+      <c r="U17" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1460,6 +1562,12 @@
       <c r="S18" t="str">
         <v>null</v>
       </c>
+      <c r="T18" t="str">
+        <v>null</v>
+      </c>
+      <c r="U18" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1519,6 +1627,12 @@
       <c r="S19" t="str">
         <v>null</v>
       </c>
+      <c r="T19" t="str">
+        <v>null</v>
+      </c>
+      <c r="U19" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1570,12 +1684,18 @@
         <v>null</v>
       </c>
       <c r="Q20" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="R20" t="str">
         <v>null</v>
       </c>
       <c r="S20" t="str">
+        <v>null</v>
+      </c>
+      <c r="T20" t="str">
+        <v>null</v>
+      </c>
+      <c r="U20" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1629,12 +1749,18 @@
         <v>null</v>
       </c>
       <c r="Q21" t="str">
+        <v>null</v>
+      </c>
+      <c r="R21" t="str">
+        <v>true</v>
+      </c>
+      <c r="S21" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/chemische_stof</v>
       </c>
-      <c r="R21" t="str">
-        <v>null</v>
-      </c>
-      <c r="S21" t="str">
+      <c r="T21" t="str">
+        <v>null</v>
+      </c>
+      <c r="U21" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1696,6 +1822,12 @@
       <c r="S22" t="str">
         <v>null</v>
       </c>
+      <c r="T22" t="str">
+        <v>null</v>
+      </c>
+      <c r="U22" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1755,6 +1887,12 @@
       <c r="S23" t="str">
         <v>null</v>
       </c>
+      <c r="T23" t="str">
+        <v>null</v>
+      </c>
+      <c r="U23" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1814,6 +1952,12 @@
       <c r="S24" t="str">
         <v>null</v>
       </c>
+      <c r="T24" t="str">
+        <v>null</v>
+      </c>
+      <c r="U24" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1873,6 +2017,12 @@
       <c r="S25" t="str">
         <v>null</v>
       </c>
+      <c r="T25" t="str">
+        <v>null</v>
+      </c>
+      <c r="U25" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1932,6 +2082,12 @@
       <c r="S26" t="str">
         <v>null</v>
       </c>
+      <c r="T26" t="str">
+        <v>null</v>
+      </c>
+      <c r="U26" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1991,6 +2147,12 @@
       <c r="S27" t="str">
         <v>null</v>
       </c>
+      <c r="T27" t="str">
+        <v>null</v>
+      </c>
+      <c r="U27" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -2050,6 +2212,12 @@
       <c r="S28" t="str">
         <v>null</v>
       </c>
+      <c r="T28" t="str">
+        <v>null</v>
+      </c>
+      <c r="U28" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -2109,6 +2277,12 @@
       <c r="S29" t="str">
         <v>null</v>
       </c>
+      <c r="T29" t="str">
+        <v>null</v>
+      </c>
+      <c r="U29" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -2168,6 +2342,12 @@
       <c r="S30" t="str">
         <v>null</v>
       </c>
+      <c r="T30" t="str">
+        <v>null</v>
+      </c>
+      <c r="U30" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -2227,6 +2407,12 @@
       <c r="S31" t="str">
         <v>null</v>
       </c>
+      <c r="T31" t="str">
+        <v>null</v>
+      </c>
+      <c r="U31" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -2281,9 +2467,15 @@
         <v>null</v>
       </c>
       <c r="R32" t="str">
+        <v>null</v>
+      </c>
+      <c r="S32" t="str">
+        <v>null</v>
+      </c>
+      <c r="T32" t="str">
         <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
-      <c r="S32" t="str">
+      <c r="U32" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2340,9 +2532,15 @@
         <v>null</v>
       </c>
       <c r="R33" t="str">
+        <v>null</v>
+      </c>
+      <c r="S33" t="str">
+        <v>null</v>
+      </c>
+      <c r="T33" t="str">
         <v>http://purl.org/adms/status/Completed</v>
       </c>
-      <c r="S33" t="str">
+      <c r="U33" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2399,9 +2597,15 @@
         <v>null</v>
       </c>
       <c r="R34" t="str">
+        <v>null</v>
+      </c>
+      <c r="S34" t="str">
+        <v>null</v>
+      </c>
+      <c r="T34" t="str">
         <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
-      <c r="S34" t="str">
+      <c r="U34" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2458,9 +2662,15 @@
         <v>null</v>
       </c>
       <c r="R35" t="str">
+        <v>null</v>
+      </c>
+      <c r="S35" t="str">
+        <v>null</v>
+      </c>
+      <c r="T35" t="str">
         <v>http://purl.org/adms/status/Deprecated</v>
       </c>
-      <c r="S35" t="str">
+      <c r="U35" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2517,9 +2727,15 @@
         <v>null</v>
       </c>
       <c r="R36" t="str">
+        <v>null</v>
+      </c>
+      <c r="S36" t="str">
+        <v>null</v>
+      </c>
+      <c r="T36" t="str">
         <v>http://purl.org/adms/status/UnderDevelopment</v>
       </c>
-      <c r="S36" t="str">
+      <c r="U36" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2579,6 +2795,12 @@
         <v>null</v>
       </c>
       <c r="S37" t="str">
+        <v>null</v>
+      </c>
+      <c r="T37" t="str">
+        <v>null</v>
+      </c>
+      <c r="U37" t="str">
         <v>http://qudt.org/vocab/unit/DEG_C|http://qudt.org/vocab/unit/K|http://qudt.org/vocab/unit/M|http://qudt.org/vocab/unit/MegaW|http://qudt.org/vocab/unit/MicroGM-PER-L|http://qudt.org/vocab/unit/MilliGM-PER-L|http://qudt.org/vocab/unit/NanoGM-PER-L|http://qudt.org/vocab/unit/PERCENT|http://qudt.org/vocab/unit/PPB|http://qudt.org/vocab/unit/PPM</v>
       </c>
     </row>
@@ -2638,6 +2860,12 @@
         <v>null</v>
       </c>
       <c r="S38" t="str">
+        <v>null</v>
+      </c>
+      <c r="T38" t="str">
+        <v>null</v>
+      </c>
+      <c r="U38" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
       </c>
     </row>
@@ -2697,6 +2925,12 @@
         <v>null</v>
       </c>
       <c r="S39" t="str">
+        <v>null</v>
+      </c>
+      <c r="T39" t="str">
+        <v>null</v>
+      </c>
+      <c r="U39" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
     </row>
@@ -2756,6 +2990,12 @@
         <v>null</v>
       </c>
       <c r="S40" t="str">
+        <v>null</v>
+      </c>
+      <c r="T40" t="str">
+        <v>null</v>
+      </c>
+      <c r="U40" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
     </row>
@@ -2815,6 +3055,12 @@
         <v>null</v>
       </c>
       <c r="S41" t="str">
+        <v>null</v>
+      </c>
+      <c r="T41" t="str">
+        <v>null</v>
+      </c>
+      <c r="U41" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
       </c>
     </row>
@@ -2874,6 +3120,12 @@
         <v>null</v>
       </c>
       <c r="S42" t="str">
+        <v>null</v>
+      </c>
+      <c r="T42" t="str">
+        <v>null</v>
+      </c>
+      <c r="U42" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
       </c>
     </row>
@@ -2933,6 +3185,12 @@
         <v>null</v>
       </c>
       <c r="S43" t="str">
+        <v>null</v>
+      </c>
+      <c r="T43" t="str">
+        <v>null</v>
+      </c>
+      <c r="U43" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
       </c>
     </row>
@@ -2992,6 +3250,12 @@
         <v>null</v>
       </c>
       <c r="S44" t="str">
+        <v>null</v>
+      </c>
+      <c r="T44" t="str">
+        <v>null</v>
+      </c>
+      <c r="U44" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
       </c>
     </row>
@@ -3051,12 +3315,18 @@
         <v>null</v>
       </c>
       <c r="S45" t="str">
+        <v>null</v>
+      </c>
+      <c r="T45" t="str">
+        <v>null</v>
+      </c>
+      <c r="U45" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -933,7 +933,7 @@
         <v>%</v>
       </c>
       <c r="E9" t="str">
-        <v>Pcent</v>
+        <v>Percent</v>
       </c>
       <c r="F9" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
@@ -1755,7 +1755,7 @@
         <v>true</v>
       </c>
       <c r="S21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/chemische_stof</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/chemische_stof</v>
       </c>
       <c r="T21" t="str">
         <v>null</v>

--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U45"/>
+  <dimension ref="A1:U47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,49 +419,49 @@
         <v>topConceptOf</v>
       </c>
       <c r="G1" t="str">
+        <v>hasTopConcept</v>
+      </c>
+      <c r="H1" t="str">
         <v>relevantUnit</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>relevantDataType</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>relevantRiepr</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>definition</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>note</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>narrower</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>narrowerTransitive</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>semanticRelation</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>broader</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>broaderTransitive</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>isVerplicht</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>isMeervoudig</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>parameterDimensie</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>seeAlso</v>
-      </c>
-      <c r="U1" t="str">
-        <v>hasTopConcept</v>
       </c>
     </row>
     <row r="2">
@@ -1116,31 +1116,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="B12" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="D12" t="str">
-        <v>diameter</v>
+        <v>null</v>
       </c>
       <c r="E12" t="str">
-        <v>Diameter van de schouw</v>
+        <v>null</v>
       </c>
       <c r="F12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="G12" t="str">
-        <v>http://qudt.org/vocab/unit/M</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="H12" t="str">
-        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
+        <v>null</v>
       </c>
       <c r="I12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>null</v>
       </c>
       <c r="J12" t="str">
         <v>null</v>
@@ -1181,7 +1181,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter</v>
       </c>
       <c r="B13" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1190,25 +1190,25 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="D13" t="str">
-        <v>hoogte</v>
+        <v>diameter</v>
       </c>
       <c r="E13" t="str">
-        <v>Hoogte van de schouw</v>
+        <v>Diameter van de schouw</v>
       </c>
       <c r="F13" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="G13" t="str">
+        <v>null</v>
+      </c>
+      <c r="H13" t="str">
         <v>http://qudt.org/vocab/unit/M</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
-      </c>
-      <c r="J13" t="str">
-        <v>null</v>
       </c>
       <c r="K13" t="str">
         <v>null</v>
@@ -1246,37 +1246,37 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
       </c>
       <c r="B14" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="D14" t="str">
-        <v>emissiepunt</v>
+        <v>hoogte</v>
       </c>
       <c r="E14" t="str">
-        <v>Emissiepunt</v>
+        <v>Hoogte van de schouw</v>
       </c>
       <c r="F14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="G14" t="str">
         <v>null</v>
       </c>
       <c r="H14" t="str">
-        <v>null</v>
+        <v>http://qudt.org/vocab/unit/M</v>
       </c>
       <c r="I14" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="J14" t="str">
-        <v>Een regulier emissiepunt.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="K14" t="str">
-        <v>Een regulier emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="L14" t="str">
         <v>null</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
       </c>
       <c r="B15" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1320,10 +1320,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D15" t="str">
-        <v>lozingspunt</v>
+        <v>emissiepunt</v>
       </c>
       <c r="E15" t="str">
-        <v>Lozingspunt</v>
+        <v>Emissiepunt</v>
       </c>
       <c r="F15" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
@@ -1338,13 +1338,13 @@
         <v>null</v>
       </c>
       <c r="J15" t="str">
-        <v>Een lozing naar water.</v>
+        <v>null</v>
       </c>
       <c r="K15" t="str">
-        <v>Een lozing naar water.</v>
+        <v>Een regulier emissiepunt.</v>
       </c>
       <c r="L15" t="str">
-        <v>null</v>
+        <v>Een regulier emissiepunt.</v>
       </c>
       <c r="M15" t="str">
         <v>null</v>
@@ -1376,7 +1376,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
       </c>
       <c r="B16" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1385,10 +1385,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D16" t="str">
-        <v>schoorsteen</v>
+        <v>lozingspunt</v>
       </c>
       <c r="E16" t="str">
-        <v>Schoorsteen</v>
+        <v>Lozingspunt</v>
       </c>
       <c r="F16" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
@@ -1403,19 +1403,19 @@
         <v>null</v>
       </c>
       <c r="J16" t="str">
-        <v>Een schoorsteen.</v>
+        <v>null</v>
       </c>
       <c r="K16" t="str">
-        <v>Een schoorsteen.</v>
+        <v>Een lozing naar water.</v>
       </c>
       <c r="L16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>Een lozing naar water.</v>
       </c>
       <c r="M16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>null</v>
       </c>
       <c r="N16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>null</v>
       </c>
       <c r="O16" t="str">
         <v>null</v>
@@ -1441,7 +1441,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="B17" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1450,10 +1450,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D17" t="str">
-        <v>schoorsteen_horizontale_uitstroom</v>
+        <v>schoorsteen</v>
       </c>
       <c r="E17" t="str">
-        <v>Schoorsteen met horizontale uitstroom</v>
+        <v>Schoorsteen</v>
       </c>
       <c r="F17" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
@@ -1471,22 +1471,22 @@
         <v>null</v>
       </c>
       <c r="K17" t="str">
-        <v>null</v>
+        <v>Een schoorsteen.</v>
       </c>
       <c r="L17" t="str">
-        <v>null</v>
+        <v>Een schoorsteen.</v>
       </c>
       <c r="M17" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="N17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="O17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="P17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="Q17" t="str">
         <v>null</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="B18" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1515,10 +1515,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D18" t="str">
-        <v>schoorsteen_verticale_uitstroom</v>
+        <v>schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="E18" t="str">
-        <v>Schoorsteen met verticale uitstroom</v>
+        <v>Schoorsteen met horizontale uitstroom</v>
       </c>
       <c r="F18" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
@@ -1545,7 +1545,7 @@
         <v>null</v>
       </c>
       <c r="N18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="O18" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
@@ -1554,7 +1554,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="Q18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="R18" t="str">
         <v>null</v>
@@ -1571,7 +1571,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="B19" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1580,10 +1580,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D19" t="str">
-        <v>schouw</v>
+        <v>schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="E19" t="str">
-        <v>Schouw</v>
+        <v>Schoorsteen met verticale uitstroom</v>
       </c>
       <c r="F19" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
@@ -1598,10 +1598,10 @@
         <v>null</v>
       </c>
       <c r="J19" t="str">
-        <v>Een schouw.</v>
+        <v>null</v>
       </c>
       <c r="K19" t="str">
-        <v>Een schouw.</v>
+        <v>null</v>
       </c>
       <c r="L19" t="str">
         <v>null</v>
@@ -1613,13 +1613,13 @@
         <v>null</v>
       </c>
       <c r="O19" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="P19" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="Q19" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="R19" t="str">
         <v>null</v>
@@ -1636,40 +1636,40 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="B20" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D20" t="str">
-        <v>GEINSTALLEERD_VERMOGEN</v>
+        <v>schouw</v>
       </c>
       <c r="E20" t="str">
-        <v>Geinstalleerd vermogen</v>
+        <v>Schouw</v>
       </c>
       <c r="F20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G20" t="str">
-        <v>http://qudt.org/vocab/unit/MegaW</v>
+        <v>null</v>
       </c>
       <c r="H20" t="str">
-        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
+        <v>null</v>
       </c>
       <c r="I20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="J20" t="str">
         <v>null</v>
       </c>
       <c r="K20" t="str">
-        <v>null</v>
+        <v>Een schouw.</v>
       </c>
       <c r="L20" t="str">
-        <v>null</v>
+        <v>Een schouw.</v>
       </c>
       <c r="M20" t="str">
         <v>null</v>
@@ -1684,7 +1684,7 @@
         <v>null</v>
       </c>
       <c r="Q20" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="R20" t="str">
         <v>null</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen</v>
       </c>
       <c r="B21" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1710,25 +1710,25 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="D21" t="str">
-        <v>VERWIJDERDINGS_RENDEMENT</v>
+        <v>GEINSTALLEERD_VERMOGEN</v>
       </c>
       <c r="E21" t="str">
-        <v>Verwijderingsrendement</v>
+        <v>Geinstalleerd vermogen</v>
       </c>
       <c r="F21" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="G21" t="str">
-        <v>http://qudt.org/vocab/unit/PERCENT</v>
+        <v>null</v>
       </c>
       <c r="H21" t="str">
+        <v>http://qudt.org/vocab/unit/MegaW</v>
+      </c>
+      <c r="I21" t="str">
         <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
-      <c r="I21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie</v>
-      </c>
       <c r="J21" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="K21" t="str">
         <v>null</v>
@@ -1755,7 +1755,7 @@
         <v>true</v>
       </c>
       <c r="S21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/chemische_stof</v>
+        <v>null</v>
       </c>
       <c r="T21" t="str">
         <v>null</v>
@@ -1766,34 +1766,34 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="B22" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="D22" t="str">
-        <v>directe_stookinstallatie</v>
+        <v>VERWIJDERDINGS_RENDEMENT</v>
       </c>
       <c r="E22" t="str">
-        <v>Directe Stookinstallatie</v>
+        <v>Verwijderingsrendement</v>
       </c>
       <c r="F22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="G22" t="str">
         <v>null</v>
       </c>
       <c r="H22" t="str">
-        <v>null</v>
+        <v>http://qudt.org/vocab/unit/PERCENT</v>
       </c>
       <c r="I22" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="J22" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie</v>
       </c>
       <c r="K22" t="str">
         <v>null</v>
@@ -1805,13 +1805,13 @@
         <v>null</v>
       </c>
       <c r="N22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="O22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="P22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="Q22" t="str">
         <v>null</v>
@@ -1820,10 +1820,10 @@
         <v>null</v>
       </c>
       <c r="S22" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="T22" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/chemische_stof</v>
       </c>
       <c r="U22" t="str">
         <v>null</v>
@@ -1831,7 +1831,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="B23" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1840,10 +1840,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D23" t="str">
-        <v>filterinstallatie</v>
+        <v>directe_stookinstallatie</v>
       </c>
       <c r="E23" t="str">
-        <v>Filter Installatie</v>
+        <v>Directe Stookinstallatie</v>
       </c>
       <c r="F23" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
@@ -1873,13 +1873,13 @@
         <v>null</v>
       </c>
       <c r="O23" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="P23" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="Q23" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="R23" t="str">
         <v>null</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie</v>
       </c>
       <c r="B24" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1905,10 +1905,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D24" t="str">
-        <v>installatie</v>
+        <v>filterinstallatie</v>
       </c>
       <c r="E24" t="str">
-        <v>Installatie</v>
+        <v>Filter Installatie</v>
       </c>
       <c r="F24" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
       </c>
       <c r="B25" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1970,10 +1970,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D25" t="str">
-        <v>stookinstallatie</v>
+        <v>installatie</v>
       </c>
       <c r="E25" t="str">
-        <v>Stookinstallatie</v>
+        <v>Installatie</v>
       </c>
       <c r="F25" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
@@ -1994,13 +1994,13 @@
         <v>null</v>
       </c>
       <c r="L25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="M25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="N25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="O25" t="str">
         <v>null</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="B26" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D26" t="str">
-        <v>meetput</v>
+        <v>stookinstallatie</v>
       </c>
       <c r="E26" t="str">
-        <v>Meetput</v>
+        <v>Stookinstallatie</v>
       </c>
       <c r="F26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G26" t="str">
         <v>null</v>
@@ -2062,13 +2062,13 @@
         <v>null</v>
       </c>
       <c r="M26" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="N26" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="O26" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="P26" t="str">
         <v>null</v>
@@ -2091,22 +2091,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
       </c>
       <c r="B27" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="D27" t="str">
-        <v>grondwaterput</v>
+        <v>meetput</v>
       </c>
       <c r="E27" t="str">
-        <v>Grondwaterput</v>
+        <v>Meetput</v>
       </c>
       <c r="F27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="G27" t="str">
         <v>null</v>
@@ -2156,37 +2156,37 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
       </c>
       <c r="B28" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="D28" t="str">
-        <v>EMISSIE</v>
+        <v>grondwaterput</v>
       </c>
       <c r="E28" t="str">
-        <v>Emissie</v>
+        <v>Grondwaterput</v>
       </c>
       <c r="F28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="G28" t="str">
         <v>null</v>
       </c>
       <c r="H28" t="str">
-        <v>http://www.w3.org/ns/sosa/Procedure</v>
+        <v>null</v>
       </c>
       <c r="I28" t="str">
         <v>null</v>
       </c>
       <c r="J28" t="str">
-        <v>De procedure emissie via een emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="K28" t="str">
-        <v>De procedure emissie via een emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="L28" t="str">
         <v>null</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
       </c>
       <c r="B29" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2230,10 +2230,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D29" t="str">
-        <v>ONTTREKKING</v>
+        <v>EMISSIE</v>
       </c>
       <c r="E29" t="str">
-        <v>Onttrekking</v>
+        <v>Emissie</v>
       </c>
       <c r="F29" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
@@ -2242,19 +2242,19 @@
         <v>null</v>
       </c>
       <c r="H29" t="str">
+        <v>null</v>
+      </c>
+      <c r="I29" t="str">
         <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
-      <c r="I29" t="str">
-        <v>null</v>
-      </c>
       <c r="J29" t="str">
-        <v>De procedure onttrekking via een onttrekingspunt.</v>
+        <v>null</v>
       </c>
       <c r="K29" t="str">
-        <v>De procedure onttrekking via een onttrekingspunt.</v>
+        <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="L29" t="str">
-        <v>null</v>
+        <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="M29" t="str">
         <v>null</v>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking</v>
       </c>
       <c r="B30" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2295,10 +2295,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D30" t="str">
-        <v>TRANSPORT</v>
+        <v>ONTTREKKING</v>
       </c>
       <c r="E30" t="str">
-        <v>Transport</v>
+        <v>Onttrekking</v>
       </c>
       <c r="F30" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
@@ -2307,19 +2307,19 @@
         <v>null</v>
       </c>
       <c r="H30" t="str">
+        <v>null</v>
+      </c>
+      <c r="I30" t="str">
         <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
-      <c r="I30" t="str">
-        <v>null</v>
-      </c>
       <c r="J30" t="str">
-        <v>De procedure transport tussen twee processen.</v>
+        <v>null</v>
       </c>
       <c r="K30" t="str">
-        <v>De procedure transport tussen twee processen.</v>
+        <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="L30" t="str">
-        <v>null</v>
+        <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="M30" t="str">
         <v>null</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport</v>
       </c>
       <c r="B31" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2360,10 +2360,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D31" t="str">
-        <v>VERWERKING</v>
+        <v>TRANSPORT</v>
       </c>
       <c r="E31" t="str">
-        <v>Verwerking</v>
+        <v>Transport</v>
       </c>
       <c r="F31" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
@@ -2372,19 +2372,19 @@
         <v>null</v>
       </c>
       <c r="H31" t="str">
+        <v>null</v>
+      </c>
+      <c r="I31" t="str">
         <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
-      <c r="I31" t="str">
-        <v>null</v>
-      </c>
       <c r="J31" t="str">
-        <v>De procedure verwerking door een installatie.</v>
+        <v>null</v>
       </c>
       <c r="K31" t="str">
-        <v>De procedure verwerking door een installatie.</v>
+        <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="L31" t="str">
-        <v>null</v>
+        <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="M31" t="str">
         <v>null</v>
@@ -2416,40 +2416,40 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
       </c>
       <c r="B32" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D32" t="str">
-        <v>DEFINITIEF_UIT_DIENST</v>
+        <v>VERWERKING</v>
       </c>
       <c r="E32" t="str">
-        <v>Definitief uit dienst</v>
+        <v>Verwerking</v>
       </c>
       <c r="F32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G32" t="str">
         <v>null</v>
       </c>
       <c r="H32" t="str">
-        <v>http://www.w3.org/ns/adms#</v>
+        <v>null</v>
       </c>
       <c r="I32" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="J32" t="str">
-        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="K32" t="str">
-        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
+        <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="L32" t="str">
-        <v>null</v>
+        <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="M32" t="str">
         <v>null</v>
@@ -2473,7 +2473,7 @@
         <v>null</v>
       </c>
       <c r="T32" t="str">
-        <v>http://purl.org/adms/status/Withdrawn</v>
+        <v>null</v>
       </c>
       <c r="U32" t="str">
         <v>null</v>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
       </c>
       <c r="B33" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2490,10 +2490,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D33" t="str">
-        <v>IN_DIENST</v>
+        <v>DEFINITIEF_UIT_DIENST</v>
       </c>
       <c r="E33" t="str">
-        <v>In dienst</v>
+        <v>Definitief uit dienst</v>
       </c>
       <c r="F33" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
@@ -2502,19 +2502,19 @@
         <v>null</v>
       </c>
       <c r="H33" t="str">
+        <v>null</v>
+      </c>
+      <c r="I33" t="str">
         <v>http://www.w3.org/ns/adms#</v>
       </c>
-      <c r="I33" t="str">
-        <v>null</v>
-      </c>
       <c r="J33" t="str">
-        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="K33" t="str">
-        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="L33" t="str">
-        <v>null</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="M33" t="str">
         <v>null</v>
@@ -2538,15 +2538,15 @@
         <v>null</v>
       </c>
       <c r="T33" t="str">
-        <v>http://purl.org/adms/status/Completed</v>
+        <v>null</v>
       </c>
       <c r="U33" t="str">
-        <v>null</v>
+        <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
       </c>
       <c r="B34" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2555,10 +2555,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D34" t="str">
-        <v>ONTMANTELD</v>
+        <v>IN_DIENST</v>
       </c>
       <c r="E34" t="str">
-        <v>Ontmanteld</v>
+        <v>In dienst</v>
       </c>
       <c r="F34" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
@@ -2567,19 +2567,19 @@
         <v>null</v>
       </c>
       <c r="H34" t="str">
+        <v>null</v>
+      </c>
+      <c r="I34" t="str">
         <v>http://www.w3.org/ns/adms#</v>
       </c>
-      <c r="I34" t="str">
-        <v>null</v>
-      </c>
       <c r="J34" t="str">
-        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+        <v>null</v>
       </c>
       <c r="K34" t="str">
-        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="L34" t="str">
-        <v>null</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="M34" t="str">
         <v>null</v>
@@ -2603,15 +2603,15 @@
         <v>null</v>
       </c>
       <c r="T34" t="str">
-        <v>http://purl.org/adms/status/Withdrawn</v>
+        <v>null</v>
       </c>
       <c r="U34" t="str">
-        <v>null</v>
+        <v>http://purl.org/adms/status/Completed</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
       </c>
       <c r="B35" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2620,10 +2620,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D35" t="str">
-        <v>TIJDELIJK_UIT_DIENST</v>
+        <v>ONTMANTELD</v>
       </c>
       <c r="E35" t="str">
-        <v>Tijdelijk uit dienst</v>
+        <v>Ontmanteld</v>
       </c>
       <c r="F35" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
@@ -2632,19 +2632,19 @@
         <v>null</v>
       </c>
       <c r="H35" t="str">
+        <v>null</v>
+      </c>
+      <c r="I35" t="str">
         <v>http://www.w3.org/ns/adms#</v>
       </c>
-      <c r="I35" t="str">
-        <v>null</v>
-      </c>
       <c r="J35" t="str">
-        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="K35" t="str">
-        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="L35" t="str">
-        <v>null</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="M35" t="str">
         <v>null</v>
@@ -2668,15 +2668,15 @@
         <v>null</v>
       </c>
       <c r="T35" t="str">
-        <v>http://purl.org/adms/status/Deprecated</v>
+        <v>null</v>
       </c>
       <c r="U35" t="str">
-        <v>null</v>
+        <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
       </c>
       <c r="B36" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2685,10 +2685,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D36" t="str">
-        <v>VOORGESTELD</v>
+        <v>TIJDELIJK_UIT_DIENST</v>
       </c>
       <c r="E36" t="str">
-        <v>Voorgesteld Ontwerp</v>
+        <v>Tijdelijk uit dienst</v>
       </c>
       <c r="F36" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
@@ -2697,19 +2697,19 @@
         <v>null</v>
       </c>
       <c r="H36" t="str">
+        <v>null</v>
+      </c>
+      <c r="I36" t="str">
         <v>http://www.w3.org/ns/adms#</v>
       </c>
-      <c r="I36" t="str">
-        <v>null</v>
-      </c>
       <c r="J36" t="str">
-        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+        <v>null</v>
       </c>
       <c r="K36" t="str">
-        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="L36" t="str">
-        <v>null</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="M36" t="str">
         <v>null</v>
@@ -2733,30 +2733,30 @@
         <v>null</v>
       </c>
       <c r="T36" t="str">
-        <v>http://purl.org/adms/status/UnderDevelopment</v>
+        <v>null</v>
       </c>
       <c r="U36" t="str">
-        <v>null</v>
+        <v>http://purl.org/adms/status/Deprecated</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
       <c r="B37" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C37" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D37" t="str">
-        <v>null</v>
+        <v>VOORGESTELD</v>
       </c>
       <c r="E37" t="str">
-        <v>null</v>
+        <v>Voorgesteld Ontwerp</v>
       </c>
       <c r="F37" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G37" t="str">
         <v>null</v>
@@ -2765,16 +2765,16 @@
         <v>null</v>
       </c>
       <c r="I37" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="J37" t="str">
         <v>null</v>
       </c>
       <c r="K37" t="str">
-        <v>null</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="L37" t="str">
-        <v>null</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="M37" t="str">
         <v>null</v>
@@ -2801,12 +2801,12 @@
         <v>null</v>
       </c>
       <c r="U37" t="str">
-        <v>http://qudt.org/vocab/unit/DEG_C|http://qudt.org/vocab/unit/K|http://qudt.org/vocab/unit/M|http://qudt.org/vocab/unit/MegaW|http://qudt.org/vocab/unit/MicroGM-PER-L|http://qudt.org/vocab/unit/MilliGM-PER-L|http://qudt.org/vocab/unit/NanoGM-PER-L|http://qudt.org/vocab/unit/PERCENT|http://qudt.org/vocab/unit/PPB|http://qudt.org/vocab/unit/PPM</v>
+        <v>http://purl.org/adms/status/UnderDevelopment</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="B38" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -2818,13 +2818,13 @@
         <v>null</v>
       </c>
       <c r="E38" t="str">
-        <v>Emissiepunt eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="F38" t="str">
         <v>null</v>
       </c>
       <c r="G38" t="str">
-        <v>null</v>
+        <v>http://qudt.org/vocab/unit/DEG_C|http://qudt.org/vocab/unit/K|http://qudt.org/vocab/unit/M|http://qudt.org/vocab/unit/MegaW|http://qudt.org/vocab/unit/MicroGM-PER-L|http://qudt.org/vocab/unit/MilliGM-PER-L|http://qudt.org/vocab/unit/NanoGM-PER-L|http://qudt.org/vocab/unit/PERCENT|http://qudt.org/vocab/unit/PPB|http://qudt.org/vocab/unit/PPM</v>
       </c>
       <c r="H38" t="str">
         <v>null</v>
@@ -2833,10 +2833,10 @@
         <v>null</v>
       </c>
       <c r="J38" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="K38" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="L38" t="str">
         <v>null</v>
@@ -2866,30 +2866,30 @@
         <v>null</v>
       </c>
       <c r="U38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
+        <v>null</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="B39" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C39" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="D39" t="str">
         <v>null</v>
       </c>
       <c r="E39" t="str">
-        <v>Emissiepunt types</v>
+        <v>Emissiepunt eigenschappen</v>
       </c>
       <c r="F39" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="G39" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
       </c>
       <c r="H39" t="str">
         <v>null</v>
@@ -2898,13 +2898,13 @@
         <v>null</v>
       </c>
       <c r="J39" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="K39" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="L39" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="M39" t="str">
         <v>null</v>
@@ -2931,30 +2931,30 @@
         <v>null</v>
       </c>
       <c r="U39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>null</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="B40" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C40" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="D40" t="str">
         <v>null</v>
       </c>
       <c r="E40" t="str">
-        <v>Installatie eigenschappen</v>
+        <v>Emissiepunt types</v>
       </c>
       <c r="F40" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="G40" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="H40" t="str">
         <v>null</v>
@@ -2963,13 +2963,13 @@
         <v>null</v>
       </c>
       <c r="J40" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>null</v>
       </c>
       <c r="K40" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="L40" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="M40" t="str">
         <v>null</v>
@@ -2996,30 +2996,30 @@
         <v>null</v>
       </c>
       <c r="U40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
+        <v>null</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="B41" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C41" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="D41" t="str">
         <v>null</v>
       </c>
       <c r="E41" t="str">
-        <v>Installatie types</v>
+        <v>Installatie eigenschappen</v>
       </c>
       <c r="F41" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="G41" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="H41" t="str">
         <v>null</v>
@@ -3028,13 +3028,13 @@
         <v>null</v>
       </c>
       <c r="J41" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>null</v>
       </c>
       <c r="K41" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="L41" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="M41" t="str">
         <v>null</v>
@@ -3061,30 +3061,30 @@
         <v>null</v>
       </c>
       <c r="U41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
+        <v>null</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="B42" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C42" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="D42" t="str">
         <v>null</v>
       </c>
       <c r="E42" t="str">
-        <v>Meetpunt types</v>
+        <v>Installatie types</v>
       </c>
       <c r="F42" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="G42" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
       </c>
       <c r="H42" t="str">
         <v>null</v>
@@ -3096,10 +3096,10 @@
         <v>null</v>
       </c>
       <c r="K42" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="L42" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="M42" t="str">
         <v>null</v>
@@ -3126,30 +3126,30 @@
         <v>null</v>
       </c>
       <c r="U42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+        <v>null</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="B43" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C43" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="D43" t="str">
         <v>null</v>
       </c>
       <c r="E43" t="str">
-        <v>Onttrekkingspunt types</v>
+        <v>Meetpunt types</v>
       </c>
       <c r="F43" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="G43" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
       </c>
       <c r="H43" t="str">
         <v>null</v>
@@ -3158,10 +3158,10 @@
         <v>null</v>
       </c>
       <c r="J43" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>null</v>
       </c>
       <c r="K43" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>null</v>
       </c>
       <c r="L43" t="str">
         <v>null</v>
@@ -3191,30 +3191,30 @@
         <v>null</v>
       </c>
       <c r="U43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+        <v>null</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="B44" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C44" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="D44" t="str">
         <v>null</v>
       </c>
       <c r="E44" t="str">
-        <v>Procedure types</v>
+        <v>Onttrekkingspunt types</v>
       </c>
       <c r="F44" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="G44" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
       </c>
       <c r="H44" t="str">
         <v>null</v>
@@ -3223,13 +3223,13 @@
         <v>null</v>
       </c>
       <c r="J44" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>null</v>
       </c>
       <c r="K44" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="L44" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="M44" t="str">
         <v>null</v>
@@ -3256,12 +3256,12 @@
         <v>null</v>
       </c>
       <c r="U44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>null</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="B45" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -3273,60 +3273,190 @@
         <v>null</v>
       </c>
       <c r="E45" t="str">
+        <v>Procedure types</v>
+      </c>
+      <c r="F45" t="str">
+        <v>null</v>
+      </c>
+      <c r="G45" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+      </c>
+      <c r="H45" t="str">
+        <v>null</v>
+      </c>
+      <c r="I45" t="str">
+        <v>null</v>
+      </c>
+      <c r="J45" t="str">
+        <v>null</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Een typering van verschillende procedures.</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Een typering van verschillende procedures.</v>
+      </c>
+      <c r="M45" t="str">
+        <v>null</v>
+      </c>
+      <c r="N45" t="str">
+        <v>null</v>
+      </c>
+      <c r="O45" t="str">
+        <v>null</v>
+      </c>
+      <c r="P45" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>null</v>
+      </c>
+      <c r="R45" t="str">
+        <v>null</v>
+      </c>
+      <c r="S45" t="str">
+        <v>null</v>
+      </c>
+      <c r="T45" t="str">
+        <v>null</v>
+      </c>
+      <c r="U45" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+      </c>
+      <c r="B46" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C46" t="str">
+        <v>null</v>
+      </c>
+      <c r="D46" t="str">
+        <v>null</v>
+      </c>
+      <c r="E46" t="str">
         <v>Status types</v>
       </c>
-      <c r="F45" t="str">
-        <v>null</v>
-      </c>
-      <c r="G45" t="str">
-        <v>null</v>
-      </c>
-      <c r="H45" t="str">
-        <v>null</v>
-      </c>
-      <c r="I45" t="str">
-        <v>null</v>
-      </c>
-      <c r="J45" t="str">
+      <c r="F46" t="str">
+        <v>null</v>
+      </c>
+      <c r="G46" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
+      </c>
+      <c r="H46" t="str">
+        <v>null</v>
+      </c>
+      <c r="I46" t="str">
+        <v>null</v>
+      </c>
+      <c r="J46" t="str">
+        <v>null</v>
+      </c>
+      <c r="K46" t="str">
         <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
-      <c r="K45" t="str">
+      <c r="L46" t="str">
         <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
-      <c r="L45" t="str">
-        <v>null</v>
-      </c>
-      <c r="M45" t="str">
-        <v>null</v>
-      </c>
-      <c r="N45" t="str">
-        <v>null</v>
-      </c>
-      <c r="O45" t="str">
-        <v>null</v>
-      </c>
-      <c r="P45" t="str">
-        <v>null</v>
-      </c>
-      <c r="Q45" t="str">
-        <v>null</v>
-      </c>
-      <c r="R45" t="str">
-        <v>null</v>
-      </c>
-      <c r="S45" t="str">
-        <v>null</v>
-      </c>
-      <c r="T45" t="str">
-        <v>null</v>
-      </c>
-      <c r="U45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
+      <c r="M46" t="str">
+        <v>null</v>
+      </c>
+      <c r="N46" t="str">
+        <v>null</v>
+      </c>
+      <c r="O46" t="str">
+        <v>null</v>
+      </c>
+      <c r="P46" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q46" t="str">
+        <v>null</v>
+      </c>
+      <c r="R46" t="str">
+        <v>null</v>
+      </c>
+      <c r="S46" t="str">
+        <v>null</v>
+      </c>
+      <c r="T46" t="str">
+        <v>null</v>
+      </c>
+      <c r="U46" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+      </c>
+      <c r="B47" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+      </c>
+      <c r="C47" t="str">
+        <v>null</v>
+      </c>
+      <c r="D47" t="str">
+        <v>null</v>
+      </c>
+      <c r="E47" t="str">
+        <v>null</v>
+      </c>
+      <c r="F47" t="str">
+        <v>null</v>
+      </c>
+      <c r="G47" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+      </c>
+      <c r="H47" t="str">
+        <v>null</v>
+      </c>
+      <c r="I47" t="str">
+        <v>null</v>
+      </c>
+      <c r="J47" t="str">
+        <v>null</v>
+      </c>
+      <c r="K47" t="str">
+        <v>null</v>
+      </c>
+      <c r="L47" t="str">
+        <v>null</v>
+      </c>
+      <c r="M47" t="str">
+        <v>null</v>
+      </c>
+      <c r="N47" t="str">
+        <v>null</v>
+      </c>
+      <c r="O47" t="str">
+        <v>null</v>
+      </c>
+      <c r="P47" t="str">
+        <v>null</v>
+      </c>
+      <c r="Q47" t="str">
+        <v>null</v>
+      </c>
+      <c r="R47" t="str">
+        <v>null</v>
+      </c>
+      <c r="S47" t="str">
+        <v>null</v>
+      </c>
+      <c r="T47" t="str">
+        <v>null</v>
+      </c>
+      <c r="U47" t="str">
+        <v>null</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,45 +422,48 @@
         <v>hasTopConcept</v>
       </c>
       <c r="H1" t="str">
+        <v>isPartOf</v>
+      </c>
+      <c r="I1" t="str">
         <v>relevantUnit</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>relevantDataType</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>relevantRiepr</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>definition</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>note</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>narrower</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>narrowerTransitive</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>semanticRelation</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>broader</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>broaderTransitive</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>isVerplicht</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>isMeervoudig</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>parameterDimensie</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>seeAlso</v>
       </c>
     </row>
@@ -528,6 +531,9 @@
       <c r="U2" t="str">
         <v>null</v>
       </c>
+      <c r="V2" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -593,6 +599,9 @@
       <c r="U3" t="str">
         <v>null</v>
       </c>
+      <c r="V3" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -658,6 +667,9 @@
       <c r="U4" t="str">
         <v>null</v>
       </c>
+      <c r="V4" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -723,6 +735,9 @@
       <c r="U5" t="str">
         <v>null</v>
       </c>
+      <c r="V5" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -788,6 +803,9 @@
       <c r="U6" t="str">
         <v>null</v>
       </c>
+      <c r="V6" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -853,6 +871,9 @@
       <c r="U7" t="str">
         <v>null</v>
       </c>
+      <c r="V7" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -918,6 +939,9 @@
       <c r="U8" t="str">
         <v>null</v>
       </c>
+      <c r="V8" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -983,6 +1007,9 @@
       <c r="U9" t="str">
         <v>null</v>
       </c>
+      <c r="V9" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -1048,6 +1075,9 @@
       <c r="U10" t="str">
         <v>null</v>
       </c>
+      <c r="V10" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1113,6 +1143,9 @@
       <c r="U11" t="str">
         <v>null</v>
       </c>
+      <c r="V11" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1178,6 +1211,9 @@
       <c r="U12" t="str">
         <v>null</v>
       </c>
+      <c r="V12" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1202,17 +1238,17 @@
         <v>null</v>
       </c>
       <c r="H13" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+      </c>
+      <c r="I13" t="str">
         <v>http://qudt.org/vocab/unit/M</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
         <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
-      <c r="J13" t="str">
+      <c r="K13" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
-      <c r="K13" t="str">
-        <v>null</v>
-      </c>
       <c r="L13" t="str">
         <v>null</v>
       </c>
@@ -1241,6 +1277,9 @@
         <v>null</v>
       </c>
       <c r="U13" t="str">
+        <v>null</v>
+      </c>
+      <c r="V13" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1267,17 +1306,17 @@
         <v>null</v>
       </c>
       <c r="H14" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+      </c>
+      <c r="I14" t="str">
         <v>http://qudt.org/vocab/unit/M</v>
       </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
         <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
-      <c r="J14" t="str">
+      <c r="K14" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
-      <c r="K14" t="str">
-        <v>null</v>
-      </c>
       <c r="L14" t="str">
         <v>null</v>
       </c>
@@ -1306,6 +1345,9 @@
         <v>null</v>
       </c>
       <c r="U14" t="str">
+        <v>null</v>
+      </c>
+      <c r="V14" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1332,7 +1374,7 @@
         <v>null</v>
       </c>
       <c r="H15" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I15" t="str">
         <v>null</v>
@@ -1341,13 +1383,13 @@
         <v>null</v>
       </c>
       <c r="K15" t="str">
-        <v>Een regulier emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="L15" t="str">
         <v>Een regulier emissiepunt.</v>
       </c>
       <c r="M15" t="str">
-        <v>null</v>
+        <v>Een regulier emissiepunt.</v>
       </c>
       <c r="N15" t="str">
         <v>null</v>
@@ -1371,6 +1413,9 @@
         <v>null</v>
       </c>
       <c r="U15" t="str">
+        <v>null</v>
+      </c>
+      <c r="V15" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1397,7 +1442,7 @@
         <v>null</v>
       </c>
       <c r="H16" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I16" t="str">
         <v>null</v>
@@ -1406,13 +1451,13 @@
         <v>null</v>
       </c>
       <c r="K16" t="str">
-        <v>Een lozing naar water.</v>
+        <v>null</v>
       </c>
       <c r="L16" t="str">
         <v>Een lozing naar water.</v>
       </c>
       <c r="M16" t="str">
-        <v>null</v>
+        <v>Een lozing naar water.</v>
       </c>
       <c r="N16" t="str">
         <v>null</v>
@@ -1436,6 +1481,9 @@
         <v>null</v>
       </c>
       <c r="U16" t="str">
+        <v>null</v>
+      </c>
+      <c r="V16" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1462,7 +1510,7 @@
         <v>null</v>
       </c>
       <c r="H17" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I17" t="str">
         <v>null</v>
@@ -1471,13 +1519,13 @@
         <v>null</v>
       </c>
       <c r="K17" t="str">
-        <v>Een schoorsteen.</v>
+        <v>null</v>
       </c>
       <c r="L17" t="str">
         <v>Een schoorsteen.</v>
       </c>
       <c r="M17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>Een schoorsteen.</v>
       </c>
       <c r="N17" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
@@ -1486,7 +1534,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="P17" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="Q17" t="str">
         <v>null</v>
@@ -1501,6 +1549,9 @@
         <v>null</v>
       </c>
       <c r="U17" t="str">
+        <v>null</v>
+      </c>
+      <c r="V17" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1527,7 +1578,7 @@
         <v>null</v>
       </c>
       <c r="H18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I18" t="str">
         <v>null</v>
@@ -1548,7 +1599,7 @@
         <v>null</v>
       </c>
       <c r="O18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="P18" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
@@ -1557,7 +1608,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="R18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="S18" t="str">
         <v>null</v>
@@ -1566,6 +1617,9 @@
         <v>null</v>
       </c>
       <c r="U18" t="str">
+        <v>null</v>
+      </c>
+      <c r="V18" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1592,7 +1646,7 @@
         <v>null</v>
       </c>
       <c r="H19" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I19" t="str">
         <v>null</v>
@@ -1613,7 +1667,7 @@
         <v>null</v>
       </c>
       <c r="O19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="P19" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
@@ -1622,7 +1676,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="R19" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="S19" t="str">
         <v>null</v>
@@ -1631,6 +1685,9 @@
         <v>null</v>
       </c>
       <c r="U19" t="str">
+        <v>null</v>
+      </c>
+      <c r="V19" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1657,7 +1714,7 @@
         <v>null</v>
       </c>
       <c r="H20" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I20" t="str">
         <v>null</v>
@@ -1666,13 +1723,13 @@
         <v>null</v>
       </c>
       <c r="K20" t="str">
-        <v>Een schouw.</v>
+        <v>null</v>
       </c>
       <c r="L20" t="str">
         <v>Een schouw.</v>
       </c>
       <c r="M20" t="str">
-        <v>null</v>
+        <v>Een schouw.</v>
       </c>
       <c r="N20" t="str">
         <v>null</v>
@@ -1696,6 +1753,9 @@
         <v>null</v>
       </c>
       <c r="U20" t="str">
+        <v>null</v>
+      </c>
+      <c r="V20" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1722,17 +1782,17 @@
         <v>null</v>
       </c>
       <c r="H21" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+      </c>
+      <c r="I21" t="str">
         <v>http://qudt.org/vocab/unit/MegaW</v>
       </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
         <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
-      <c r="J21" t="str">
+      <c r="K21" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
-      <c r="K21" t="str">
-        <v>null</v>
-      </c>
       <c r="L21" t="str">
         <v>null</v>
       </c>
@@ -1752,15 +1812,18 @@
         <v>null</v>
       </c>
       <c r="R21" t="str">
+        <v>null</v>
+      </c>
+      <c r="S21" t="str">
         <v>true</v>
       </c>
-      <c r="S21" t="str">
-        <v>null</v>
-      </c>
       <c r="T21" t="str">
         <v>null</v>
       </c>
       <c r="U21" t="str">
+        <v>null</v>
+      </c>
+      <c r="V21" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1787,17 +1850,17 @@
         <v>null</v>
       </c>
       <c r="H22" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+      </c>
+      <c r="I22" t="str">
         <v>http://qudt.org/vocab/unit/PERCENT</v>
       </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
         <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
-      <c r="J22" t="str">
+      <c r="K22" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie</v>
       </c>
-      <c r="K22" t="str">
-        <v>null</v>
-      </c>
       <c r="L22" t="str">
         <v>null</v>
       </c>
@@ -1820,12 +1883,15 @@
         <v>null</v>
       </c>
       <c r="S22" t="str">
+        <v>null</v>
+      </c>
+      <c r="T22" t="str">
         <v>true</v>
       </c>
-      <c r="T22" t="str">
+      <c r="U22" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/chemische_stof</v>
       </c>
-      <c r="U22" t="str">
+      <c r="V22" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1852,7 +1918,7 @@
         <v>null</v>
       </c>
       <c r="H23" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I23" t="str">
         <v>null</v>
@@ -1873,7 +1939,7 @@
         <v>null</v>
       </c>
       <c r="O23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="P23" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
@@ -1882,7 +1948,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="R23" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="S23" t="str">
         <v>null</v>
@@ -1891,6 +1957,9 @@
         <v>null</v>
       </c>
       <c r="U23" t="str">
+        <v>null</v>
+      </c>
+      <c r="V23" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1917,7 +1986,7 @@
         <v>null</v>
       </c>
       <c r="H24" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I24" t="str">
         <v>null</v>
@@ -1956,6 +2025,9 @@
         <v>null</v>
       </c>
       <c r="U24" t="str">
+        <v>null</v>
+      </c>
+      <c r="V24" t="str">
         <v>null</v>
       </c>
     </row>
@@ -1982,7 +2054,7 @@
         <v>null</v>
       </c>
       <c r="H25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I25" t="str">
         <v>null</v>
@@ -2021,6 +2093,9 @@
         <v>null</v>
       </c>
       <c r="U25" t="str">
+        <v>null</v>
+      </c>
+      <c r="V25" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2047,7 +2122,7 @@
         <v>null</v>
       </c>
       <c r="H26" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I26" t="str">
         <v>null</v>
@@ -2062,7 +2137,7 @@
         <v>null</v>
       </c>
       <c r="M26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="N26" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
@@ -2071,7 +2146,7 @@
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="P26" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="Q26" t="str">
         <v>null</v>
@@ -2086,6 +2161,9 @@
         <v>null</v>
       </c>
       <c r="U26" t="str">
+        <v>null</v>
+      </c>
+      <c r="V26" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2112,7 +2190,7 @@
         <v>null</v>
       </c>
       <c r="H27" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I27" t="str">
         <v>null</v>
@@ -2151,6 +2229,9 @@
         <v>null</v>
       </c>
       <c r="U27" t="str">
+        <v>null</v>
+      </c>
+      <c r="V27" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2177,7 +2258,7 @@
         <v>null</v>
       </c>
       <c r="H28" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
       </c>
       <c r="I28" t="str">
         <v>null</v>
@@ -2216,6 +2297,9 @@
         <v>null</v>
       </c>
       <c r="U28" t="str">
+        <v>null</v>
+      </c>
+      <c r="V28" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2245,19 +2329,19 @@
         <v>null</v>
       </c>
       <c r="I29" t="str">
+        <v>null</v>
+      </c>
+      <c r="J29" t="str">
         <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
-      <c r="J29" t="str">
-        <v>null</v>
-      </c>
       <c r="K29" t="str">
-        <v>De procedure emissie via een emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="L29" t="str">
         <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="M29" t="str">
-        <v>null</v>
+        <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="N29" t="str">
         <v>null</v>
@@ -2281,6 +2365,9 @@
         <v>null</v>
       </c>
       <c r="U29" t="str">
+        <v>null</v>
+      </c>
+      <c r="V29" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2310,19 +2397,19 @@
         <v>null</v>
       </c>
       <c r="I30" t="str">
+        <v>null</v>
+      </c>
+      <c r="J30" t="str">
         <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
-      <c r="J30" t="str">
-        <v>null</v>
-      </c>
       <c r="K30" t="str">
-        <v>De procedure onttrekking via een onttrekingspunt.</v>
+        <v>null</v>
       </c>
       <c r="L30" t="str">
         <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="M30" t="str">
-        <v>null</v>
+        <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="N30" t="str">
         <v>null</v>
@@ -2346,6 +2433,9 @@
         <v>null</v>
       </c>
       <c r="U30" t="str">
+        <v>null</v>
+      </c>
+      <c r="V30" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2375,19 +2465,19 @@
         <v>null</v>
       </c>
       <c r="I31" t="str">
+        <v>null</v>
+      </c>
+      <c r="J31" t="str">
         <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
-      <c r="J31" t="str">
-        <v>null</v>
-      </c>
       <c r="K31" t="str">
-        <v>De procedure transport tussen twee processen.</v>
+        <v>null</v>
       </c>
       <c r="L31" t="str">
         <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="M31" t="str">
-        <v>null</v>
+        <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="N31" t="str">
         <v>null</v>
@@ -2411,6 +2501,9 @@
         <v>null</v>
       </c>
       <c r="U31" t="str">
+        <v>null</v>
+      </c>
+      <c r="V31" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2440,19 +2533,19 @@
         <v>null</v>
       </c>
       <c r="I32" t="str">
+        <v>null</v>
+      </c>
+      <c r="J32" t="str">
         <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
-      <c r="J32" t="str">
-        <v>null</v>
-      </c>
       <c r="K32" t="str">
-        <v>De procedure verwerking door een installatie.</v>
+        <v>null</v>
       </c>
       <c r="L32" t="str">
         <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="M32" t="str">
-        <v>null</v>
+        <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="N32" t="str">
         <v>null</v>
@@ -2476,6 +2569,9 @@
         <v>null</v>
       </c>
       <c r="U32" t="str">
+        <v>null</v>
+      </c>
+      <c r="V32" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2505,19 +2601,19 @@
         <v>null</v>
       </c>
       <c r="I33" t="str">
+        <v>null</v>
+      </c>
+      <c r="J33" t="str">
         <v>http://www.w3.org/ns/adms#</v>
       </c>
-      <c r="J33" t="str">
-        <v>null</v>
-      </c>
       <c r="K33" t="str">
-        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="L33" t="str">
         <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="M33" t="str">
-        <v>null</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="N33" t="str">
         <v>null</v>
@@ -2541,6 +2637,9 @@
         <v>null</v>
       </c>
       <c r="U33" t="str">
+        <v>null</v>
+      </c>
+      <c r="V33" t="str">
         <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
     </row>
@@ -2570,19 +2669,19 @@
         <v>null</v>
       </c>
       <c r="I34" t="str">
+        <v>null</v>
+      </c>
+      <c r="J34" t="str">
         <v>http://www.w3.org/ns/adms#</v>
       </c>
-      <c r="J34" t="str">
-        <v>null</v>
-      </c>
       <c r="K34" t="str">
-        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="L34" t="str">
         <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="M34" t="str">
-        <v>null</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="N34" t="str">
         <v>null</v>
@@ -2606,6 +2705,9 @@
         <v>null</v>
       </c>
       <c r="U34" t="str">
+        <v>null</v>
+      </c>
+      <c r="V34" t="str">
         <v>http://purl.org/adms/status/Completed</v>
       </c>
     </row>
@@ -2635,19 +2737,19 @@
         <v>null</v>
       </c>
       <c r="I35" t="str">
+        <v>null</v>
+      </c>
+      <c r="J35" t="str">
         <v>http://www.w3.org/ns/adms#</v>
       </c>
-      <c r="J35" t="str">
-        <v>null</v>
-      </c>
       <c r="K35" t="str">
-        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+        <v>null</v>
       </c>
       <c r="L35" t="str">
         <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="M35" t="str">
-        <v>null</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="N35" t="str">
         <v>null</v>
@@ -2671,6 +2773,9 @@
         <v>null</v>
       </c>
       <c r="U35" t="str">
+        <v>null</v>
+      </c>
+      <c r="V35" t="str">
         <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
     </row>
@@ -2700,19 +2805,19 @@
         <v>null</v>
       </c>
       <c r="I36" t="str">
+        <v>null</v>
+      </c>
+      <c r="J36" t="str">
         <v>http://www.w3.org/ns/adms#</v>
       </c>
-      <c r="J36" t="str">
-        <v>null</v>
-      </c>
       <c r="K36" t="str">
-        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="L36" t="str">
         <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="M36" t="str">
-        <v>null</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="N36" t="str">
         <v>null</v>
@@ -2736,6 +2841,9 @@
         <v>null</v>
       </c>
       <c r="U36" t="str">
+        <v>null</v>
+      </c>
+      <c r="V36" t="str">
         <v>http://purl.org/adms/status/Deprecated</v>
       </c>
     </row>
@@ -2765,19 +2873,19 @@
         <v>null</v>
       </c>
       <c r="I37" t="str">
+        <v>null</v>
+      </c>
+      <c r="J37" t="str">
         <v>http://www.w3.org/ns/adms#</v>
       </c>
-      <c r="J37" t="str">
-        <v>null</v>
-      </c>
       <c r="K37" t="str">
-        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+        <v>null</v>
       </c>
       <c r="L37" t="str">
         <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="M37" t="str">
-        <v>null</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="N37" t="str">
         <v>null</v>
@@ -2801,6 +2909,9 @@
         <v>null</v>
       </c>
       <c r="U37" t="str">
+        <v>null</v>
+      </c>
+      <c r="V37" t="str">
         <v>http://purl.org/adms/status/UnderDevelopment</v>
       </c>
     </row>
@@ -2868,6 +2979,9 @@
       <c r="U38" t="str">
         <v>null</v>
       </c>
+      <c r="V38" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2901,13 +3015,13 @@
         <v>null</v>
       </c>
       <c r="K39" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="L39" t="str">
         <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="M39" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="N39" t="str">
         <v>null</v>
@@ -2931,6 +3045,9 @@
         <v>null</v>
       </c>
       <c r="U39" t="str">
+        <v>null</v>
+      </c>
+      <c r="V39" t="str">
         <v>null</v>
       </c>
     </row>
@@ -2966,13 +3083,13 @@
         <v>null</v>
       </c>
       <c r="K40" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="L40" t="str">
         <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="M40" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="N40" t="str">
         <v>null</v>
@@ -2996,6 +3113,9 @@
         <v>null</v>
       </c>
       <c r="U40" t="str">
+        <v>null</v>
+      </c>
+      <c r="V40" t="str">
         <v>null</v>
       </c>
     </row>
@@ -3031,13 +3151,13 @@
         <v>null</v>
       </c>
       <c r="K41" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>null</v>
       </c>
       <c r="L41" t="str">
         <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="M41" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="N41" t="str">
         <v>null</v>
@@ -3061,6 +3181,9 @@
         <v>null</v>
       </c>
       <c r="U41" t="str">
+        <v>null</v>
+      </c>
+      <c r="V41" t="str">
         <v>null</v>
       </c>
     </row>
@@ -3096,13 +3219,13 @@
         <v>null</v>
       </c>
       <c r="K42" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>null</v>
       </c>
       <c r="L42" t="str">
         <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="M42" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="N42" t="str">
         <v>null</v>
@@ -3126,6 +3249,9 @@
         <v>null</v>
       </c>
       <c r="U42" t="str">
+        <v>null</v>
+      </c>
+      <c r="V42" t="str">
         <v>null</v>
       </c>
     </row>
@@ -3193,6 +3319,9 @@
       <c r="U43" t="str">
         <v>null</v>
       </c>
+      <c r="V43" t="str">
+        <v>null</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -3226,13 +3355,13 @@
         <v>null</v>
       </c>
       <c r="K44" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>null</v>
       </c>
       <c r="L44" t="str">
         <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="M44" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="N44" t="str">
         <v>null</v>
@@ -3256,6 +3385,9 @@
         <v>null</v>
       </c>
       <c r="U44" t="str">
+        <v>null</v>
+      </c>
+      <c r="V44" t="str">
         <v>null</v>
       </c>
     </row>
@@ -3291,13 +3423,13 @@
         <v>null</v>
       </c>
       <c r="K45" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>null</v>
       </c>
       <c r="L45" t="str">
         <v>Een typering van verschillende procedures.</v>
       </c>
       <c r="M45" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende procedures.</v>
       </c>
       <c r="N45" t="str">
         <v>null</v>
@@ -3321,6 +3453,9 @@
         <v>null</v>
       </c>
       <c r="U45" t="str">
+        <v>null</v>
+      </c>
+      <c r="V45" t="str">
         <v>null</v>
       </c>
     </row>
@@ -3356,13 +3491,13 @@
         <v>null</v>
       </c>
       <c r="K46" t="str">
-        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
+        <v>null</v>
       </c>
       <c r="L46" t="str">
         <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
       <c r="M46" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
       <c r="N46" t="str">
         <v>null</v>
@@ -3386,6 +3521,9 @@
         <v>null</v>
       </c>
       <c r="U46" t="str">
+        <v>null</v>
+      </c>
+      <c r="V46" t="str">
         <v>null</v>
       </c>
     </row>
@@ -3453,10 +3591,13 @@
       <c r="U47" t="str">
         <v>null</v>
       </c>
+      <c r="V47" t="str">
+        <v>null</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V47"/>
+  <dimension ref="A1:V46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1167,7 +1167,7 @@
         <v>null</v>
       </c>
       <c r="G12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="H12" t="str">
         <v>null</v>
@@ -1374,7 +1374,7 @@
         <v>null</v>
       </c>
       <c r="H15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I15" t="str">
         <v>null</v>
@@ -1442,7 +1442,7 @@
         <v>null</v>
       </c>
       <c r="H16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I16" t="str">
         <v>null</v>
@@ -1510,7 +1510,7 @@
         <v>null</v>
       </c>
       <c r="H17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I17" t="str">
         <v>null</v>
@@ -1572,13 +1572,13 @@
         <v>Schoorsteen met horizontale uitstroom</v>
       </c>
       <c r="F18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>null</v>
       </c>
       <c r="G18" t="str">
         <v>null</v>
       </c>
       <c r="H18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I18" t="str">
         <v>null</v>
@@ -1640,13 +1640,13 @@
         <v>Schoorsteen met verticale uitstroom</v>
       </c>
       <c r="F19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>null</v>
       </c>
       <c r="G19" t="str">
         <v>null</v>
       </c>
       <c r="H19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I19" t="str">
         <v>null</v>
@@ -1714,7 +1714,7 @@
         <v>null</v>
       </c>
       <c r="H20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I20" t="str">
         <v>null</v>
@@ -1912,13 +1912,13 @@
         <v>Directe Stookinstallatie</v>
       </c>
       <c r="F23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>null</v>
       </c>
       <c r="G23" t="str">
         <v>null</v>
       </c>
       <c r="H23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I23" t="str">
         <v>null</v>
@@ -1986,7 +1986,7 @@
         <v>null</v>
       </c>
       <c r="H24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I24" t="str">
         <v>null</v>
@@ -2054,7 +2054,7 @@
         <v>null</v>
       </c>
       <c r="H25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I25" t="str">
         <v>null</v>
@@ -2122,7 +2122,7 @@
         <v>null</v>
       </c>
       <c r="H26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I26" t="str">
         <v>null</v>
@@ -2190,7 +2190,7 @@
         <v>null</v>
       </c>
       <c r="H27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I27" t="str">
         <v>null</v>
@@ -2258,7 +2258,7 @@
         <v>null</v>
       </c>
       <c r="H28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I28" t="str">
         <v>null</v>
@@ -2988,10 +2988,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="B39" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="D39" t="str">
         <v>null</v>
@@ -3000,13 +3000,13 @@
         <v>Emissiepunt eigenschappen</v>
       </c>
       <c r="F39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="G39" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
       </c>
       <c r="H39" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="I39" t="str">
         <v>null</v>
@@ -3056,10 +3056,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="B40" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>null</v>
       </c>
       <c r="D40" t="str">
         <v>null</v>
@@ -3068,13 +3068,13 @@
         <v>Emissiepunt types</v>
       </c>
       <c r="F40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>null</v>
       </c>
       <c r="G40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="H40" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I40" t="str">
         <v>null</v>
@@ -3124,10 +3124,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="B41" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="D41" t="str">
         <v>null</v>
@@ -3136,13 +3136,13 @@
         <v>Installatie eigenschappen</v>
       </c>
       <c r="F41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="G41" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="H41" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
       <c r="I41" t="str">
         <v>null</v>
@@ -3192,10 +3192,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="B42" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>null</v>
       </c>
       <c r="D42" t="str">
         <v>null</v>
@@ -3204,13 +3204,13 @@
         <v>Installatie types</v>
       </c>
       <c r="F42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>null</v>
       </c>
       <c r="G42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
       </c>
       <c r="H42" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
       <c r="I42" t="str">
         <v>null</v>
@@ -3527,77 +3527,9 @@
         <v>null</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
-      </c>
-      <c r="B47" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C47" t="str">
-        <v>null</v>
-      </c>
-      <c r="D47" t="str">
-        <v>null</v>
-      </c>
-      <c r="E47" t="str">
-        <v>null</v>
-      </c>
-      <c r="F47" t="str">
-        <v>null</v>
-      </c>
-      <c r="G47" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
-      </c>
-      <c r="H47" t="str">
-        <v>null</v>
-      </c>
-      <c r="I47" t="str">
-        <v>null</v>
-      </c>
-      <c r="J47" t="str">
-        <v>null</v>
-      </c>
-      <c r="K47" t="str">
-        <v>null</v>
-      </c>
-      <c r="L47" t="str">
-        <v>null</v>
-      </c>
-      <c r="M47" t="str">
-        <v>null</v>
-      </c>
-      <c r="N47" t="str">
-        <v>null</v>
-      </c>
-      <c r="O47" t="str">
-        <v>null</v>
-      </c>
-      <c r="P47" t="str">
-        <v>null</v>
-      </c>
-      <c r="Q47" t="str">
-        <v>null</v>
-      </c>
-      <c r="R47" t="str">
-        <v>null</v>
-      </c>
-      <c r="S47" t="str">
-        <v>null</v>
-      </c>
-      <c r="T47" t="str">
-        <v>null</v>
-      </c>
-      <c r="U47" t="str">
-        <v>null</v>
-      </c>
-      <c r="V47" t="str">
-        <v>null</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V46"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
+++ b/src/main/resources/be/vlaanderen/omgeving/data/id/conceptscheme/rie-iepr/rie-iepr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:V45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,52 +419,52 @@
         <v>topConceptOf</v>
       </c>
       <c r="G1" t="str">
+        <v>relevantUnit</v>
+      </c>
+      <c r="H1" t="str">
+        <v>relevantDataType</v>
+      </c>
+      <c r="I1" t="str">
+        <v>relevantRiepr</v>
+      </c>
+      <c r="J1" t="str">
+        <v>definition</v>
+      </c>
+      <c r="K1" t="str">
+        <v>note</v>
+      </c>
+      <c r="L1" t="str">
+        <v>narrower</v>
+      </c>
+      <c r="M1" t="str">
+        <v>narrowerTransitive</v>
+      </c>
+      <c r="N1" t="str">
+        <v>semanticRelation</v>
+      </c>
+      <c r="O1" t="str">
+        <v>broader</v>
+      </c>
+      <c r="P1" t="str">
+        <v>broaderTransitive</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>isVerplicht</v>
+      </c>
+      <c r="R1" t="str">
+        <v>isMeervoudig</v>
+      </c>
+      <c r="S1" t="str">
+        <v>parameterDimensie</v>
+      </c>
+      <c r="T1" t="str">
+        <v>seeAlso</v>
+      </c>
+      <c r="U1" t="str">
         <v>hasTopConcept</v>
       </c>
-      <c r="H1" t="str">
+      <c r="V1" t="str">
         <v>isPartOf</v>
-      </c>
-      <c r="I1" t="str">
-        <v>relevantUnit</v>
-      </c>
-      <c r="J1" t="str">
-        <v>relevantDataType</v>
-      </c>
-      <c r="K1" t="str">
-        <v>relevantRiepr</v>
-      </c>
-      <c r="L1" t="str">
-        <v>definition</v>
-      </c>
-      <c r="M1" t="str">
-        <v>note</v>
-      </c>
-      <c r="N1" t="str">
-        <v>narrower</v>
-      </c>
-      <c r="O1" t="str">
-        <v>narrowerTransitive</v>
-      </c>
-      <c r="P1" t="str">
-        <v>semanticRelation</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>broader</v>
-      </c>
-      <c r="R1" t="str">
-        <v>broaderTransitive</v>
-      </c>
-      <c r="S1" t="str">
-        <v>isVerplicht</v>
-      </c>
-      <c r="T1" t="str">
-        <v>isMeervoudig</v>
-      </c>
-      <c r="U1" t="str">
-        <v>parameterDimensie</v>
-      </c>
-      <c r="V1" t="str">
-        <v>seeAlso</v>
       </c>
     </row>
     <row r="2">
@@ -1149,31 +1149,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter</v>
       </c>
       <c r="B12" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C12" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="D12" t="str">
-        <v>null</v>
+        <v>diameter</v>
       </c>
       <c r="E12" t="str">
-        <v>null</v>
+        <v>Diameter van de schouw</v>
       </c>
       <c r="F12" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="G12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type|https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>http://qudt.org/vocab/unit/M</v>
       </c>
       <c r="H12" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I12" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="J12" t="str">
         <v>null</v>
@@ -1217,7 +1217,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
       </c>
       <c r="B13" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1226,28 +1226,28 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="D13" t="str">
-        <v>diameter</v>
+        <v>hoogte</v>
       </c>
       <c r="E13" t="str">
-        <v>Diameter van de schouw</v>
+        <v>Hoogte van de schouw</v>
       </c>
       <c r="F13" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="G13" t="str">
-        <v>null</v>
+        <v>http://qudt.org/vocab/unit/M</v>
       </c>
       <c r="H13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I13" t="str">
-        <v>http://qudt.org/vocab/unit/M</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="J13" t="str">
-        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
+        <v>null</v>
       </c>
       <c r="K13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>null</v>
       </c>
       <c r="L13" t="str">
         <v>null</v>
@@ -1285,37 +1285,37 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
       </c>
       <c r="B14" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D14" t="str">
-        <v>hoogte</v>
+        <v>emissiepunt</v>
       </c>
       <c r="E14" t="str">
-        <v>Hoogte van de schouw</v>
+        <v>Emissiepunt</v>
       </c>
       <c r="F14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G14" t="str">
         <v>null</v>
       </c>
       <c r="H14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="I14" t="str">
-        <v>http://qudt.org/vocab/unit/M</v>
+        <v>null</v>
       </c>
       <c r="J14" t="str">
-        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
+        <v>Een regulier emissiepunt.</v>
       </c>
       <c r="K14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>Een regulier emissiepunt.</v>
       </c>
       <c r="L14" t="str">
         <v>null</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
       </c>
       <c r="B15" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1362,10 +1362,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D15" t="str">
-        <v>emissiepunt</v>
+        <v>lozingspunt</v>
       </c>
       <c r="E15" t="str">
-        <v>Emissiepunt</v>
+        <v>Lozingspunt</v>
       </c>
       <c r="F15" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
@@ -1374,22 +1374,22 @@
         <v>null</v>
       </c>
       <c r="H15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I15" t="str">
         <v>null</v>
       </c>
       <c r="J15" t="str">
-        <v>null</v>
+        <v>Een lozing naar water.</v>
       </c>
       <c r="K15" t="str">
-        <v>null</v>
+        <v>Een lozing naar water.</v>
       </c>
       <c r="L15" t="str">
-        <v>Een regulier emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="M15" t="str">
-        <v>Een regulier emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="N15" t="str">
         <v>null</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="B16" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1430,10 +1430,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D16" t="str">
-        <v>lozingspunt</v>
+        <v>schoorsteen</v>
       </c>
       <c r="E16" t="str">
-        <v>Lozingspunt</v>
+        <v>Schoorsteen</v>
       </c>
       <c r="F16" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
@@ -1442,25 +1442,25 @@
         <v>null</v>
       </c>
       <c r="H16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I16" t="str">
         <v>null</v>
       </c>
       <c r="J16" t="str">
-        <v>null</v>
+        <v>Een schoorsteen.</v>
       </c>
       <c r="K16" t="str">
-        <v>null</v>
+        <v>Een schoorsteen.</v>
       </c>
       <c r="L16" t="str">
-        <v>Een lozing naar water.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="M16" t="str">
-        <v>Een lozing naar water.</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="N16" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="O16" t="str">
         <v>null</v>
@@ -1489,7 +1489,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="B17" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1498,19 +1498,19 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D17" t="str">
-        <v>schoorsteen</v>
+        <v>schoorsteen_horizontale_uitstroom</v>
       </c>
       <c r="E17" t="str">
-        <v>Schoorsteen</v>
+        <v>Schoorsteen met horizontale uitstroom</v>
       </c>
       <c r="F17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>null</v>
       </c>
       <c r="G17" t="str">
         <v>null</v>
       </c>
       <c r="H17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I17" t="str">
         <v>null</v>
@@ -1522,19 +1522,19 @@
         <v>null</v>
       </c>
       <c r="L17" t="str">
-        <v>Een schoorsteen.</v>
+        <v>null</v>
       </c>
       <c r="M17" t="str">
-        <v>Een schoorsteen.</v>
+        <v>null</v>
       </c>
       <c r="N17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="O17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="P17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="Q17" t="str">
         <v>null</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_horizontale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="B18" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1566,10 +1566,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D18" t="str">
-        <v>schoorsteen_horizontale_uitstroom</v>
+        <v>schoorsteen_verticale_uitstroom</v>
       </c>
       <c r="E18" t="str">
-        <v>Schoorsteen met horizontale uitstroom</v>
+        <v>Schoorsteen met verticale uitstroom</v>
       </c>
       <c r="F18" t="str">
         <v>null</v>
@@ -1578,7 +1578,7 @@
         <v>null</v>
       </c>
       <c r="H18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I18" t="str">
         <v>null</v>
@@ -1596,19 +1596,19 @@
         <v>null</v>
       </c>
       <c r="N18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="O18" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="P18" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="Q18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="R18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="S18" t="str">
         <v>null</v>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen_verticale_uitstroom</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
       </c>
       <c r="B19" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1634,28 +1634,28 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="D19" t="str">
-        <v>schoorsteen_verticale_uitstroom</v>
+        <v>schouw</v>
       </c>
       <c r="E19" t="str">
-        <v>Schoorsteen met verticale uitstroom</v>
+        <v>Schouw</v>
       </c>
       <c r="F19" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="G19" t="str">
         <v>null</v>
       </c>
       <c r="H19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I19" t="str">
         <v>null</v>
       </c>
       <c r="J19" t="str">
-        <v>null</v>
+        <v>Een schouw.</v>
       </c>
       <c r="K19" t="str">
-        <v>null</v>
+        <v>Een schouw.</v>
       </c>
       <c r="L19" t="str">
         <v>null</v>
@@ -1670,13 +1670,13 @@
         <v>null</v>
       </c>
       <c r="P19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="Q19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="R19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="S19" t="str">
         <v>null</v>
@@ -1693,31 +1693,31 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen</v>
       </c>
       <c r="B20" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="D20" t="str">
-        <v>schouw</v>
+        <v>GEINSTALLEERD_VERMOGEN</v>
       </c>
       <c r="E20" t="str">
-        <v>Schouw</v>
+        <v>Geinstalleerd vermogen</v>
       </c>
       <c r="F20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="G20" t="str">
-        <v>null</v>
+        <v>http://qudt.org/vocab/unit/MegaW</v>
       </c>
       <c r="H20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I20" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="J20" t="str">
         <v>null</v>
@@ -1726,10 +1726,10 @@
         <v>null</v>
       </c>
       <c r="L20" t="str">
-        <v>Een schouw.</v>
+        <v>null</v>
       </c>
       <c r="M20" t="str">
-        <v>Een schouw.</v>
+        <v>null</v>
       </c>
       <c r="N20" t="str">
         <v>null</v>
@@ -1741,7 +1741,7 @@
         <v>null</v>
       </c>
       <c r="Q20" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="R20" t="str">
         <v>null</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="B21" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1770,28 +1770,28 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="D21" t="str">
-        <v>GEINSTALLEERD_VERMOGEN</v>
+        <v>VERWIJDERDINGS_RENDEMENT</v>
       </c>
       <c r="E21" t="str">
-        <v>Geinstalleerd vermogen</v>
+        <v>Verwijderingsrendement</v>
       </c>
       <c r="F21" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="G21" t="str">
-        <v>null</v>
+        <v>http://qudt.org/vocab/unit/PERCENT</v>
       </c>
       <c r="H21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
       </c>
       <c r="I21" t="str">
-        <v>http://qudt.org/vocab/unit/MegaW</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie</v>
       </c>
       <c r="J21" t="str">
-        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
+        <v>null</v>
       </c>
       <c r="K21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="L21" t="str">
         <v>null</v>
@@ -1812,10 +1812,10 @@
         <v>null</v>
       </c>
       <c r="R21" t="str">
-        <v>null</v>
+        <v>true</v>
       </c>
       <c r="S21" t="str">
-        <v>true</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/chemische_stof</v>
       </c>
       <c r="T21" t="str">
         <v>null</v>
@@ -1829,37 +1829,37 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="B22" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D22" t="str">
-        <v>VERWIJDERDINGS_RENDEMENT</v>
+        <v>directe_stookinstallatie</v>
       </c>
       <c r="E22" t="str">
-        <v>Verwijderingsrendement</v>
+        <v>Directe Stookinstallatie</v>
       </c>
       <c r="F22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="G22" t="str">
         <v>null</v>
       </c>
       <c r="H22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="I22" t="str">
-        <v>http://qudt.org/vocab/unit/PERCENT</v>
+        <v>null</v>
       </c>
       <c r="J22" t="str">
-        <v>http://www.w3.org/2001/XMLSchema#decimal</v>
+        <v>null</v>
       </c>
       <c r="K22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie</v>
+        <v>null</v>
       </c>
       <c r="L22" t="str">
         <v>null</v>
@@ -1868,13 +1868,13 @@
         <v>null</v>
       </c>
       <c r="N22" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="O22" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="P22" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="Q22" t="str">
         <v>null</v>
@@ -1886,10 +1886,10 @@
         <v>null</v>
       </c>
       <c r="T22" t="str">
-        <v>true</v>
+        <v>null</v>
       </c>
       <c r="U22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/chemische_stof</v>
+        <v>null</v>
       </c>
       <c r="V22" t="str">
         <v>null</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie</v>
       </c>
       <c r="B23" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1906,19 +1906,19 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D23" t="str">
-        <v>directe_stookinstallatie</v>
+        <v>filterinstallatie</v>
       </c>
       <c r="E23" t="str">
-        <v>Directe Stookinstallatie</v>
+        <v>Filter Installatie</v>
       </c>
       <c r="F23" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="G23" t="str">
         <v>null</v>
       </c>
       <c r="H23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I23" t="str">
         <v>null</v>
@@ -1942,13 +1942,13 @@
         <v>null</v>
       </c>
       <c r="P23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="Q23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="R23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="S23" t="str">
         <v>null</v>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
       </c>
       <c r="B24" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -1974,10 +1974,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D24" t="str">
-        <v>filterinstallatie</v>
+        <v>installatie</v>
       </c>
       <c r="E24" t="str">
-        <v>Filter Installatie</v>
+        <v>Installatie</v>
       </c>
       <c r="F24" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
@@ -1986,7 +1986,7 @@
         <v>null</v>
       </c>
       <c r="H24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I24" t="str">
         <v>null</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
       </c>
       <c r="B25" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2042,10 +2042,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="D25" t="str">
-        <v>installatie</v>
+        <v>stookinstallatie</v>
       </c>
       <c r="E25" t="str">
-        <v>Installatie</v>
+        <v>Stookinstallatie</v>
       </c>
       <c r="F25" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
@@ -2054,7 +2054,7 @@
         <v>null</v>
       </c>
       <c r="H25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I25" t="str">
         <v>null</v>
@@ -2066,13 +2066,13 @@
         <v>null</v>
       </c>
       <c r="L25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="M25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="N25" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
       </c>
       <c r="O25" t="str">
         <v>null</v>
@@ -2101,28 +2101,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
       </c>
       <c r="B26" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="D26" t="str">
-        <v>stookinstallatie</v>
+        <v>meetput</v>
       </c>
       <c r="E26" t="str">
-        <v>Stookinstallatie</v>
+        <v>Meetput</v>
       </c>
       <c r="F26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="G26" t="str">
         <v>null</v>
       </c>
       <c r="H26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I26" t="str">
         <v>null</v>
@@ -2140,13 +2140,13 @@
         <v>null</v>
       </c>
       <c r="N26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="O26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="P26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/directe_stookinstallatie</v>
+        <v>null</v>
       </c>
       <c r="Q26" t="str">
         <v>null</v>
@@ -2169,22 +2169,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
       </c>
       <c r="B27" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="D27" t="str">
-        <v>meetput</v>
+        <v>grondwaterput</v>
       </c>
       <c r="E27" t="str">
-        <v>Meetput</v>
+        <v>Grondwaterput</v>
       </c>
       <c r="F27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="G27" t="str">
         <v>null</v>
@@ -2237,37 +2237,37 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
       </c>
       <c r="B28" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D28" t="str">
-        <v>grondwaterput</v>
+        <v>EMISSIE</v>
       </c>
       <c r="E28" t="str">
-        <v>Grondwaterput</v>
+        <v>Emissie</v>
       </c>
       <c r="F28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="G28" t="str">
         <v>null</v>
       </c>
       <c r="H28" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I28" t="str">
         <v>null</v>
       </c>
       <c r="J28" t="str">
-        <v>null</v>
+        <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="K28" t="str">
-        <v>null</v>
+        <v>De procedure emissie via een emissiepunt.</v>
       </c>
       <c r="L28" t="str">
         <v>null</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking</v>
       </c>
       <c r="B29" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2314,10 +2314,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D29" t="str">
-        <v>EMISSIE</v>
+        <v>ONTTREKKING</v>
       </c>
       <c r="E29" t="str">
-        <v>Emissie</v>
+        <v>Onttrekking</v>
       </c>
       <c r="F29" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
@@ -2326,22 +2326,22 @@
         <v>null</v>
       </c>
       <c r="H29" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I29" t="str">
         <v>null</v>
       </c>
       <c r="J29" t="str">
-        <v>http://www.w3.org/ns/sosa/Procedure</v>
+        <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="K29" t="str">
-        <v>null</v>
+        <v>De procedure onttrekking via een onttrekingspunt.</v>
       </c>
       <c r="L29" t="str">
-        <v>De procedure emissie via een emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="M29" t="str">
-        <v>De procedure emissie via een emissiepunt.</v>
+        <v>null</v>
       </c>
       <c r="N29" t="str">
         <v>null</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport</v>
       </c>
       <c r="B30" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2382,10 +2382,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D30" t="str">
-        <v>ONTTREKKING</v>
+        <v>TRANSPORT</v>
       </c>
       <c r="E30" t="str">
-        <v>Onttrekking</v>
+        <v>Transport</v>
       </c>
       <c r="F30" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
@@ -2394,22 +2394,22 @@
         <v>null</v>
       </c>
       <c r="H30" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I30" t="str">
         <v>null</v>
       </c>
       <c r="J30" t="str">
-        <v>http://www.w3.org/ns/sosa/Procedure</v>
+        <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="K30" t="str">
-        <v>null</v>
+        <v>De procedure transport tussen twee processen.</v>
       </c>
       <c r="L30" t="str">
-        <v>De procedure onttrekking via een onttrekingspunt.</v>
+        <v>null</v>
       </c>
       <c r="M30" t="str">
-        <v>De procedure onttrekking via een onttrekingspunt.</v>
+        <v>null</v>
       </c>
       <c r="N30" t="str">
         <v>null</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
       </c>
       <c r="B31" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2450,10 +2450,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="D31" t="str">
-        <v>TRANSPORT</v>
+        <v>VERWERKING</v>
       </c>
       <c r="E31" t="str">
-        <v>Transport</v>
+        <v>Verwerking</v>
       </c>
       <c r="F31" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
@@ -2462,22 +2462,22 @@
         <v>null</v>
       </c>
       <c r="H31" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/sosa/Procedure</v>
       </c>
       <c r="I31" t="str">
         <v>null</v>
       </c>
       <c r="J31" t="str">
-        <v>http://www.w3.org/ns/sosa/Procedure</v>
+        <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="K31" t="str">
-        <v>null</v>
+        <v>De procedure verwerking door een installatie.</v>
       </c>
       <c r="L31" t="str">
-        <v>De procedure transport tussen twee processen.</v>
+        <v>null</v>
       </c>
       <c r="M31" t="str">
-        <v>De procedure transport tussen twee processen.</v>
+        <v>null</v>
       </c>
       <c r="N31" t="str">
         <v>null</v>
@@ -2509,43 +2509,43 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
       </c>
       <c r="B32" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D32" t="str">
-        <v>VERWERKING</v>
+        <v>DEFINITIEF_UIT_DIENST</v>
       </c>
       <c r="E32" t="str">
-        <v>Verwerking</v>
+        <v>Definitief uit dienst</v>
       </c>
       <c r="F32" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="G32" t="str">
         <v>null</v>
       </c>
       <c r="H32" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I32" t="str">
         <v>null</v>
       </c>
       <c r="J32" t="str">
-        <v>http://www.w3.org/ns/sosa/Procedure</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="K32" t="str">
-        <v>null</v>
+        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
       </c>
       <c r="L32" t="str">
-        <v>De procedure verwerking door een installatie.</v>
+        <v>null</v>
       </c>
       <c r="M32" t="str">
-        <v>De procedure verwerking door een installatie.</v>
+        <v>null</v>
       </c>
       <c r="N32" t="str">
         <v>null</v>
@@ -2566,7 +2566,7 @@
         <v>null</v>
       </c>
       <c r="T32" t="str">
-        <v>null</v>
+        <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
       <c r="U32" t="str">
         <v>null</v>
@@ -2577,7 +2577,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
       </c>
       <c r="B33" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2586,10 +2586,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D33" t="str">
-        <v>DEFINITIEF_UIT_DIENST</v>
+        <v>IN_DIENST</v>
       </c>
       <c r="E33" t="str">
-        <v>Definitief uit dienst</v>
+        <v>In dienst</v>
       </c>
       <c r="F33" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
@@ -2598,22 +2598,22 @@
         <v>null</v>
       </c>
       <c r="H33" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I33" t="str">
         <v>null</v>
       </c>
       <c r="J33" t="str">
-        <v>http://www.w3.org/ns/adms#</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="K33" t="str">
-        <v>null</v>
+        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
       </c>
       <c r="L33" t="str">
-        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="M33" t="str">
-        <v>De status definitief uit dienst geeft aan dat een entiteit definitief buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="N33" t="str">
         <v>null</v>
@@ -2634,18 +2634,18 @@
         <v>null</v>
       </c>
       <c r="T33" t="str">
-        <v>null</v>
+        <v>http://purl.org/adms/status/Completed</v>
       </c>
       <c r="U33" t="str">
         <v>null</v>
       </c>
       <c r="V33" t="str">
-        <v>http://purl.org/adms/status/Withdrawn</v>
+        <v>null</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
       </c>
       <c r="B34" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2654,10 +2654,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D34" t="str">
-        <v>IN_DIENST</v>
+        <v>ONTMANTELD</v>
       </c>
       <c r="E34" t="str">
-        <v>In dienst</v>
+        <v>Ontmanteld</v>
       </c>
       <c r="F34" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
@@ -2666,22 +2666,22 @@
         <v>null</v>
       </c>
       <c r="H34" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I34" t="str">
         <v>null</v>
       </c>
       <c r="J34" t="str">
-        <v>http://www.w3.org/ns/adms#</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="K34" t="str">
-        <v>null</v>
+        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
       </c>
       <c r="L34" t="str">
-        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="M34" t="str">
-        <v>De status in dienst geeft aan dat een entiteit momenteel in gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="N34" t="str">
         <v>null</v>
@@ -2702,18 +2702,18 @@
         <v>null</v>
       </c>
       <c r="T34" t="str">
-        <v>null</v>
+        <v>http://purl.org/adms/status/Withdrawn</v>
       </c>
       <c r="U34" t="str">
         <v>null</v>
       </c>
       <c r="V34" t="str">
-        <v>http://purl.org/adms/status/Completed</v>
+        <v>null</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
       </c>
       <c r="B35" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2722,10 +2722,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D35" t="str">
-        <v>ONTMANTELD</v>
+        <v>TIJDELIJK_UIT_DIENST</v>
       </c>
       <c r="E35" t="str">
-        <v>Ontmanteld</v>
+        <v>Tijdelijk uit dienst</v>
       </c>
       <c r="F35" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
@@ -2734,22 +2734,22 @@
         <v>null</v>
       </c>
       <c r="H35" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I35" t="str">
         <v>null</v>
       </c>
       <c r="J35" t="str">
-        <v>http://www.w3.org/ns/adms#</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="K35" t="str">
-        <v>null</v>
+        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
       </c>
       <c r="L35" t="str">
-        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+        <v>null</v>
       </c>
       <c r="M35" t="str">
-        <v>De status ontmanteld geeft aan dat een entiteit niet meer bestaat.</v>
+        <v>null</v>
       </c>
       <c r="N35" t="str">
         <v>null</v>
@@ -2770,18 +2770,18 @@
         <v>null</v>
       </c>
       <c r="T35" t="str">
-        <v>null</v>
+        <v>http://purl.org/adms/status/Deprecated</v>
       </c>
       <c r="U35" t="str">
         <v>null</v>
       </c>
       <c r="V35" t="str">
-        <v>http://purl.org/adms/status/Withdrawn</v>
+        <v>null</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
       <c r="B36" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
@@ -2790,10 +2790,10 @@
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="D36" t="str">
-        <v>TIJDELIJK_UIT_DIENST</v>
+        <v>VOORGESTELD</v>
       </c>
       <c r="E36" t="str">
-        <v>Tijdelijk uit dienst</v>
+        <v>Voorgesteld Ontwerp</v>
       </c>
       <c r="F36" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
@@ -2802,22 +2802,22 @@
         <v>null</v>
       </c>
       <c r="H36" t="str">
-        <v>null</v>
+        <v>http://www.w3.org/ns/adms#</v>
       </c>
       <c r="I36" t="str">
         <v>null</v>
       </c>
       <c r="J36" t="str">
-        <v>http://www.w3.org/ns/adms#</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="K36" t="str">
-        <v>null</v>
+        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
       </c>
       <c r="L36" t="str">
-        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="M36" t="str">
-        <v>De status tijdelijk uit dienst geeft aan dat een entiteit tijden buiten gebruik is.</v>
+        <v>null</v>
       </c>
       <c r="N36" t="str">
         <v>null</v>
@@ -2838,33 +2838,33 @@
         <v>null</v>
       </c>
       <c r="T36" t="str">
-        <v>null</v>
+        <v>http://purl.org/adms/status/UnderDevelopment</v>
       </c>
       <c r="U36" t="str">
         <v>null</v>
       </c>
       <c r="V36" t="str">
-        <v>http://purl.org/adms/status/Deprecated</v>
+        <v>null</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
       </c>
       <c r="B37" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>null</v>
       </c>
       <c r="D37" t="str">
-        <v>VOORGESTELD</v>
+        <v>null</v>
       </c>
       <c r="E37" t="str">
-        <v>Voorgesteld Ontwerp</v>
+        <v>null</v>
       </c>
       <c r="F37" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
+        <v>null</v>
       </c>
       <c r="G37" t="str">
         <v>null</v>
@@ -2876,16 +2876,16 @@
         <v>null</v>
       </c>
       <c r="J37" t="str">
-        <v>http://www.w3.org/ns/adms#</v>
+        <v>null</v>
       </c>
       <c r="K37" t="str">
         <v>null</v>
       </c>
       <c r="L37" t="str">
-        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+        <v>null</v>
       </c>
       <c r="M37" t="str">
-        <v>De status voorgesteld geeft aan dat een entiteit voorsgesteld is door de Vlaamse Overheid.</v>
+        <v>null</v>
       </c>
       <c r="N37" t="str">
         <v>null</v>
@@ -2909,15 +2909,15 @@
         <v>null</v>
       </c>
       <c r="U37" t="str">
-        <v>null</v>
+        <v>http://qudt.org/vocab/unit/DEG_C|http://qudt.org/vocab/unit/K|http://qudt.org/vocab/unit/M|http://qudt.org/vocab/unit/MegaW|http://qudt.org/vocab/unit/MicroGM-PER-L|http://qudt.org/vocab/unit/MilliGM-PER-L|http://qudt.org/vocab/unit/NanoGM-PER-L|http://qudt.org/vocab/unit/PERCENT|http://qudt.org/vocab/unit/PPB|http://qudt.org/vocab/unit/PPM</v>
       </c>
       <c r="V37" t="str">
-        <v>http://purl.org/adms/status/UnderDevelopment</v>
+        <v>null</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/eenheden</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
       </c>
       <c r="B38" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -2929,13 +2929,13 @@
         <v>null</v>
       </c>
       <c r="E38" t="str">
-        <v>null</v>
+        <v>Emissiepunt eigenschappen</v>
       </c>
       <c r="F38" t="str">
         <v>null</v>
       </c>
       <c r="G38" t="str">
-        <v>http://qudt.org/vocab/unit/DEG_C|http://qudt.org/vocab/unit/K|http://qudt.org/vocab/unit/M|http://qudt.org/vocab/unit/MegaW|http://qudt.org/vocab/unit/MicroGM-PER-L|http://qudt.org/vocab/unit/MilliGM-PER-L|http://qudt.org/vocab/unit/NanoGM-PER-L|http://qudt.org/vocab/unit/PERCENT|http://qudt.org/vocab/unit/PPB|http://qudt.org/vocab/unit/PPM</v>
+        <v>null</v>
       </c>
       <c r="H38" t="str">
         <v>null</v>
@@ -2944,10 +2944,10 @@
         <v>null</v>
       </c>
       <c r="J38" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="K38" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
       </c>
       <c r="L38" t="str">
         <v>null</v>
@@ -2977,15 +2977,15 @@
         <v>null</v>
       </c>
       <c r="U38" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
       </c>
       <c r="V38" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
       </c>
       <c r="B39" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -2997,31 +2997,31 @@
         <v>null</v>
       </c>
       <c r="E39" t="str">
-        <v>Emissiepunt eigenschappen</v>
+        <v>Emissiepunt types</v>
       </c>
       <c r="F39" t="str">
         <v>null</v>
       </c>
       <c r="G39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-diameter|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-eigenschappen/schouw-hoogte</v>
+        <v>null</v>
       </c>
       <c r="H39" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="I39" t="str">
         <v>null</v>
       </c>
       <c r="J39" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="K39" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten emissiepunten.</v>
       </c>
       <c r="L39" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="M39" t="str">
-        <v>Een typering van verschillende eigenschappen voor emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="N39" t="str">
         <v>null</v>
@@ -3045,15 +3045,15 @@
         <v>null</v>
       </c>
       <c r="U39" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
       </c>
       <c r="V39" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/emissiepunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
       </c>
       <c r="B40" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -3065,31 +3065,31 @@
         <v>null</v>
       </c>
       <c r="E40" t="str">
-        <v>Emissiepunt types</v>
+        <v>Installatie eigenschappen</v>
       </c>
       <c r="F40" t="str">
         <v>null</v>
       </c>
       <c r="G40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schouw|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/emissiepunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/lozingspunt|https://data.omgeving.vlaanderen.be/id/concept/riepr/emissiepunt-type/schoorsteen</v>
+        <v>null</v>
       </c>
       <c r="H40" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I40" t="str">
         <v>null</v>
       </c>
       <c r="J40" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="K40" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende eigenschappen voor installaties.</v>
       </c>
       <c r="L40" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="M40" t="str">
-        <v>Een typering van verschillende soorten emissiepunten.</v>
+        <v>null</v>
       </c>
       <c r="N40" t="str">
         <v>null</v>
@@ -3113,15 +3113,15 @@
         <v>null</v>
       </c>
       <c r="U40" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
       </c>
       <c r="V40" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_eigenschappen</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
       </c>
       <c r="B41" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -3133,31 +3133,31 @@
         <v>null</v>
       </c>
       <c r="E41" t="str">
-        <v>Installatie eigenschappen</v>
+        <v>Installatie types</v>
       </c>
       <c r="F41" t="str">
         <v>null</v>
       </c>
       <c r="G41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/geinstalleerd_vermogen|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-eigenschappen/verwijderingsrendement</v>
+        <v>null</v>
       </c>
       <c r="H41" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_eigenschappen</v>
+        <v>null</v>
       </c>
       <c r="I41" t="str">
         <v>null</v>
       </c>
       <c r="J41" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="K41" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten installaties.</v>
       </c>
       <c r="L41" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>null</v>
       </c>
       <c r="M41" t="str">
-        <v>Een typering van verschillende eigenschappen voor installaties.</v>
+        <v>null</v>
       </c>
       <c r="N41" t="str">
         <v>null</v>
@@ -3181,15 +3181,15 @@
         <v>null</v>
       </c>
       <c r="U41" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
       </c>
       <c r="V41" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/installatie_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
       </c>
       <c r="B42" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -3201,16 +3201,16 @@
         <v>null</v>
       </c>
       <c r="E42" t="str">
-        <v>Installatie types</v>
+        <v>Meetpunt types</v>
       </c>
       <c r="F42" t="str">
         <v>null</v>
       </c>
       <c r="G42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/stookinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/filterinstallatie|https://data.omgeving.vlaanderen.be/id/concept/riepr/installatie-type/installatie</v>
+        <v>null</v>
       </c>
       <c r="H42" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/systeem_type</v>
+        <v>null</v>
       </c>
       <c r="I42" t="str">
         <v>null</v>
@@ -3222,10 +3222,10 @@
         <v>null</v>
       </c>
       <c r="L42" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>null</v>
       </c>
       <c r="M42" t="str">
-        <v>Een typering van verschillende soorten installaties.</v>
+        <v>null</v>
       </c>
       <c r="N42" t="str">
         <v>null</v>
@@ -3249,7 +3249,7 @@
         <v>null</v>
       </c>
       <c r="U42" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
       </c>
       <c r="V42" t="str">
         <v>null</v>
@@ -3257,25 +3257,25 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/meetpunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
       </c>
       <c r="B43" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>null</v>
       </c>
       <c r="D43" t="str">
         <v>null</v>
       </c>
       <c r="E43" t="str">
-        <v>Meetpunt types</v>
+        <v>Onttrekkingspunt types</v>
       </c>
       <c r="F43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>null</v>
       </c>
       <c r="G43" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/meetpunt-type/meetput</v>
+        <v>null</v>
       </c>
       <c r="H43" t="str">
         <v>null</v>
@@ -3284,10 +3284,10 @@
         <v>null</v>
       </c>
       <c r="J43" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="K43" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
       </c>
       <c r="L43" t="str">
         <v>null</v>
@@ -3317,7 +3317,7 @@
         <v>null</v>
       </c>
       <c r="U43" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
       </c>
       <c r="V43" t="str">
         <v>null</v>
@@ -3325,25 +3325,25 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/onttrekkingspunt_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
       </c>
       <c r="B44" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Concept|http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
+        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
       <c r="C44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>null</v>
       </c>
       <c r="D44" t="str">
         <v>null</v>
       </c>
       <c r="E44" t="str">
-        <v>Onttrekkingspunt types</v>
+        <v>Procedure types</v>
       </c>
       <c r="F44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/rie-iepr/conceptscheme_systeem_type</v>
+        <v>null</v>
       </c>
       <c r="G44" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/onttrekkingspunt-type/grondwaterput</v>
+        <v>null</v>
       </c>
       <c r="H44" t="str">
         <v>null</v>
@@ -3352,16 +3352,16 @@
         <v>null</v>
       </c>
       <c r="J44" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende procedures.</v>
       </c>
       <c r="K44" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende procedures.</v>
       </c>
       <c r="L44" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>null</v>
       </c>
       <c r="M44" t="str">
-        <v>Een typering van verschillende soorten onttrekkingspunten.</v>
+        <v>null</v>
       </c>
       <c r="N44" t="str">
         <v>null</v>
@@ -3385,7 +3385,7 @@
         <v>null</v>
       </c>
       <c r="U44" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
       </c>
       <c r="V44" t="str">
         <v>null</v>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/procedure_type</v>
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
       </c>
       <c r="B45" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
@@ -3405,13 +3405,13 @@
         <v>null</v>
       </c>
       <c r="E45" t="str">
-        <v>Procedure types</v>
+        <v>Status types</v>
       </c>
       <c r="F45" t="str">
         <v>null</v>
       </c>
       <c r="G45" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/emissie|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/onttrekking|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/transport|https://data.omgeving.vlaanderen.be/id/concept/riepr/procedure-type/verwerking</v>
+        <v>null</v>
       </c>
       <c r="H45" t="str">
         <v>null</v>
@@ -3420,16 +3420,16 @@
         <v>null</v>
       </c>
       <c r="J45" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
       <c r="K45" t="str">
-        <v>null</v>
+        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
       </c>
       <c r="L45" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>null</v>
       </c>
       <c r="M45" t="str">
-        <v>Een typering van verschillende procedures.</v>
+        <v>null</v>
       </c>
       <c r="N45" t="str">
         <v>null</v>
@@ -3453,83 +3453,15 @@
         <v>null</v>
       </c>
       <c r="U45" t="str">
-        <v>null</v>
+        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
       </c>
       <c r="V45" t="str">
-        <v>null</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/riepr/status_type</v>
-      </c>
-      <c r="B46" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
-      </c>
-      <c r="C46" t="str">
-        <v>null</v>
-      </c>
-      <c r="D46" t="str">
-        <v>null</v>
-      </c>
-      <c r="E46" t="str">
-        <v>Status types</v>
-      </c>
-      <c r="F46" t="str">
-        <v>null</v>
-      </c>
-      <c r="G46" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/definitief_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/in_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/ontmanteld|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/tijdelijk_uit_dienst|https://data.omgeving.vlaanderen.be/id/concept/riepr/status-type/voorgesteld</v>
-      </c>
-      <c r="H46" t="str">
-        <v>null</v>
-      </c>
-      <c r="I46" t="str">
-        <v>null</v>
-      </c>
-      <c r="J46" t="str">
-        <v>null</v>
-      </c>
-      <c r="K46" t="str">
-        <v>null</v>
-      </c>
-      <c r="L46" t="str">
-        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
-      </c>
-      <c r="M46" t="str">
-        <v>Een typering van verschillende statussen (actief, inactief, ...).</v>
-      </c>
-      <c r="N46" t="str">
-        <v>null</v>
-      </c>
-      <c r="O46" t="str">
-        <v>null</v>
-      </c>
-      <c r="P46" t="str">
-        <v>null</v>
-      </c>
-      <c r="Q46" t="str">
-        <v>null</v>
-      </c>
-      <c r="R46" t="str">
-        <v>null</v>
-      </c>
-      <c r="S46" t="str">
-        <v>null</v>
-      </c>
-      <c r="T46" t="str">
-        <v>null</v>
-      </c>
-      <c r="U46" t="str">
-        <v>null</v>
-      </c>
-      <c r="V46" t="str">
         <v>null</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V45"/>
   </ignoredErrors>
 </worksheet>
 </file>